--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 10\Desktop\Pagina distri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB83E30D-CBEF-42E9-9858-C427BF92D8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831F8AFD-023E-4848-B127-E97CDEB6CAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="165" windowWidth="10185" windowHeight="10515" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6699" uniqueCount="3904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6482" uniqueCount="3907">
   <si>
     <t>BRM-050</t>
   </si>
@@ -11705,9 +11705,6 @@
     <t>CMA-005</t>
   </si>
   <si>
-    <t>Eastaman</t>
-  </si>
-  <si>
     <t>Eurotech</t>
   </si>
   <si>
@@ -11739,6 +11736,18 @@
   </si>
   <si>
     <t>Disco desbaste escofina inclinado</t>
+  </si>
+  <si>
+    <t>cerrajeria</t>
+  </si>
+  <si>
+    <t>Cerrajería</t>
+  </si>
+  <si>
+    <t>Jardinería</t>
+  </si>
+  <si>
+    <t>Construcción</t>
   </si>
 </sst>
 </file>
@@ -13578,8 +13587,8 @@
     <col min="2" max="2" width="36.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="0.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" style="5" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.7109375" style="1" customWidth="1"/>
@@ -13610,7 +13619,7 @@
         <v>1646</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -13631,7 +13640,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>1647</v>
+        <v>3905</v>
       </c>
       <c r="G2" s="143">
         <v>6604.3</v>
@@ -13655,7 +13664,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G3" s="143">
         <v>3764.6</v>
@@ -13679,7 +13688,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G4" s="143">
         <v>7241.9</v>
@@ -13703,7 +13712,7 @@
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G5" s="143">
         <v>4121</v>
@@ -13726,9 +13735,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="143">
         <v>1036.7</v>
       </c>
@@ -13751,9 +13758,7 @@
         <v>1256</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="143">
         <v>5192.3999999999996</v>
       </c>
@@ -13776,9 +13781,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="143">
         <v>3285.6</v>
       </c>
@@ -13801,9 +13804,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="143">
         <v>877.8</v>
       </c>
@@ -13827,7 +13828,7 @@
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G10" s="143">
         <v>1369.4</v>
@@ -13852,7 +13853,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G11" s="144">
         <v>1234.3</v>
@@ -13877,7 +13878,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G12" s="143">
         <v>2196</v>
@@ -13902,7 +13903,7 @@
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G13" s="143">
         <v>3728.3</v>
@@ -13927,7 +13928,7 @@
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G14" s="143">
         <v>10323.5</v>
@@ -13951,9 +13952,7 @@
         <v>36</v>
       </c>
       <c r="E15" s="58"/>
-      <c r="F15" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="143">
         <v>1787.6</v>
       </c>
@@ -13977,7 +13976,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G16" s="143">
         <v>1072.4000000000001</v>
@@ -14002,7 +14001,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G17" s="143">
         <v>1294.8</v>
@@ -14027,7 +14026,7 @@
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G18" s="143">
         <v>1738</v>
@@ -14052,7 +14051,7 @@
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G19" s="143">
         <v>2723.9</v>
@@ -14077,7 +14076,7 @@
       </c>
       <c r="E20" s="59"/>
       <c r="F20" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G20" s="143">
         <v>2723.9</v>
@@ -14102,7 +14101,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G21" s="143">
         <v>5107.2</v>
@@ -14127,7 +14126,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>3892</v>
+        <v>3906</v>
       </c>
       <c r="G22" s="143">
         <v>6060.6</v>
@@ -14152,7 +14151,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G23" s="143">
         <v>5277.5</v>
@@ -14177,7 +14176,7 @@
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G24" s="144">
         <v>3217.3</v>
@@ -14202,7 +14201,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G25" s="145">
         <v>3511.2</v>
@@ -14227,7 +14226,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G26" s="143">
         <v>5022.1000000000004</v>
@@ -14251,9 +14250,7 @@
         <v>1138</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="143">
         <v>4564.6000000000004</v>
       </c>
@@ -14276,9 +14273,7 @@
         <v>69</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="143">
         <v>468</v>
       </c>
@@ -14301,9 +14296,7 @@
         <v>685</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="143">
         <v>260</v>
       </c>
@@ -14326,9 +14319,7 @@
         <v>856</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="144">
         <v>5969.1</v>
       </c>
@@ -14352,9 +14343,7 @@
         <v>73</v>
       </c>
       <c r="E31" s="6"/>
-      <c r="F31" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="143">
         <v>4936.6000000000004</v>
       </c>
@@ -14377,9 +14366,7 @@
         <v>752</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="143">
         <v>5400</v>
       </c>
@@ -14402,9 +14389,7 @@
         <v>753</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="143">
         <v>5400</v>
       </c>
@@ -14427,9 +14412,7 @@
         <v>754</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="143">
         <v>5400</v>
       </c>
@@ -14453,7 +14436,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>1647</v>
+        <v>3905</v>
       </c>
       <c r="G35" s="145">
         <v>4915.7</v>
@@ -14478,7 +14461,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>1647</v>
+        <v>3905</v>
       </c>
       <c r="G36" s="145">
         <v>546.9</v>
@@ -14503,7 +14486,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>1647</v>
+        <v>3905</v>
       </c>
       <c r="G37" s="143">
         <v>2274.3000000000002</v>
@@ -14527,9 +14510,7 @@
         <v>89</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="143">
         <v>7660.8</v>
       </c>
@@ -14552,9 +14533,7 @@
         <v>90</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="143">
         <v>1327.9</v>
       </c>
@@ -14577,9 +14556,7 @@
         <v>797</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="144">
         <v>2723.9</v>
       </c>
@@ -14602,9 +14579,7 @@
         <v>1171</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="145">
         <v>5107.3</v>
       </c>
@@ -14627,9 +14602,7 @@
         <v>92</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>1480</v>
-      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="143">
         <v>11916.8</v>
       </c>
@@ -14652,9 +14625,7 @@
         <v>1217</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="144">
         <v>12113.7</v>
       </c>
@@ -14677,9 +14648,7 @@
         <v>95</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="143">
         <v>1957.7</v>
       </c>
@@ -14702,9 +14671,7 @@
         <v>99</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="143">
         <v>3288</v>
       </c>
@@ -14727,9 +14694,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="143">
         <v>4697.1000000000004</v>
       </c>
@@ -14752,9 +14717,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="143">
         <v>6144.6</v>
       </c>
@@ -14778,7 +14741,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>1647</v>
+        <v>3904</v>
       </c>
       <c r="G48" s="144">
         <v>2475.4</v>
@@ -14803,7 +14766,7 @@
       </c>
       <c r="E49" s="142"/>
       <c r="F49" s="2" t="s">
-        <v>1647</v>
+        <v>3904</v>
       </c>
       <c r="G49" s="143">
         <v>3212.8</v>
@@ -14828,7 +14791,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>1647</v>
+        <v>3904</v>
       </c>
       <c r="G50" s="143">
         <v>4562.5</v>
@@ -14853,7 +14816,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>1647</v>
+        <v>3904</v>
       </c>
       <c r="G51" s="146">
         <v>5958.4</v>
@@ -14878,7 +14841,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G52" s="143">
         <v>1957.8</v>
@@ -14903,7 +14866,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G53" s="144">
         <v>3192</v>
@@ -14928,7 +14891,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G54" s="143">
         <v>22301.8</v>
@@ -14954,7 +14917,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>1480</v>
+        <v>3906</v>
       </c>
       <c r="G55" s="144">
         <v>1578.2</v>
@@ -14978,9 +14941,7 @@
         <v>121</v>
       </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F56" s="2"/>
       <c r="G56" s="145">
         <v>34899.199999999997</v>
       </c>
@@ -15004,7 +14965,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>1647</v>
+        <v>3904</v>
       </c>
       <c r="G57" s="143">
         <v>747.9</v>
@@ -15028,9 +14989,7 @@
         <v>125</v>
       </c>
       <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="143">
         <v>10469.799999999999</v>
       </c>
@@ -15053,9 +15012,7 @@
         <v>818</v>
       </c>
       <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F59" s="2"/>
       <c r="G59" s="143">
         <v>12087.2</v>
       </c>
@@ -15078,9 +15035,7 @@
         <v>820</v>
       </c>
       <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="143">
         <v>17024</v>
       </c>
@@ -15104,7 +15059,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G61" s="143">
         <v>1895.3</v>
@@ -15129,7 +15084,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G62" s="143">
         <v>1895.3</v>
@@ -15154,7 +15109,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G63" s="143">
         <v>544.79999999999995</v>
@@ -15179,7 +15134,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G64" s="143">
         <v>885.2</v>
@@ -15204,7 +15159,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G65" s="143">
         <v>3089.9</v>
@@ -15229,7 +15184,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G66" s="143">
         <v>7328.3</v>
@@ -15254,7 +15209,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G67" s="143">
         <v>10866.1</v>
@@ -15279,7 +15234,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G68" s="143">
         <v>14277.6</v>
@@ -15304,7 +15259,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G69" s="147">
         <v>4652.3999999999996</v>
@@ -15316,18 +15271,16 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B70" s="34" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="C70" s="37" t="s">
         <v>1647</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="E70" s="2"/>
-      <c r="F70" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F70" s="2"/>
       <c r="G70" s="147">
         <v>54796</v>
       </c>
@@ -15338,18 +15291,16 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B71" s="34" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="C71" s="37" t="s">
         <v>1647</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F71" s="2"/>
       <c r="G71" s="147">
         <v>2000</v>
       </c>
@@ -15373,7 +15324,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G72" s="143">
         <v>2894.1</v>
@@ -15398,7 +15349,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G73" s="143">
         <v>2194.5</v>
@@ -15423,7 +15374,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G74" s="148">
         <v>1158.7</v>
@@ -15448,9 +15399,7 @@
         <v>954</v>
       </c>
       <c r="E75" s="2"/>
-      <c r="F75" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="37">
         <v>3072.3</v>
       </c>
@@ -15473,9 +15422,7 @@
         <v>154</v>
       </c>
       <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="149">
         <v>17117.099999999999</v>
       </c>
@@ -15497,7 +15444,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G77" s="37">
         <v>1229</v>
@@ -15522,7 +15469,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G78" s="150">
         <v>2989.2</v>
@@ -15547,7 +15494,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G79" s="150">
         <v>3916.9</v>
@@ -15571,9 +15518,7 @@
         <v>160</v>
       </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F80" s="2"/>
       <c r="G80" s="37">
         <v>12768</v>
       </c>
@@ -15596,9 +15541,7 @@
         <v>823</v>
       </c>
       <c r="E81" s="2"/>
-      <c r="F81" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F81" s="2"/>
       <c r="G81" s="37">
         <v>19092.2</v>
       </c>
@@ -15621,9 +15564,7 @@
         <v>163</v>
       </c>
       <c r="E82" s="2"/>
-      <c r="F82" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F82" s="2"/>
       <c r="G82" s="37">
         <v>20638.099999999999</v>
       </c>
@@ -15646,9 +15587,7 @@
         <v>167</v>
       </c>
       <c r="E83" s="2"/>
-      <c r="F83" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F83" s="2"/>
       <c r="G83" s="151">
         <v>21280</v>
       </c>
@@ -15671,9 +15610,7 @@
         <v>171</v>
       </c>
       <c r="E84" s="2"/>
-      <c r="F84" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F84" s="2"/>
       <c r="G84" s="143">
         <v>46179.4</v>
       </c>
@@ -15697,7 +15634,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G85" s="143">
         <v>1782.6</v>
@@ -15722,7 +15659,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G86" s="143">
         <v>31920</v>
@@ -15747,7 +15684,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G87" s="145">
         <v>2229.6</v>
@@ -15772,7 +15709,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G88" s="143">
         <v>1489.6</v>
@@ -15796,9 +15733,7 @@
         <v>888</v>
       </c>
       <c r="E89" s="2"/>
-      <c r="F89" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F89" s="2"/>
       <c r="G89" s="145">
         <v>24490.7</v>
       </c>
@@ -15822,7 +15757,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G90" s="143">
         <v>8778</v>
@@ -15847,7 +15782,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G91" s="143">
         <v>854.1</v>
@@ -15872,7 +15807,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G92" s="143">
         <v>1957.8</v>
@@ -15897,7 +15832,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G93" s="144">
         <v>2587.6999999999998</v>
@@ -15922,7 +15857,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G94" s="146">
         <v>4256</v>
@@ -15947,7 +15882,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G95" s="37">
         <v>5958.4</v>
@@ -15972,7 +15907,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G96" s="144">
         <v>766.1</v>
@@ -15997,7 +15932,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G97" s="144">
         <v>51072</v>
@@ -16022,7 +15957,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G98" s="144">
         <v>62988.800000000003</v>
@@ -16047,7 +15982,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G99" s="143">
         <v>2633.4</v>
@@ -16072,7 +16007,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G100" s="143">
         <v>2809</v>
@@ -16097,7 +16032,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>1647</v>
+        <v>3906</v>
       </c>
       <c r="G101" s="143">
         <v>3072.3</v>
@@ -16121,9 +16056,7 @@
         <v>194</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F102" s="2"/>
       <c r="G102" s="143">
         <v>8171.6</v>
       </c>
@@ -16146,9 +16079,7 @@
         <v>726</v>
       </c>
       <c r="E103" s="2"/>
-      <c r="F103" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F103" s="2"/>
       <c r="G103" s="143">
         <v>1316.7</v>
       </c>
@@ -16171,9 +16102,7 @@
         <v>1083</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F104" s="2"/>
       <c r="G104" s="143">
         <v>4389</v>
       </c>
@@ -16198,9 +16127,7 @@
         <v>204</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F105" s="2"/>
       <c r="G105" s="143">
         <v>3472.9</v>
       </c>
@@ -16223,9 +16150,7 @@
         <v>208</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F106" s="2"/>
       <c r="G106" s="143">
         <v>957.6</v>
       </c>
@@ -16236,13 +16161,13 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B107" s="26" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="C107" s="37" t="s">
         <v>1647</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
@@ -16268,9 +16193,7 @@
         <v>1074</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F108" s="2"/>
       <c r="G108" s="144">
         <v>10554.9</v>
       </c>
@@ -16293,9 +16216,7 @@
         <v>212</v>
       </c>
       <c r="E109" s="2"/>
-      <c r="F109" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F109" s="2"/>
       <c r="G109" s="143">
         <v>985.6</v>
       </c>
@@ -16318,9 +16239,7 @@
         <v>216</v>
       </c>
       <c r="E110" s="2"/>
-      <c r="F110" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F110" s="2"/>
       <c r="G110" s="14"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
@@ -16341,9 +16260,7 @@
         <v>219</v>
       </c>
       <c r="E111" s="2"/>
-      <c r="F111" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F111" s="2"/>
       <c r="G111" s="14"/>
       <c r="H111" s="58"/>
       <c r="I111" s="2"/>
@@ -16364,9 +16281,7 @@
         <v>1193</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F112" s="2"/>
       <c r="G112" s="14"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -16387,9 +16302,7 @@
         <v>223</v>
       </c>
       <c r="E113" s="2"/>
-      <c r="F113" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F113" s="2"/>
       <c r="G113" s="14"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
@@ -16410,9 +16323,7 @@
         <v>226</v>
       </c>
       <c r="E114" s="2"/>
-      <c r="F114" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F114" s="2"/>
       <c r="G114" s="14"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
@@ -16433,9 +16344,7 @@
         <v>228</v>
       </c>
       <c r="E115" s="2"/>
-      <c r="F115" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F115" s="2"/>
       <c r="G115" s="14"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
@@ -16456,9 +16365,7 @@
         <v>233</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F116" s="2"/>
       <c r="G116" s="14"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -16479,9 +16386,7 @@
         <v>237</v>
       </c>
       <c r="E117" s="2"/>
-      <c r="F117" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F117" s="2"/>
       <c r="G117" s="14"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -16502,9 +16407,7 @@
         <v>240</v>
       </c>
       <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F118" s="2"/>
       <c r="G118" s="14"/>
       <c r="H118" s="58"/>
       <c r="I118" s="2"/>
@@ -16525,9 +16428,7 @@
         <v>244</v>
       </c>
       <c r="E119" s="2"/>
-      <c r="F119" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F119" s="2"/>
       <c r="G119" s="14"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -16548,9 +16449,7 @@
         <v>248</v>
       </c>
       <c r="E120" s="2"/>
-      <c r="F120" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F120" s="2"/>
       <c r="G120" s="14"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
@@ -16571,9 +16470,7 @@
         <v>252</v>
       </c>
       <c r="E121" s="2"/>
-      <c r="F121" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F121" s="2"/>
       <c r="G121" s="14"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
@@ -16594,9 +16491,7 @@
         <v>256</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F122" s="2"/>
       <c r="G122" s="14"/>
       <c r="H122" s="58"/>
       <c r="I122" s="2"/>
@@ -16618,9 +16513,7 @@
         <v>260</v>
       </c>
       <c r="E123" s="2"/>
-      <c r="F123" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F123" s="2"/>
       <c r="G123" s="14"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
@@ -16641,9 +16534,7 @@
         <v>264</v>
       </c>
       <c r="E124" s="2"/>
-      <c r="F124" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F124" s="2"/>
       <c r="G124" s="14"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
@@ -16664,9 +16555,7 @@
         <v>266</v>
       </c>
       <c r="E125" s="2"/>
-      <c r="F125" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F125" s="2"/>
       <c r="G125" s="14"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
@@ -16687,9 +16576,7 @@
         <v>918</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F126" s="2"/>
       <c r="G126" s="14"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
@@ -16710,9 +16597,7 @@
         <v>1150</v>
       </c>
       <c r="E127" s="2"/>
-      <c r="F127" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F127" s="2"/>
       <c r="G127" s="14"/>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
@@ -16733,9 +16618,7 @@
         <v>838</v>
       </c>
       <c r="E128" s="2"/>
-      <c r="F128" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F128" s="2"/>
       <c r="G128" s="14"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
@@ -16756,9 +16639,7 @@
         <v>270</v>
       </c>
       <c r="E129" s="2"/>
-      <c r="F129" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F129" s="2"/>
       <c r="G129" s="14"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
@@ -16779,9 +16660,7 @@
         <v>274</v>
       </c>
       <c r="E130" s="2"/>
-      <c r="F130" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F130" s="2"/>
       <c r="G130" s="14"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
@@ -16802,9 +16681,7 @@
         <v>277</v>
       </c>
       <c r="E131" s="2"/>
-      <c r="F131" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F131" s="2"/>
       <c r="G131" s="14"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
@@ -16825,9 +16702,7 @@
         <v>280</v>
       </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F132" s="2"/>
       <c r="G132" s="14"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
@@ -16848,9 +16723,7 @@
         <v>878</v>
       </c>
       <c r="E133" s="2"/>
-      <c r="F133" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F133" s="2"/>
       <c r="G133" s="14"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
@@ -16871,9 +16744,7 @@
         <v>283</v>
       </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F134" s="2"/>
       <c r="G134" s="14"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
@@ -16894,9 +16765,7 @@
         <v>286</v>
       </c>
       <c r="E135" s="2"/>
-      <c r="F135" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F135" s="2"/>
       <c r="G135" s="14"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
@@ -16917,9 +16786,7 @@
         <v>289</v>
       </c>
       <c r="E136" s="2"/>
-      <c r="F136" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F136" s="2"/>
       <c r="G136" s="14"/>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
@@ -16940,9 +16807,7 @@
         <v>292</v>
       </c>
       <c r="E137" s="2"/>
-      <c r="F137" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F137" s="2"/>
       <c r="G137" s="14"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
@@ -16963,9 +16828,7 @@
         <v>294</v>
       </c>
       <c r="E138" s="2"/>
-      <c r="F138" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F138" s="2"/>
       <c r="G138" s="14"/>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
@@ -16986,9 +16849,7 @@
         <v>296</v>
       </c>
       <c r="E139" s="2"/>
-      <c r="F139" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F139" s="2"/>
       <c r="G139" s="14"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
@@ -17009,9 +16870,7 @@
         <v>298</v>
       </c>
       <c r="E140" s="2"/>
-      <c r="F140" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F140" s="2"/>
       <c r="G140" s="14"/>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
@@ -17032,9 +16891,7 @@
         <v>300</v>
       </c>
       <c r="E141" s="2"/>
-      <c r="F141" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F141" s="2"/>
       <c r="G141" s="14"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
@@ -17055,9 +16912,7 @@
         <v>304</v>
       </c>
       <c r="E142" s="2"/>
-      <c r="F142" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F142" s="2"/>
       <c r="G142" s="14"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
@@ -17078,9 +16933,7 @@
         <v>308</v>
       </c>
       <c r="E143" s="2"/>
-      <c r="F143" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F143" s="2"/>
       <c r="G143" s="14"/>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
@@ -17101,9 +16954,7 @@
         <v>312</v>
       </c>
       <c r="E144" s="2"/>
-      <c r="F144" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F144" s="2"/>
       <c r="G144" s="14"/>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
@@ -17124,9 +16975,7 @@
         <v>314</v>
       </c>
       <c r="E145" s="2"/>
-      <c r="F145" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F145" s="2"/>
       <c r="G145" s="14"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
@@ -17147,9 +16996,7 @@
         <v>317</v>
       </c>
       <c r="E146" s="2"/>
-      <c r="F146" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F146" s="2"/>
       <c r="G146" s="14"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
@@ -17170,9 +17017,7 @@
         <v>196</v>
       </c>
       <c r="E147" s="2"/>
-      <c r="F147" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F147" s="2"/>
       <c r="G147" s="14"/>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
@@ -17193,9 +17038,7 @@
         <v>198</v>
       </c>
       <c r="E148" s="2"/>
-      <c r="F148" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F148" s="2"/>
       <c r="G148" s="14"/>
       <c r="H148" s="61"/>
       <c r="I148" s="2"/>
@@ -17216,9 +17059,7 @@
         <v>922</v>
       </c>
       <c r="E149" s="2"/>
-      <c r="F149" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F149" s="2"/>
       <c r="G149" s="14"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
@@ -17239,9 +17080,7 @@
         <v>200</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F150" s="2"/>
       <c r="G150" s="14"/>
       <c r="J150" s="3"/>
       <c r="K150" s="11"/>
@@ -17260,9 +17099,7 @@
         <v>749</v>
       </c>
       <c r="E151" s="2"/>
-      <c r="F151" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F151" s="2"/>
       <c r="G151" s="14"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
@@ -17283,9 +17120,7 @@
         <v>1085</v>
       </c>
       <c r="E152" s="2"/>
-      <c r="F152" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F152" s="2"/>
       <c r="G152" s="14"/>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
@@ -17306,9 +17141,7 @@
         <v>1087</v>
       </c>
       <c r="E153" s="2"/>
-      <c r="F153" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F153" s="2"/>
       <c r="G153" s="14"/>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
@@ -17329,9 +17162,7 @@
         <v>870</v>
       </c>
       <c r="E154" s="2"/>
-      <c r="F154" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F154" s="2"/>
       <c r="G154" s="14"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
@@ -17352,9 +17183,7 @@
         <v>302</v>
       </c>
       <c r="E155" s="2"/>
-      <c r="F155" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F155" s="2"/>
       <c r="G155" s="14"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
@@ -17375,9 +17204,7 @@
         <v>1105</v>
       </c>
       <c r="E156" s="2"/>
-      <c r="F156" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F156" s="2"/>
       <c r="G156" s="14"/>
       <c r="H156" s="59"/>
       <c r="I156" s="59"/>
@@ -17398,9 +17225,7 @@
         <v>1108</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F157" s="2"/>
       <c r="G157" s="14"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
@@ -17421,9 +17246,7 @@
         <v>306</v>
       </c>
       <c r="E158" s="2"/>
-      <c r="F158" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F158" s="2"/>
       <c r="G158" s="14"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
@@ -17444,9 +17267,7 @@
         <v>310</v>
       </c>
       <c r="E159" s="2"/>
-      <c r="F159" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F159" s="2"/>
       <c r="G159" s="14"/>
       <c r="H159" s="58"/>
       <c r="I159" s="2"/>
@@ -17467,9 +17288,7 @@
         <v>316</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F160" s="2"/>
       <c r="G160" s="14"/>
       <c r="H160" s="58"/>
       <c r="I160" s="2"/>
@@ -17481,18 +17300,16 @@
         <v>162</v>
       </c>
       <c r="B161" s="26" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="C161" s="37" t="s">
         <v>1647</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="E161" s="2"/>
-      <c r="F161" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F161" s="2"/>
       <c r="G161" s="14"/>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
@@ -17513,9 +17330,7 @@
         <v>319</v>
       </c>
       <c r="E162" s="2"/>
-      <c r="F162" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F162" s="2"/>
       <c r="G162" s="14"/>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
@@ -17536,9 +17351,7 @@
         <v>320</v>
       </c>
       <c r="E163" s="2"/>
-      <c r="F163" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F163" s="2"/>
       <c r="G163" s="14"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
@@ -17559,9 +17372,7 @@
         <v>322</v>
       </c>
       <c r="E164" s="2"/>
-      <c r="F164" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F164" s="2"/>
       <c r="G164" s="14"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
@@ -17582,9 +17393,7 @@
         <v>1136</v>
       </c>
       <c r="E165" s="2"/>
-      <c r="F165" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F165" s="2"/>
       <c r="G165" s="14"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
@@ -17605,9 +17414,7 @@
         <v>1128</v>
       </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F166" s="2"/>
       <c r="G166" s="14"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
@@ -17628,9 +17435,7 @@
         <v>326</v>
       </c>
       <c r="E167" s="2"/>
-      <c r="F167" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F167" s="2"/>
       <c r="G167" s="14"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
@@ -17651,9 +17456,7 @@
         <v>842</v>
       </c>
       <c r="E168" s="2"/>
-      <c r="F168" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F168" s="2"/>
       <c r="G168" s="14"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
@@ -17674,9 +17477,7 @@
         <v>844</v>
       </c>
       <c r="E169" s="2"/>
-      <c r="F169" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F169" s="2"/>
       <c r="G169" s="14"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
@@ -17697,9 +17498,7 @@
         <v>328</v>
       </c>
       <c r="E170" s="2"/>
-      <c r="F170" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F170" s="2"/>
       <c r="G170" s="14"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
@@ -17720,9 +17519,7 @@
         <v>330</v>
       </c>
       <c r="E171" s="2"/>
-      <c r="F171" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F171" s="2"/>
       <c r="G171" s="14"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
@@ -17743,9 +17540,7 @@
         <v>334</v>
       </c>
       <c r="E172" s="2"/>
-      <c r="F172" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F172" s="2"/>
       <c r="G172" s="14"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -17766,9 +17561,7 @@
         <v>893</v>
       </c>
       <c r="E173" s="2"/>
-      <c r="F173" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F173" s="2"/>
       <c r="G173" s="14"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
@@ -17789,9 +17582,7 @@
         <v>338</v>
       </c>
       <c r="E174" s="2"/>
-      <c r="F174" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F174" s="2"/>
       <c r="G174" s="14"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -17812,9 +17603,7 @@
         <v>342</v>
       </c>
       <c r="E175" s="2"/>
-      <c r="F175" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F175" s="2"/>
       <c r="G175" s="14"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
@@ -17835,9 +17624,7 @@
         <v>344</v>
       </c>
       <c r="E176" s="2"/>
-      <c r="F176" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F176" s="2"/>
       <c r="G176" s="14"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
@@ -17858,9 +17645,7 @@
         <v>1054</v>
       </c>
       <c r="E177" s="2"/>
-      <c r="F177" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F177" s="2"/>
       <c r="G177" s="14"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
@@ -17881,9 +17666,7 @@
         <v>345</v>
       </c>
       <c r="E178" s="2"/>
-      <c r="F178" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F178" s="2"/>
       <c r="G178" s="14"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
@@ -17904,9 +17687,7 @@
         <v>347</v>
       </c>
       <c r="E179" s="2"/>
-      <c r="F179" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F179" s="2"/>
       <c r="G179" s="14"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -17927,9 +17708,7 @@
         <v>1052</v>
       </c>
       <c r="E180" s="2"/>
-      <c r="F180" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F180" s="2"/>
       <c r="G180" s="14"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
@@ -17950,9 +17729,7 @@
         <v>350</v>
       </c>
       <c r="E181" s="2"/>
-      <c r="F181" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F181" s="2"/>
       <c r="G181" s="14"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
@@ -17973,9 +17750,7 @@
         <v>933</v>
       </c>
       <c r="E182" s="2"/>
-      <c r="F182" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F182" s="2"/>
       <c r="G182" s="14"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
@@ -17996,9 +17771,7 @@
         <v>352</v>
       </c>
       <c r="E183" s="2"/>
-      <c r="F183" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F183" s="2"/>
       <c r="G183" s="14"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
@@ -18020,9 +17793,7 @@
         <v>356</v>
       </c>
       <c r="E184" s="2"/>
-      <c r="F184" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F184" s="2"/>
       <c r="G184" s="14"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
@@ -18044,9 +17815,7 @@
         <v>360</v>
       </c>
       <c r="E185" s="2"/>
-      <c r="F185" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F185" s="2"/>
       <c r="G185" s="14"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
@@ -18067,9 +17836,7 @@
         <v>364</v>
       </c>
       <c r="E186" s="2"/>
-      <c r="F186" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F186" s="2"/>
       <c r="G186" s="14"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
@@ -18091,9 +17858,7 @@
         <v>1196</v>
       </c>
       <c r="E187" s="2"/>
-      <c r="F187" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F187" s="2"/>
       <c r="G187" s="14"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
@@ -18115,9 +17880,7 @@
         <v>366</v>
       </c>
       <c r="E188" s="2"/>
-      <c r="F188" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F188" s="2"/>
       <c r="G188" s="14"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
@@ -18139,9 +17902,7 @@
         <v>369</v>
       </c>
       <c r="E189" s="2"/>
-      <c r="F189" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F189" s="2"/>
       <c r="G189" s="14"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
@@ -18162,9 +17923,7 @@
         <v>812</v>
       </c>
       <c r="E190" s="2"/>
-      <c r="F190" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F190" s="2"/>
       <c r="G190" s="14"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
@@ -18185,9 +17944,7 @@
         <v>809</v>
       </c>
       <c r="E191" s="2"/>
-      <c r="F191" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F191" s="2"/>
       <c r="G191" s="14"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
@@ -18208,9 +17965,7 @@
         <v>376</v>
       </c>
       <c r="E192" s="2"/>
-      <c r="F192" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F192" s="2"/>
       <c r="G192" s="14"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
@@ -18231,9 +17986,7 @@
         <v>380</v>
       </c>
       <c r="E193" s="2"/>
-      <c r="F193" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F193" s="2"/>
       <c r="G193" s="14"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
@@ -18254,9 +18007,7 @@
         <v>381</v>
       </c>
       <c r="E194" s="2"/>
-      <c r="F194" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F194" s="2"/>
       <c r="G194" s="14"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
@@ -18277,9 +18028,7 @@
         <v>382</v>
       </c>
       <c r="E195" s="2"/>
-      <c r="F195" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F195" s="2"/>
       <c r="G195" s="14"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
@@ -18300,9 +18049,7 @@
         <v>1199</v>
       </c>
       <c r="E196" s="2"/>
-      <c r="F196" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F196" s="2"/>
       <c r="G196" s="14"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
@@ -18323,9 +18070,7 @@
         <v>384</v>
       </c>
       <c r="E197" s="2"/>
-      <c r="F197" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F197" s="2"/>
       <c r="G197" s="14"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
@@ -18346,9 +18091,7 @@
         <v>387</v>
       </c>
       <c r="E198" s="2"/>
-      <c r="F198" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F198" s="2"/>
       <c r="G198" s="14"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -18369,9 +18112,7 @@
         <v>391</v>
       </c>
       <c r="E199" s="2"/>
-      <c r="F199" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F199" s="2"/>
       <c r="G199" s="14"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -18392,9 +18133,7 @@
         <v>394</v>
       </c>
       <c r="E200" s="2"/>
-      <c r="F200" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F200" s="2"/>
       <c r="G200" s="14"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
@@ -18415,9 +18154,7 @@
         <v>398</v>
       </c>
       <c r="E201" s="2"/>
-      <c r="F201" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F201" s="2"/>
       <c r="G201" s="14"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
@@ -18438,9 +18175,7 @@
         <v>400</v>
       </c>
       <c r="E202" s="2"/>
-      <c r="F202" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F202" s="2"/>
       <c r="G202" s="14"/>
       <c r="J202" s="3"/>
       <c r="K202" s="11"/>
@@ -18459,9 +18194,7 @@
         <v>409</v>
       </c>
       <c r="E203" s="2"/>
-      <c r="F203" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F203" s="2"/>
       <c r="G203" s="14"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
@@ -18482,9 +18215,7 @@
         <v>919</v>
       </c>
       <c r="E204" s="2"/>
-      <c r="F204" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F204" s="2"/>
       <c r="G204" s="14"/>
       <c r="H204" s="58"/>
       <c r="I204" s="63"/>
@@ -18505,9 +18236,7 @@
         <v>411</v>
       </c>
       <c r="E205" s="2"/>
-      <c r="F205" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F205" s="2"/>
       <c r="G205" s="14"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
@@ -18528,9 +18257,7 @@
         <v>413</v>
       </c>
       <c r="E206" s="2"/>
-      <c r="F206" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F206" s="2"/>
       <c r="G206" s="14"/>
       <c r="J206" s="64"/>
       <c r="K206" s="11"/>
@@ -18549,9 +18276,7 @@
         <v>415</v>
       </c>
       <c r="E207" s="2"/>
-      <c r="F207" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F207" s="2"/>
       <c r="G207" s="14"/>
       <c r="J207" s="3"/>
       <c r="K207" s="11"/>
@@ -18570,9 +18295,7 @@
         <v>416</v>
       </c>
       <c r="E208" s="2"/>
-      <c r="F208" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F208" s="2"/>
       <c r="G208" s="14"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
@@ -18592,9 +18315,7 @@
         <v>419</v>
       </c>
       <c r="E209" s="2"/>
-      <c r="F209" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F209" s="2"/>
       <c r="G209" s="14"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
@@ -18615,9 +18336,7 @@
         <v>421</v>
       </c>
       <c r="E210" s="2"/>
-      <c r="F210" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F210" s="2"/>
       <c r="G210" s="14"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
@@ -18638,9 +18357,7 @@
         <v>1167</v>
       </c>
       <c r="E211" s="2"/>
-      <c r="F211" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F211" s="2"/>
       <c r="G211" s="14"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
@@ -18661,9 +18378,7 @@
         <v>429</v>
       </c>
       <c r="E212" s="2"/>
-      <c r="F212" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F212" s="2"/>
       <c r="G212" s="14"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -18684,9 +18399,7 @@
         <v>430</v>
       </c>
       <c r="E213" s="2"/>
-      <c r="F213" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F213" s="2"/>
       <c r="G213" s="14"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
@@ -18707,9 +18420,7 @@
         <v>434</v>
       </c>
       <c r="E214" s="2"/>
-      <c r="F214" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F214" s="2"/>
       <c r="G214" s="14"/>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
@@ -18730,9 +18441,7 @@
         <v>436</v>
       </c>
       <c r="E215" s="2"/>
-      <c r="F215" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F215" s="2"/>
       <c r="G215" s="14"/>
       <c r="H215" s="58"/>
       <c r="I215" s="2"/>
@@ -18753,9 +18462,7 @@
         <v>440</v>
       </c>
       <c r="E216" s="2"/>
-      <c r="F216" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F216" s="2"/>
       <c r="G216" s="14"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
@@ -18776,9 +18483,7 @@
         <v>443</v>
       </c>
       <c r="E217" s="2"/>
-      <c r="F217" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F217" s="2"/>
       <c r="G217" s="14"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
@@ -18799,9 +18504,7 @@
         <v>447</v>
       </c>
       <c r="E218" s="2"/>
-      <c r="F218" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F218" s="2"/>
       <c r="G218" s="14"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
@@ -18822,9 +18525,7 @@
         <v>451</v>
       </c>
       <c r="E219" s="2"/>
-      <c r="F219" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F219" s="2"/>
       <c r="G219" s="14"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -18845,9 +18546,7 @@
         <v>455</v>
       </c>
       <c r="E220" s="2"/>
-      <c r="F220" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F220" s="2"/>
       <c r="G220" s="14"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
@@ -18868,9 +18567,7 @@
         <v>764</v>
       </c>
       <c r="E221" s="2"/>
-      <c r="F221" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F221" s="2"/>
       <c r="G221" s="14"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -18891,9 +18588,7 @@
         <v>460</v>
       </c>
       <c r="E222" s="2"/>
-      <c r="F222" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F222" s="2"/>
       <c r="G222" s="14"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
@@ -18914,9 +18609,7 @@
         <v>464</v>
       </c>
       <c r="E223" s="2"/>
-      <c r="F223" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F223" s="2"/>
       <c r="G223" s="14"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
@@ -18937,9 +18630,7 @@
         <v>467</v>
       </c>
       <c r="E224" s="2"/>
-      <c r="F224" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F224" s="2"/>
       <c r="G224" s="14"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
@@ -18960,9 +18651,7 @@
         <v>703</v>
       </c>
       <c r="E225" s="2"/>
-      <c r="F225" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F225" s="2"/>
       <c r="G225" s="14"/>
       <c r="H225" s="58"/>
       <c r="I225" s="2"/>
@@ -18983,9 +18672,7 @@
         <v>1296</v>
       </c>
       <c r="E226" s="2"/>
-      <c r="F226" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F226" s="2"/>
       <c r="G226" s="14"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
@@ -19006,9 +18693,7 @@
         <v>1230</v>
       </c>
       <c r="E227" s="2"/>
-      <c r="F227" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F227" s="2"/>
       <c r="G227" s="14"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
@@ -19029,9 +18714,7 @@
         <v>1132</v>
       </c>
       <c r="E228" s="2"/>
-      <c r="F228" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F228" s="2"/>
       <c r="G228" s="14"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
@@ -19052,9 +18735,7 @@
         <v>859</v>
       </c>
       <c r="E229" s="2"/>
-      <c r="F229" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F229" s="2"/>
       <c r="G229" s="14"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
@@ -19075,9 +18756,7 @@
         <v>471</v>
       </c>
       <c r="E230" s="2"/>
-      <c r="F230" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F230" s="2"/>
       <c r="G230" s="14"/>
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
@@ -19098,9 +18777,7 @@
         <v>470</v>
       </c>
       <c r="E231" s="2"/>
-      <c r="F231" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F231" s="2"/>
       <c r="G231" s="14"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
@@ -19121,9 +18798,7 @@
         <v>686</v>
       </c>
       <c r="E232" s="2"/>
-      <c r="F232" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F232" s="2"/>
       <c r="G232" s="14"/>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
@@ -19144,9 +18819,7 @@
         <v>895</v>
       </c>
       <c r="E233" s="2"/>
-      <c r="F233" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F233" s="2"/>
       <c r="G233" s="14"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
@@ -19167,9 +18840,7 @@
         <v>896</v>
       </c>
       <c r="E234" s="2"/>
-      <c r="F234" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F234" s="2"/>
       <c r="G234" s="14"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
@@ -19191,9 +18862,7 @@
         <v>473</v>
       </c>
       <c r="E235" s="2"/>
-      <c r="F235" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F235" s="2"/>
       <c r="G235" s="14"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
@@ -19214,9 +18883,7 @@
         <v>1142</v>
       </c>
       <c r="E236" s="2"/>
-      <c r="F236" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F236" s="2"/>
       <c r="G236" s="14"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
@@ -19237,9 +18904,7 @@
         <v>1158</v>
       </c>
       <c r="E237" s="2"/>
-      <c r="F237" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F237" s="2"/>
       <c r="G237" s="14"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
@@ -19260,9 +18925,7 @@
         <v>476</v>
       </c>
       <c r="E238" s="2"/>
-      <c r="F238" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F238" s="2"/>
       <c r="G238" s="14"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
@@ -19283,9 +18946,7 @@
         <v>1204</v>
       </c>
       <c r="E239" s="2"/>
-      <c r="F239" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F239" s="2"/>
       <c r="G239" s="14"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
@@ -19306,9 +18967,7 @@
         <v>1293</v>
       </c>
       <c r="E240" s="2"/>
-      <c r="F240" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F240" s="2"/>
       <c r="G240" s="14"/>
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
@@ -19329,9 +18988,7 @@
         <v>479</v>
       </c>
       <c r="E241" s="2"/>
-      <c r="F241" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F241" s="2"/>
       <c r="G241" s="14"/>
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
@@ -19352,9 +19009,7 @@
         <v>721</v>
       </c>
       <c r="E242" s="2"/>
-      <c r="F242" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F242" s="2"/>
       <c r="G242" s="14"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
@@ -19375,9 +19030,7 @@
         <v>483</v>
       </c>
       <c r="E243" s="2"/>
-      <c r="F243" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F243" s="2"/>
       <c r="G243" s="14"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
@@ -19398,9 +19051,7 @@
         <v>486</v>
       </c>
       <c r="E244" s="2"/>
-      <c r="F244" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F244" s="2"/>
       <c r="G244" s="14"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
@@ -19421,9 +19072,7 @@
         <v>488</v>
       </c>
       <c r="E245" s="2"/>
-      <c r="F245" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F245" s="2"/>
       <c r="G245" s="14"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
@@ -19444,9 +19093,7 @@
         <v>489</v>
       </c>
       <c r="E246" s="2"/>
-      <c r="F246" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F246" s="2"/>
       <c r="G246" s="14"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
@@ -19467,9 +19114,7 @@
         <v>493</v>
       </c>
       <c r="E247" s="2"/>
-      <c r="F247" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F247" s="2"/>
       <c r="G247" s="14"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
@@ -19490,9 +19135,7 @@
         <v>824</v>
       </c>
       <c r="E248" s="2"/>
-      <c r="F248" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F248" s="2"/>
       <c r="G248" s="14"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
@@ -19513,9 +19156,7 @@
         <v>495</v>
       </c>
       <c r="E249" s="2"/>
-      <c r="F249" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F249" s="2"/>
       <c r="G249" s="14"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
@@ -19536,9 +19177,7 @@
         <v>496</v>
       </c>
       <c r="E250" s="2"/>
-      <c r="F250" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F250" s="2"/>
       <c r="G250" s="14"/>
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
@@ -19559,9 +19198,7 @@
         <v>1215</v>
       </c>
       <c r="E251" s="2"/>
-      <c r="F251" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F251" s="2"/>
       <c r="G251" s="14"/>
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
@@ -19582,9 +19219,7 @@
         <v>720</v>
       </c>
       <c r="E252" s="2"/>
-      <c r="F252" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F252" s="2"/>
       <c r="G252" s="14"/>
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
@@ -19605,9 +19240,7 @@
         <v>1310</v>
       </c>
       <c r="E253" s="2"/>
-      <c r="F253" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F253" s="2"/>
       <c r="G253" s="14"/>
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
@@ -19628,9 +19261,7 @@
         <v>1169</v>
       </c>
       <c r="E254" s="2"/>
-      <c r="F254" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F254" s="2"/>
       <c r="G254" s="14"/>
       <c r="J254" s="3"/>
       <c r="K254" s="11"/>
@@ -19649,9 +19280,7 @@
         <v>516</v>
       </c>
       <c r="E255" s="2"/>
-      <c r="F255" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F255" s="2"/>
       <c r="G255" s="14"/>
       <c r="J255" s="3"/>
       <c r="K255" s="11"/>
@@ -19670,9 +19299,7 @@
         <v>519</v>
       </c>
       <c r="E256" s="2"/>
-      <c r="F256" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F256" s="2"/>
       <c r="G256" s="14"/>
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
@@ -19693,9 +19320,7 @@
         <v>777</v>
       </c>
       <c r="E257" s="2"/>
-      <c r="F257" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F257" s="2"/>
       <c r="G257" s="14"/>
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
@@ -19716,9 +19341,7 @@
         <v>826</v>
       </c>
       <c r="E258" s="2"/>
-      <c r="F258" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F258" s="2"/>
       <c r="G258" s="14"/>
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
@@ -19739,9 +19362,7 @@
         <v>522</v>
       </c>
       <c r="E259" s="2"/>
-      <c r="F259" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F259" s="2"/>
       <c r="G259" s="14"/>
       <c r="J259" s="3"/>
       <c r="K259" s="11"/>
@@ -19760,9 +19381,7 @@
         <v>872</v>
       </c>
       <c r="E260" s="2"/>
-      <c r="F260" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F260" s="2"/>
       <c r="G260" s="14"/>
       <c r="J260" s="3"/>
       <c r="K260" s="11"/>
@@ -19781,9 +19400,7 @@
         <v>525</v>
       </c>
       <c r="E261" s="2"/>
-      <c r="F261" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F261" s="2"/>
       <c r="G261" s="14"/>
       <c r="H261" s="2"/>
       <c r="I261" s="2"/>
@@ -19804,9 +19421,7 @@
         <v>530</v>
       </c>
       <c r="E262" s="2"/>
-      <c r="F262" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F262" s="2"/>
       <c r="G262" s="14"/>
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
@@ -19827,9 +19442,7 @@
         <v>533</v>
       </c>
       <c r="E263" s="2"/>
-      <c r="F263" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F263" s="2"/>
       <c r="G263" s="14"/>
       <c r="H263" s="58"/>
       <c r="I263" s="2"/>
@@ -19850,9 +19463,7 @@
         <v>534</v>
       </c>
       <c r="E264" s="2"/>
-      <c r="F264" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F264" s="2"/>
       <c r="G264" s="14"/>
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
@@ -19873,9 +19484,7 @@
         <v>810</v>
       </c>
       <c r="E265" s="2"/>
-      <c r="F265" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F265" s="2"/>
       <c r="G265" s="14"/>
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
@@ -19896,9 +19505,7 @@
         <v>536</v>
       </c>
       <c r="E266" s="2"/>
-      <c r="F266" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F266" s="2"/>
       <c r="G266" s="14"/>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
@@ -19919,9 +19526,7 @@
         <v>956</v>
       </c>
       <c r="E267" s="2"/>
-      <c r="F267" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F267" s="2"/>
       <c r="G267" s="14"/>
       <c r="H267" s="6"/>
       <c r="I267" s="6"/>
@@ -19942,9 +19547,7 @@
         <v>1093</v>
       </c>
       <c r="E268" s="2"/>
-      <c r="F268" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F268" s="2"/>
       <c r="G268" s="14"/>
       <c r="H268" s="6"/>
       <c r="I268" s="6"/>
@@ -19965,9 +19568,7 @@
         <v>539</v>
       </c>
       <c r="E269" s="2"/>
-      <c r="F269" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F269" s="2"/>
       <c r="G269" s="14"/>
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
@@ -19988,9 +19589,7 @@
         <v>734</v>
       </c>
       <c r="E270" s="2"/>
-      <c r="F270" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F270" s="2"/>
       <c r="G270" s="14"/>
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
@@ -20011,9 +19610,7 @@
         <v>540</v>
       </c>
       <c r="E271" s="2"/>
-      <c r="F271" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F271" s="2"/>
       <c r="G271" s="14"/>
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
@@ -20034,9 +19631,7 @@
         <v>543</v>
       </c>
       <c r="E272" s="2"/>
-      <c r="F272" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F272" s="2"/>
       <c r="G272" s="14"/>
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
@@ -20057,9 +19652,7 @@
         <v>815</v>
       </c>
       <c r="E273" s="2"/>
-      <c r="F273" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F273" s="2"/>
       <c r="G273" s="14"/>
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
@@ -20080,9 +19673,7 @@
         <v>545</v>
       </c>
       <c r="E274" s="2"/>
-      <c r="F274" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F274" s="2"/>
       <c r="G274" s="14"/>
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
@@ -20103,9 +19694,7 @@
         <v>547</v>
       </c>
       <c r="E275" s="2"/>
-      <c r="F275" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F275" s="2"/>
       <c r="G275" s="14"/>
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
@@ -20126,9 +19715,7 @@
         <v>549</v>
       </c>
       <c r="E276" s="2"/>
-      <c r="F276" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F276" s="2"/>
       <c r="G276" s="14"/>
       <c r="H276" s="2"/>
       <c r="I276" s="2"/>
@@ -20149,9 +19736,7 @@
         <v>1248</v>
       </c>
       <c r="E277" s="2"/>
-      <c r="F277" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F277" s="2"/>
       <c r="G277" s="14"/>
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
@@ -20172,9 +19757,7 @@
         <v>1249</v>
       </c>
       <c r="E278" s="2"/>
-      <c r="F278" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F278" s="2"/>
       <c r="G278" s="14"/>
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
@@ -20195,9 +19778,7 @@
         <v>875</v>
       </c>
       <c r="E279" s="2"/>
-      <c r="F279" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F279" s="2"/>
       <c r="G279" s="14"/>
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
@@ -20218,9 +19799,7 @@
         <v>554</v>
       </c>
       <c r="E280" s="2"/>
-      <c r="F280" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F280" s="2"/>
       <c r="G280" s="14"/>
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
@@ -20241,9 +19820,7 @@
         <v>1307</v>
       </c>
       <c r="E281" s="2"/>
-      <c r="F281" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F281" s="2"/>
       <c r="G281" s="14"/>
       <c r="H281" s="6"/>
       <c r="I281" s="6"/>
@@ -20264,9 +19841,7 @@
         <v>1162</v>
       </c>
       <c r="E282" s="2"/>
-      <c r="F282" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F282" s="2"/>
       <c r="G282" s="14"/>
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
@@ -20287,9 +19862,7 @@
         <v>799</v>
       </c>
       <c r="E283" s="2"/>
-      <c r="F283" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F283" s="2"/>
       <c r="G283" s="14"/>
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
@@ -20310,9 +19883,7 @@
         <v>1027</v>
       </c>
       <c r="E284" s="2"/>
-      <c r="F284" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F284" s="2"/>
       <c r="G284" s="14"/>
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
@@ -20333,9 +19904,7 @@
         <v>1115</v>
       </c>
       <c r="E285" s="2"/>
-      <c r="F285" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F285" s="2"/>
       <c r="G285" s="14"/>
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
@@ -20356,9 +19925,7 @@
         <v>562</v>
       </c>
       <c r="E286" s="2"/>
-      <c r="F286" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F286" s="2"/>
       <c r="G286" s="14"/>
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
@@ -20379,9 +19946,7 @@
         <v>832</v>
       </c>
       <c r="E287" s="2"/>
-      <c r="F287" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F287" s="2"/>
       <c r="G287" s="14"/>
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
@@ -20402,9 +19967,7 @@
         <v>748</v>
       </c>
       <c r="E288" s="2"/>
-      <c r="F288" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F288" s="2"/>
       <c r="G288" s="14"/>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
@@ -20425,9 +19988,7 @@
         <v>1206</v>
       </c>
       <c r="E289" s="2"/>
-      <c r="F289" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F289" s="2"/>
       <c r="G289" s="14"/>
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
@@ -20448,9 +20009,7 @@
         <v>568</v>
       </c>
       <c r="E290" s="2"/>
-      <c r="F290" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F290" s="2"/>
       <c r="G290" s="14"/>
       <c r="H290" s="59"/>
       <c r="I290" s="59"/>
@@ -20471,9 +20030,7 @@
         <v>571</v>
       </c>
       <c r="E291" s="2"/>
-      <c r="F291" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F291" s="2"/>
       <c r="G291" s="14"/>
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
@@ -20494,9 +20051,7 @@
         <v>1220</v>
       </c>
       <c r="E292" s="2"/>
-      <c r="F292" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F292" s="2"/>
       <c r="G292" s="14"/>
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
@@ -20517,9 +20072,7 @@
         <v>576</v>
       </c>
       <c r="E293" s="2"/>
-      <c r="F293" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F293" s="2"/>
       <c r="G293" s="14"/>
       <c r="H293" s="6"/>
       <c r="I293" s="6"/>
@@ -20540,9 +20093,7 @@
         <v>1113</v>
       </c>
       <c r="E294" s="2"/>
-      <c r="F294" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F294" s="2"/>
       <c r="G294" s="14"/>
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
@@ -20563,9 +20114,7 @@
         <v>579</v>
       </c>
       <c r="E295" s="2"/>
-      <c r="F295" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F295" s="2"/>
       <c r="G295" s="14"/>
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
@@ -20586,9 +20135,7 @@
         <v>580</v>
       </c>
       <c r="E296" s="2"/>
-      <c r="F296" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F296" s="2"/>
       <c r="G296" s="14"/>
       <c r="H296" s="6"/>
       <c r="I296" s="6"/>
@@ -20609,9 +20156,7 @@
         <v>828</v>
       </c>
       <c r="E297" s="2"/>
-      <c r="F297" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F297" s="2"/>
       <c r="G297" s="14"/>
       <c r="H297" s="58"/>
       <c r="I297" s="2"/>
@@ -20632,9 +20177,7 @@
         <v>583</v>
       </c>
       <c r="E298" s="2"/>
-      <c r="F298" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F298" s="2"/>
       <c r="G298" s="14"/>
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
@@ -20655,9 +20198,7 @@
         <v>830</v>
       </c>
       <c r="E299" s="2"/>
-      <c r="F299" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F299" s="2"/>
       <c r="G299" s="14"/>
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
@@ -20678,9 +20219,7 @@
         <v>1286</v>
       </c>
       <c r="E300" s="2"/>
-      <c r="F300" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F300" s="2"/>
       <c r="G300" s="14"/>
       <c r="H300" s="58"/>
       <c r="I300" s="2"/>
@@ -20701,9 +20240,7 @@
         <v>959</v>
       </c>
       <c r="E301" s="2"/>
-      <c r="F301" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F301" s="2"/>
       <c r="G301" s="14"/>
       <c r="H301" s="58"/>
       <c r="I301" s="2"/>
@@ -20724,9 +20261,7 @@
         <v>591</v>
       </c>
       <c r="E302" s="2"/>
-      <c r="F302" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F302" s="2"/>
       <c r="G302" s="14"/>
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
@@ -20747,9 +20282,7 @@
         <v>592</v>
       </c>
       <c r="E303" s="2"/>
-      <c r="F303" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F303" s="2"/>
       <c r="G303" s="14"/>
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
@@ -20770,9 +20303,7 @@
         <v>514</v>
       </c>
       <c r="E304" s="2"/>
-      <c r="F304" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F304" s="2"/>
       <c r="G304" s="14"/>
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
@@ -20793,9 +20324,7 @@
         <v>612</v>
       </c>
       <c r="E305" s="2"/>
-      <c r="F305" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F305" s="2"/>
       <c r="G305" s="14"/>
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
@@ -20816,9 +20345,7 @@
         <v>613</v>
       </c>
       <c r="E306" s="2"/>
-      <c r="F306" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F306" s="2"/>
       <c r="G306" s="14"/>
       <c r="H306" s="6"/>
       <c r="I306" s="6"/>
@@ -20839,9 +20366,7 @@
         <v>614</v>
       </c>
       <c r="E307" s="2"/>
-      <c r="F307" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F307" s="2"/>
       <c r="G307" s="14"/>
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
@@ -20862,9 +20387,7 @@
         <v>617</v>
       </c>
       <c r="E308" s="2"/>
-      <c r="F308" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F308" s="2"/>
       <c r="G308" s="14"/>
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
@@ -20885,9 +20408,7 @@
         <v>619</v>
       </c>
       <c r="E309" s="2"/>
-      <c r="F309" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F309" s="2"/>
       <c r="G309" s="14"/>
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
@@ -20908,9 +20429,7 @@
         <v>1272</v>
       </c>
       <c r="E310" s="2"/>
-      <c r="F310" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F310" s="2"/>
       <c r="G310" s="14"/>
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
@@ -20931,9 +20450,7 @@
         <v>621</v>
       </c>
       <c r="E311" s="2"/>
-      <c r="F311" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F311" s="2"/>
       <c r="G311" s="14"/>
       <c r="H311" s="2"/>
       <c r="I311" s="2"/>
@@ -20954,9 +20471,7 @@
         <v>864</v>
       </c>
       <c r="E312" s="2"/>
-      <c r="F312" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F312" s="2"/>
       <c r="G312" s="14"/>
       <c r="J312" s="3"/>
       <c r="K312" s="11"/>
@@ -20975,9 +20490,7 @@
         <v>701</v>
       </c>
       <c r="E313" s="2"/>
-      <c r="F313" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F313" s="2"/>
       <c r="G313" s="14"/>
       <c r="J313" s="3"/>
       <c r="K313" s="11"/>
@@ -20996,9 +20509,7 @@
         <v>1253</v>
       </c>
       <c r="E314" s="2"/>
-      <c r="F314" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F314" s="2"/>
       <c r="G314" s="14"/>
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
@@ -21019,9 +20530,7 @@
         <v>627</v>
       </c>
       <c r="E315" s="2"/>
-      <c r="F315" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F315" s="2"/>
       <c r="G315" s="14"/>
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
@@ -21042,9 +20551,7 @@
         <v>775</v>
       </c>
       <c r="E316" s="2"/>
-      <c r="F316" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F316" s="2"/>
       <c r="G316" s="14"/>
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
@@ -21065,9 +20572,7 @@
         <v>629</v>
       </c>
       <c r="E317" s="2"/>
-      <c r="F317" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F317" s="2"/>
       <c r="G317" s="14"/>
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
@@ -21088,9 +20593,7 @@
         <v>630</v>
       </c>
       <c r="E318" s="2"/>
-      <c r="F318" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F318" s="2"/>
       <c r="G318" s="14"/>
       <c r="H318" s="2"/>
       <c r="I318" s="2"/>
@@ -21111,9 +20614,7 @@
         <v>632</v>
       </c>
       <c r="E319" s="2"/>
-      <c r="F319" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F319" s="2"/>
       <c r="G319" s="14"/>
       <c r="H319" s="2"/>
       <c r="I319" s="2"/>
@@ -21134,9 +20635,7 @@
         <v>636</v>
       </c>
       <c r="E320" s="2"/>
-      <c r="F320" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F320" s="2"/>
       <c r="G320" s="14"/>
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
@@ -21157,9 +20656,7 @@
         <v>1174</v>
       </c>
       <c r="E321" s="2"/>
-      <c r="F321" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F321" s="2"/>
       <c r="G321" s="14"/>
       <c r="H321" s="2"/>
       <c r="I321" s="2"/>
@@ -21180,9 +20677,7 @@
         <v>1173</v>
       </c>
       <c r="E322" s="2"/>
-      <c r="F322" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F322" s="2"/>
       <c r="G322" s="14"/>
       <c r="H322" s="2"/>
       <c r="I322" s="2"/>
@@ -21203,9 +20698,7 @@
         <v>794</v>
       </c>
       <c r="E323" s="2"/>
-      <c r="F323" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F323" s="2"/>
       <c r="G323" s="14"/>
       <c r="J323" s="3"/>
       <c r="K323" s="11"/>
@@ -21224,9 +20717,7 @@
         <v>640</v>
       </c>
       <c r="E324" s="2"/>
-      <c r="F324" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F324" s="2"/>
       <c r="G324" s="14"/>
       <c r="J324" s="3"/>
       <c r="K324" s="11"/>
@@ -21245,9 +20736,7 @@
         <v>1148</v>
       </c>
       <c r="E325" s="2"/>
-      <c r="F325" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F325" s="2"/>
       <c r="G325" s="14"/>
       <c r="K325" s="11"/>
     </row>
@@ -21265,9 +20754,7 @@
         <v>644</v>
       </c>
       <c r="E326" s="2"/>
-      <c r="F326" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F326" s="2"/>
       <c r="G326" s="14"/>
       <c r="H326" s="55"/>
       <c r="I326" s="55"/>
@@ -21287,9 +20774,7 @@
         <v>647</v>
       </c>
       <c r="E327" s="2"/>
-      <c r="F327" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F327" s="2"/>
       <c r="G327" s="14"/>
       <c r="K327" s="11"/>
     </row>
@@ -21307,9 +20792,7 @@
         <v>961</v>
       </c>
       <c r="E328" s="2"/>
-      <c r="F328" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F328" s="2"/>
       <c r="G328" s="14"/>
       <c r="H328" s="21"/>
       <c r="I328" s="21"/>
@@ -21330,9 +20813,7 @@
         <v>904</v>
       </c>
       <c r="E329" s="2"/>
-      <c r="F329" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F329" s="2"/>
       <c r="G329" s="14"/>
       <c r="J329" s="62"/>
       <c r="K329" s="11"/>
@@ -21351,9 +20832,7 @@
         <v>649</v>
       </c>
       <c r="E330" s="2"/>
-      <c r="F330" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F330" s="2"/>
       <c r="G330" s="14"/>
       <c r="H330" s="2"/>
       <c r="I330" s="2"/>
@@ -21374,9 +20853,7 @@
         <v>651</v>
       </c>
       <c r="E331" s="2"/>
-      <c r="F331" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F331" s="2"/>
       <c r="G331" s="14"/>
       <c r="J331" s="62"/>
       <c r="K331" s="11"/>
@@ -21395,9 +20872,7 @@
         <v>654</v>
       </c>
       <c r="E332" s="2"/>
-      <c r="F332" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F332" s="2"/>
       <c r="G332" s="14"/>
       <c r="J332" s="14"/>
       <c r="K332" s="11"/>
@@ -21416,9 +20891,7 @@
         <v>892</v>
       </c>
       <c r="E333" s="2"/>
-      <c r="F333" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F333" s="2"/>
       <c r="G333" s="14"/>
       <c r="J333" s="4"/>
       <c r="K333" s="11"/>
@@ -21437,9 +20910,7 @@
         <v>834</v>
       </c>
       <c r="E334" s="2"/>
-      <c r="F334" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F334" s="2"/>
       <c r="G334" s="14"/>
       <c r="J334" s="62"/>
       <c r="K334" s="11"/>
@@ -21458,9 +20929,7 @@
         <v>1212</v>
       </c>
       <c r="E335" s="2"/>
-      <c r="F335" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F335" s="2"/>
       <c r="G335" s="14"/>
       <c r="J335" s="62"/>
       <c r="K335" s="11"/>
@@ -21479,9 +20948,7 @@
         <v>662</v>
       </c>
       <c r="E336" s="2"/>
-      <c r="F336" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F336" s="2"/>
       <c r="G336" s="14"/>
       <c r="J336" s="62"/>
       <c r="K336" s="11"/>
@@ -21500,9 +20967,7 @@
         <v>658</v>
       </c>
       <c r="E337" s="2"/>
-      <c r="F337" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F337" s="2"/>
       <c r="G337" s="14"/>
       <c r="J337" s="62"/>
       <c r="K337" s="11"/>
@@ -21521,9 +20986,7 @@
         <v>660</v>
       </c>
       <c r="E338" s="2"/>
-      <c r="F338" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F338" s="2"/>
       <c r="G338" s="14"/>
       <c r="J338" s="62"/>
       <c r="K338" s="11"/>
@@ -21542,9 +21005,7 @@
         <v>661</v>
       </c>
       <c r="E339" s="2"/>
-      <c r="F339" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F339" s="2"/>
       <c r="G339" s="14"/>
       <c r="J339" s="62"/>
       <c r="K339" s="11"/>
@@ -21563,9 +21024,7 @@
         <v>663</v>
       </c>
       <c r="E340" s="2"/>
-      <c r="F340" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F340" s="2"/>
       <c r="G340" s="14"/>
       <c r="H340" s="2"/>
       <c r="I340" s="2"/>
@@ -21586,9 +21045,7 @@
         <v>665</v>
       </c>
       <c r="E341" s="2"/>
-      <c r="F341" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F341" s="2"/>
       <c r="G341" s="14"/>
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
@@ -21609,9 +21066,7 @@
         <v>667</v>
       </c>
       <c r="E342" s="2"/>
-      <c r="F342" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F342" s="2"/>
       <c r="G342" s="14"/>
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
@@ -21632,9 +21087,7 @@
         <v>669</v>
       </c>
       <c r="E343" s="2"/>
-      <c r="F343" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F343" s="2"/>
       <c r="G343" s="14"/>
       <c r="H343" s="2"/>
       <c r="I343" s="2"/>
@@ -21655,9 +21108,7 @@
         <v>673</v>
       </c>
       <c r="E344" s="2"/>
-      <c r="F344" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F344" s="2"/>
       <c r="G344" s="14"/>
       <c r="J344" s="68"/>
       <c r="K344" s="11"/>
@@ -21676,9 +21127,7 @@
         <v>1140</v>
       </c>
       <c r="E345" s="2"/>
-      <c r="F345" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F345" s="2"/>
       <c r="G345" s="14"/>
       <c r="J345" s="3"/>
       <c r="K345" s="11"/>
@@ -21697,9 +21146,7 @@
         <v>676</v>
       </c>
       <c r="E346" s="2"/>
-      <c r="F346" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F346" s="2"/>
       <c r="G346" s="14"/>
       <c r="J346" s="1"/>
       <c r="K346" s="11"/>
@@ -21718,9 +21165,7 @@
         <v>1182</v>
       </c>
       <c r="E347" s="2"/>
-      <c r="F347" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F347" s="2"/>
       <c r="G347" s="14"/>
       <c r="J347" s="1"/>
       <c r="K347" s="11"/>
@@ -21739,9 +21184,7 @@
         <v>1267</v>
       </c>
       <c r="E348" s="2"/>
-      <c r="F348" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F348" s="2"/>
       <c r="G348" s="14"/>
       <c r="K348" s="11"/>
     </row>
@@ -21759,9 +21202,7 @@
         <v>678</v>
       </c>
       <c r="E349" s="2"/>
-      <c r="F349" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F349" s="2"/>
       <c r="G349" s="14"/>
       <c r="J349" s="1"/>
       <c r="K349" s="11"/>
@@ -21780,9 +21221,7 @@
         <v>682</v>
       </c>
       <c r="E350" s="2"/>
-      <c r="F350" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F350" s="2"/>
       <c r="G350" s="14"/>
       <c r="J350" s="1"/>
       <c r="K350" s="11"/>
@@ -21801,9 +21240,7 @@
         <v>683</v>
       </c>
       <c r="E351" s="2"/>
-      <c r="F351" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F351" s="2"/>
       <c r="G351" s="14"/>
       <c r="J351" s="1"/>
       <c r="K351" s="11"/>
@@ -21823,9 +21260,7 @@
         <v>861</v>
       </c>
       <c r="E352" s="2"/>
-      <c r="F352" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F352" s="2"/>
       <c r="G352" s="14"/>
       <c r="J352" s="1"/>
       <c r="K352" s="11"/>
@@ -21844,9 +21279,7 @@
         <v>595</v>
       </c>
       <c r="E353" s="2"/>
-      <c r="F353" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F353" s="2"/>
       <c r="G353" s="14"/>
       <c r="J353" s="1"/>
       <c r="K353" s="11"/>
@@ -21867,9 +21300,7 @@
         <v>597</v>
       </c>
       <c r="E354" s="2"/>
-      <c r="F354" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F354" s="2"/>
       <c r="G354" s="14"/>
       <c r="J354" s="1"/>
       <c r="K354" s="11"/>
@@ -21890,9 +21321,7 @@
         <v>1109</v>
       </c>
       <c r="E355" s="2"/>
-      <c r="F355" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F355" s="2"/>
       <c r="G355" s="14"/>
       <c r="J355" s="1"/>
       <c r="K355" s="11"/>
@@ -21913,9 +21342,7 @@
         <v>1036</v>
       </c>
       <c r="E356" s="2"/>
-      <c r="F356" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F356" s="2"/>
       <c r="G356" s="143">
         <v>17380.5</v>
       </c>
@@ -21938,9 +21365,7 @@
         <v>5</v>
       </c>
       <c r="E357" s="2"/>
-      <c r="F357" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F357" s="2"/>
       <c r="G357" s="144">
         <v>1276.8</v>
       </c>
@@ -21961,9 +21386,7 @@
         <v>884</v>
       </c>
       <c r="E358" s="2"/>
-      <c r="F358" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F358" s="2"/>
       <c r="G358" s="144">
         <v>93016.4</v>
       </c>
@@ -21984,9 +21407,7 @@
         <v>1118</v>
       </c>
       <c r="E359" s="2"/>
-      <c r="F359" s="2" t="s">
-        <v>1647</v>
-      </c>
+      <c r="F359" s="2"/>
       <c r="G359" s="14"/>
       <c r="J359" s="1"/>
       <c r="K359" s="11"/>
@@ -22006,7 +21427,7 @@
       </c>
       <c r="E360" s="2"/>
       <c r="F360" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G360" s="14"/>
       <c r="J360" s="1"/>
@@ -22444,7 +21865,7 @@
         <v>43</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G382" s="14"/>
       <c r="K382" s="11"/>
@@ -22463,7 +21884,7 @@
         <v>47</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G383" s="14"/>
       <c r="K383" s="11"/>
@@ -22482,7 +21903,7 @@
         <v>51</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G384" s="14"/>
       <c r="K384" s="11"/>
@@ -22501,7 +21922,7 @@
         <v>53</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G385" s="14"/>
       <c r="K385" s="11"/>
@@ -22520,7 +21941,7 @@
         <v>55</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G386" s="14"/>
       <c r="K386" s="11"/>
@@ -22539,7 +21960,7 @@
         <v>58</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G387" s="14"/>
       <c r="K387" s="11"/>
@@ -22558,7 +21979,7 @@
         <v>61</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G388" s="14"/>
       <c r="K388" s="11"/>
@@ -22577,7 +21998,7 @@
         <v>65</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G389" s="14"/>
       <c r="K389" s="11"/>
@@ -22653,7 +22074,7 @@
         <v>1033</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G393" s="14"/>
       <c r="K393" s="11"/>
@@ -22672,7 +22093,7 @@
         <v>75</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G394" s="14"/>
       <c r="K394" s="11"/>
@@ -22691,7 +22112,7 @@
         <v>77</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G395" s="14"/>
       <c r="K395" s="11"/>
@@ -22710,7 +22131,7 @@
         <v>80</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>1647</v>
+        <v>3903</v>
       </c>
       <c r="G396" s="14"/>
       <c r="K396" s="11"/>
@@ -23264,6 +22685,7 @@
         <v>1647</v>
       </c>
       <c r="G425" s="14"/>
+      <c r="I425" s="139"/>
       <c r="K425" s="4"/>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
@@ -27664,7 +27086,7 @@
         <v>1327</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="670" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -27681,7 +27103,7 @@
         <v>1328</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="671" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -27698,7 +27120,7 @@
         <v>1329</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="H671" s="139"/>
     </row>
@@ -27716,7 +27138,7 @@
         <v>1330</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="673" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27733,7 +27155,7 @@
         <v>1331</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="674" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27750,7 +27172,7 @@
         <v>1332</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="675" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27767,7 +27189,7 @@
         <v>1333</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="676" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27784,7 +27206,7 @@
         <v>1334</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="677" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27801,7 +27223,7 @@
         <v>1335</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="678" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27818,7 +27240,7 @@
         <v>1336</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="679" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27835,7 +27257,7 @@
         <v>1337</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="680" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27852,7 +27274,7 @@
         <v>1338</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="681" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27869,7 +27291,7 @@
         <v>1339</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="682" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27886,7 +27308,7 @@
         <v>1340</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="683" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27903,7 +27325,7 @@
         <v>1341</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="684" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27920,7 +27342,7 @@
         <v>1342</v>
       </c>
       <c r="F684" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="685" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27937,7 +27359,7 @@
         <v>1343</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="686" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27954,7 +27376,7 @@
         <v>1344</v>
       </c>
       <c r="F686" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="687" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27971,7 +27393,7 @@
         <v>1345</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="688" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -27988,7 +27410,7 @@
         <v>1346</v>
       </c>
       <c r="F688" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="689" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28005,7 +27427,7 @@
         <v>1347</v>
       </c>
       <c r="F689" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="690" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28022,7 +27444,7 @@
         <v>1348</v>
       </c>
       <c r="F690" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="691" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28039,7 +27461,7 @@
         <v>1349</v>
       </c>
       <c r="F691" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="692" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28056,7 +27478,7 @@
         <v>1350</v>
       </c>
       <c r="F692" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="693" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28073,7 +27495,7 @@
         <v>1351</v>
       </c>
       <c r="F693" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="694" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28090,7 +27512,7 @@
         <v>1352</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="695" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28107,7 +27529,7 @@
         <v>1353</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="696" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28124,7 +27546,7 @@
         <v>1354</v>
       </c>
       <c r="F696" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="697" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28141,7 +27563,7 @@
         <v>1355</v>
       </c>
       <c r="F697" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="698" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28158,7 +27580,7 @@
         <v>1356</v>
       </c>
       <c r="F698" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="699" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28175,7 +27597,7 @@
         <v>1357</v>
       </c>
       <c r="F699" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="700" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28192,7 +27614,7 @@
         <v>1358</v>
       </c>
       <c r="F700" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="701" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28209,7 +27631,7 @@
         <v>1359</v>
       </c>
       <c r="F701" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="702" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28226,7 +27648,7 @@
         <v>1360</v>
       </c>
       <c r="F702" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="703" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28243,7 +27665,7 @@
         <v>1361</v>
       </c>
       <c r="F703" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="704" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28260,7 +27682,7 @@
         <v>1362</v>
       </c>
       <c r="F704" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="705" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28277,7 +27699,7 @@
         <v>1363</v>
       </c>
       <c r="F705" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="706" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28294,7 +27716,7 @@
         <v>1364</v>
       </c>
       <c r="F706" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="707" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28311,7 +27733,7 @@
         <v>1365</v>
       </c>
       <c r="F707" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="708" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28328,7 +27750,7 @@
         <v>1366</v>
       </c>
       <c r="F708" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="709" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28345,7 +27767,7 @@
         <v>1367</v>
       </c>
       <c r="F709" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="710" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28362,7 +27784,7 @@
         <v>1368</v>
       </c>
       <c r="F710" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="711" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28376,7 +27798,7 @@
         <v>1411</v>
       </c>
       <c r="F711" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="712" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28390,7 +27812,7 @@
         <v>1412</v>
       </c>
       <c r="F712" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="713" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -28404,7 +27826,7 @@
         <v>1413</v>
       </c>
       <c r="F713" s="1" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="714" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -29177,7 +28599,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="769" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
         <v>770</v>
       </c>
@@ -29191,7 +28613,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="770" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
         <v>771</v>
       </c>
@@ -29205,7 +28627,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="771" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
         <v>772</v>
       </c>
@@ -29219,7 +28641,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
         <v>773</v>
       </c>
@@ -29233,7 +28655,7 @@
         <v>3887</v>
       </c>
     </row>
-    <row r="773" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
         <v>774</v>
       </c>
@@ -29247,7 +28669,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="774" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
         <v>775</v>
       </c>
@@ -29260,8 +28682,11 @@
       <c r="D774" s="102" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="775" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F774" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
         <v>776</v>
       </c>
@@ -29274,8 +28699,11 @@
       <c r="D775" s="102" t="s">
         <v>1541</v>
       </c>
-    </row>
-    <row r="776" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F775" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
         <v>777</v>
       </c>
@@ -29288,8 +28716,11 @@
       <c r="D776" s="102" t="s">
         <v>1542</v>
       </c>
-    </row>
-    <row r="777" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F776" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
         <v>778</v>
       </c>
@@ -29302,8 +28733,11 @@
       <c r="D777" s="102" t="s">
         <v>1543</v>
       </c>
-    </row>
-    <row r="778" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F777" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
         <v>779</v>
       </c>
@@ -29316,8 +28750,11 @@
       <c r="D778" s="102" t="s">
         <v>1544</v>
       </c>
-    </row>
-    <row r="779" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F778" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
         <v>780</v>
       </c>
@@ -29330,8 +28767,11 @@
       <c r="D779" s="102" t="s">
         <v>1545</v>
       </c>
-    </row>
-    <row r="780" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F779" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
         <v>781</v>
       </c>
@@ -29344,8 +28784,11 @@
       <c r="D780" s="102" t="s">
         <v>1546</v>
       </c>
-    </row>
-    <row r="781" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F780" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
         <v>782</v>
       </c>
@@ -29358,8 +28801,11 @@
       <c r="D781" s="102" t="s">
         <v>1547</v>
       </c>
-    </row>
-    <row r="782" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F781" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
         <v>783</v>
       </c>
@@ -29372,8 +28818,11 @@
       <c r="D782" s="102" t="s">
         <v>1548</v>
       </c>
-    </row>
-    <row r="783" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F782" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
         <v>784</v>
       </c>
@@ -29386,8 +28835,11 @@
       <c r="D783" s="102" t="s">
         <v>1549</v>
       </c>
-    </row>
-    <row r="784" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F783" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
         <v>785</v>
       </c>
@@ -29400,8 +28852,11 @@
       <c r="D784" s="102" t="s">
         <v>1550</v>
       </c>
-    </row>
-    <row r="785" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F784" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
         <v>786</v>
       </c>
@@ -29414,8 +28869,11 @@
       <c r="D785" s="102" t="s">
         <v>1551</v>
       </c>
-    </row>
-    <row r="786" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F785" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
         <v>787</v>
       </c>
@@ -29428,8 +28886,11 @@
       <c r="D786" s="102" t="s">
         <v>1561</v>
       </c>
-    </row>
-    <row r="787" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F786" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
         <v>788</v>
       </c>
@@ -29442,8 +28903,11 @@
       <c r="D787" s="102" t="s">
         <v>1562</v>
       </c>
-    </row>
-    <row r="788" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F787" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
         <v>789</v>
       </c>
@@ -29456,8 +28920,11 @@
       <c r="D788" s="102" t="s">
         <v>1563</v>
       </c>
-    </row>
-    <row r="789" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F788" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
         <v>790</v>
       </c>
@@ -29470,8 +28937,11 @@
       <c r="D789" s="102" t="s">
         <v>1564</v>
       </c>
-    </row>
-    <row r="790" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F789" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
         <v>791</v>
       </c>
@@ -29484,8 +28954,11 @@
       <c r="D790" s="102" t="s">
         <v>1565</v>
       </c>
-    </row>
-    <row r="791" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F790" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
         <v>792</v>
       </c>
@@ -29498,8 +28971,11 @@
       <c r="D791" s="102" t="s">
         <v>1566</v>
       </c>
-    </row>
-    <row r="792" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F791" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
         <v>793</v>
       </c>
@@ -29512,8 +28988,11 @@
       <c r="D792" s="102" t="s">
         <v>1567</v>
       </c>
-    </row>
-    <row r="793" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F792" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
         <v>794</v>
       </c>
@@ -29526,8 +29005,11 @@
       <c r="D793" s="102" t="s">
         <v>1568</v>
       </c>
-    </row>
-    <row r="794" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F793" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
         <v>795</v>
       </c>
@@ -29540,8 +29022,11 @@
       <c r="D794" s="104" t="s">
         <v>1569</v>
       </c>
-    </row>
-    <row r="795" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F794" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
         <v>796</v>
       </c>
@@ -29554,8 +29039,11 @@
       <c r="D795" s="102" t="s">
         <v>1570</v>
       </c>
-    </row>
-    <row r="796" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F795" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
         <v>797</v>
       </c>
@@ -29568,8 +29056,11 @@
       <c r="D796" s="102" t="s">
         <v>1571</v>
       </c>
-    </row>
-    <row r="797" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F796" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
         <v>798</v>
       </c>
@@ -29582,8 +29073,11 @@
       <c r="D797" s="102" t="s">
         <v>1572</v>
       </c>
-    </row>
-    <row r="798" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F797" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
         <v>799</v>
       </c>
@@ -29596,8 +29090,11 @@
       <c r="D798" s="102" t="s">
         <v>1573</v>
       </c>
-    </row>
-    <row r="799" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F798" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
         <v>800</v>
       </c>
@@ -29610,8 +29107,11 @@
       <c r="D799" s="102" t="s">
         <v>1574</v>
       </c>
-    </row>
-    <row r="800" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F799" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
         <v>801</v>
       </c>
@@ -29624,8 +29124,11 @@
       <c r="D800" s="102" t="s">
         <v>1575</v>
       </c>
-    </row>
-    <row r="801" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F800" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
         <v>802</v>
       </c>
@@ -29638,8 +29141,11 @@
       <c r="D801" s="102" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="802" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F801" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
         <v>803</v>
       </c>
@@ -29652,8 +29158,11 @@
       <c r="D802" s="102" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="803" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F802" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
         <v>804</v>
       </c>
@@ -29666,8 +29175,11 @@
       <c r="D803" s="102" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="804" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F803" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
         <v>805</v>
       </c>
@@ -29680,8 +29192,11 @@
       <c r="D804" s="102" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="805" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F804" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
         <v>806</v>
       </c>
@@ -29694,8 +29209,11 @@
       <c r="D805" s="102" t="s">
         <v>1580</v>
       </c>
-    </row>
-    <row r="806" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F805" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
         <v>807</v>
       </c>
@@ -29708,8 +29226,11 @@
       <c r="D806" s="70" t="s">
         <v>1581</v>
       </c>
-    </row>
-    <row r="807" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F806" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
         <v>808</v>
       </c>
@@ -29722,8 +29243,11 @@
       <c r="D807" s="70" t="s">
         <v>1582</v>
       </c>
-    </row>
-    <row r="808" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F807" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
         <v>809</v>
       </c>
@@ -29736,8 +29260,11 @@
       <c r="D808" s="102" t="s">
         <v>1583</v>
       </c>
-    </row>
-    <row r="809" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F808" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
         <v>810</v>
       </c>
@@ -29750,8 +29277,11 @@
       <c r="D809" s="102" t="s">
         <v>1584</v>
       </c>
-    </row>
-    <row r="810" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F809" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
         <v>811</v>
       </c>
@@ -29764,8 +29294,11 @@
       <c r="D810" s="102" t="s">
         <v>1585</v>
       </c>
-    </row>
-    <row r="811" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F810" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
         <v>812</v>
       </c>
@@ -29778,8 +29311,11 @@
       <c r="D811" s="102" t="s">
         <v>1586</v>
       </c>
-    </row>
-    <row r="812" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F811" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
         <v>813</v>
       </c>
@@ -29792,8 +29328,11 @@
       <c r="D812" s="102" t="s">
         <v>1587</v>
       </c>
-    </row>
-    <row r="813" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F812" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
         <v>814</v>
       </c>
@@ -29806,8 +29345,11 @@
       <c r="D813" s="102" t="s">
         <v>1588</v>
       </c>
-    </row>
-    <row r="814" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F813" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
         <v>815</v>
       </c>
@@ -29820,8 +29362,11 @@
       <c r="D814" s="104" t="s">
         <v>1589</v>
       </c>
-    </row>
-    <row r="815" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F814" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
         <v>816</v>
       </c>
@@ -29834,8 +29379,11 @@
       <c r="D815" s="102" t="s">
         <v>1590</v>
       </c>
-    </row>
-    <row r="816" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F815" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
         <v>817</v>
       </c>
@@ -29849,7 +29397,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="817" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
         <v>818</v>
       </c>
@@ -29863,7 +29411,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="818" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
         <v>819</v>
       </c>
@@ -29877,7 +29425,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="819" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
         <v>820</v>
       </c>
@@ -29891,7 +29439,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="820" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
         <v>821</v>
       </c>
@@ -29905,7 +29453,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="821" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
         <v>822</v>
       </c>
@@ -29919,7 +29467,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="822" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
         <v>823</v>
       </c>
@@ -29933,7 +29481,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="823" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
         <v>824</v>
       </c>
@@ -29947,7 +29495,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="824" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
         <v>825</v>
       </c>
@@ -29961,7 +29509,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="825" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
         <v>826</v>
       </c>
@@ -29975,7 +29523,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="826" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
         <v>827</v>
       </c>
@@ -29989,7 +29537,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="827" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
         <v>828</v>
       </c>
@@ -30003,7 +29551,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="828" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
         <v>829</v>
       </c>
@@ -30017,7 +29565,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
         <v>830</v>
       </c>
@@ -30030,8 +29578,11 @@
       <c r="D829" s="107" t="s">
         <v>1648</v>
       </c>
-    </row>
-    <row r="830" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F829" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
         <v>831</v>
       </c>
@@ -30044,8 +29595,11 @@
       <c r="D830" s="107" t="s">
         <v>1649</v>
       </c>
-    </row>
-    <row r="831" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F830" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
         <v>832</v>
       </c>
@@ -30058,8 +29612,11 @@
       <c r="D831" s="107" t="s">
         <v>1650</v>
       </c>
-    </row>
-    <row r="832" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F831" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
         <v>833</v>
       </c>
@@ -30072,8 +29629,11 @@
       <c r="D832" s="107" t="s">
         <v>1651</v>
       </c>
-    </row>
-    <row r="833" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F832" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
         <v>834</v>
       </c>
@@ -30086,8 +29646,11 @@
       <c r="D833" s="107" t="s">
         <v>1652</v>
       </c>
-    </row>
-    <row r="834" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F833" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
         <v>835</v>
       </c>
@@ -30100,8 +29663,11 @@
       <c r="D834" s="107" t="s">
         <v>1653</v>
       </c>
-    </row>
-    <row r="835" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F834" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
         <v>836</v>
       </c>
@@ -30114,8 +29680,11 @@
       <c r="D835" s="107" t="s">
         <v>1654</v>
       </c>
-    </row>
-    <row r="836" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F835" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
         <v>837</v>
       </c>
@@ -30128,8 +29697,11 @@
       <c r="D836" s="70" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="837" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F836" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
         <v>838</v>
       </c>
@@ -30142,8 +29714,11 @@
       <c r="D837" s="70" t="s">
         <v>1662</v>
       </c>
-    </row>
-    <row r="838" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F837" s="1" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
         <v>839</v>
       </c>
@@ -30157,7 +29732,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="839" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
         <v>840</v>
       </c>
@@ -30171,7 +29746,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="840" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
         <v>841</v>
       </c>
@@ -30185,7 +29760,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="841" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
         <v>842</v>
       </c>
@@ -30199,7 +29774,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="842" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
         <v>843</v>
       </c>
@@ -30213,7 +29788,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="843" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
         <v>844</v>
       </c>
@@ -30227,7 +29802,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="844" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
         <v>845</v>
       </c>
@@ -30241,7 +29816,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="845" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
         <v>846</v>
       </c>
@@ -30255,7 +29830,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="846" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
         <v>847</v>
       </c>
@@ -30269,7 +29844,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="847" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
         <v>848</v>
       </c>
@@ -30283,7 +29858,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="848" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
         <v>849</v>
       </c>
@@ -31139,7 +30714,7 @@
         <v>1822</v>
       </c>
       <c r="C918" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D918" s="122">
         <v>3721</v>
@@ -31153,7 +30728,7 @@
         <v>1823</v>
       </c>
       <c r="C919" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D919" s="122">
         <v>2533</v>
@@ -31167,7 +30742,7 @@
         <v>1824</v>
       </c>
       <c r="C920" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D920" s="122">
         <v>2532</v>
@@ -31181,7 +30756,7 @@
         <v>1825</v>
       </c>
       <c r="C921" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D921" s="122">
         <v>3303</v>
@@ -31195,7 +30770,7 @@
         <v>1826</v>
       </c>
       <c r="C922" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D922" s="122">
         <v>2531</v>
@@ -31209,7 +30784,7 @@
         <v>1827</v>
       </c>
       <c r="C923" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D923" s="122">
         <v>2530</v>
@@ -31223,7 +30798,7 @@
         <v>1828</v>
       </c>
       <c r="C924" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D924" s="122">
         <v>4416</v>
@@ -31237,7 +30812,7 @@
         <v>1829</v>
       </c>
       <c r="C925" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D925" s="122">
         <v>4415</v>
@@ -31251,7 +30826,7 @@
         <v>1830</v>
       </c>
       <c r="C926" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D926" s="122">
         <v>2305</v>
@@ -31265,7 +30840,7 @@
         <v>1831</v>
       </c>
       <c r="C927" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D927" s="122">
         <v>2566</v>
@@ -31279,7 +30854,7 @@
         <v>1832</v>
       </c>
       <c r="C928" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D928" s="122">
         <v>2629</v>
@@ -31293,7 +30868,7 @@
         <v>1833</v>
       </c>
       <c r="C929" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D929" s="122">
         <v>2625</v>
@@ -31307,7 +30882,7 @@
         <v>1834</v>
       </c>
       <c r="C930" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D930" s="122">
         <v>3113</v>
@@ -31321,7 +30896,7 @@
         <v>1835</v>
       </c>
       <c r="C931" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D931" s="122">
         <v>3118</v>
@@ -31335,7 +30910,7 @@
         <v>1836</v>
       </c>
       <c r="C932" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D932" s="122">
         <v>1049</v>
@@ -31349,7 +30924,7 @@
         <v>1837</v>
       </c>
       <c r="C933" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D933" s="122">
         <v>2428</v>
@@ -31363,7 +30938,7 @@
         <v>1838</v>
       </c>
       <c r="C934" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D934" s="122">
         <v>3119</v>
@@ -31377,7 +30952,7 @@
         <v>1839</v>
       </c>
       <c r="C935" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D935" s="122">
         <v>3725</v>
@@ -31391,7 +30966,7 @@
         <v>1840</v>
       </c>
       <c r="C936" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D936" s="122">
         <v>3726</v>
@@ -31405,7 +30980,7 @@
         <v>1841</v>
       </c>
       <c r="C937" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D937" s="122">
         <v>3727</v>
@@ -31419,7 +30994,7 @@
         <v>1842</v>
       </c>
       <c r="C938" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D938" s="123">
         <v>3728</v>
@@ -31433,7 +31008,7 @@
         <v>1843</v>
       </c>
       <c r="C939" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D939" s="122">
         <v>816</v>
@@ -31447,7 +31022,7 @@
         <v>1844</v>
       </c>
       <c r="C940" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D940" s="122">
         <v>1180</v>
@@ -31461,7 +31036,7 @@
         <v>1845</v>
       </c>
       <c r="C941" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D941" s="122">
         <v>5017</v>
@@ -31475,7 +31050,7 @@
         <v>1846</v>
       </c>
       <c r="C942" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D942" s="122">
         <v>3859</v>
@@ -31489,7 +31064,7 @@
         <v>1847</v>
       </c>
       <c r="C943" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D943" s="122">
         <v>3464</v>
@@ -31503,7 +31078,7 @@
         <v>1848</v>
       </c>
       <c r="C944" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D944" s="122">
         <v>6854</v>
@@ -31517,7 +31092,7 @@
         <v>1849</v>
       </c>
       <c r="C945" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D945" s="122">
         <v>4666</v>
@@ -31531,7 +31106,7 @@
         <v>1850</v>
       </c>
       <c r="C946" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D946" s="122">
         <v>4102</v>
@@ -31545,7 +31120,7 @@
         <v>1851</v>
       </c>
       <c r="C947" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D947" s="122">
         <v>2317</v>
@@ -31559,7 +31134,7 @@
         <v>1852</v>
       </c>
       <c r="C948" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D948" s="123">
         <v>4422</v>
@@ -31573,7 +31148,7 @@
         <v>1853</v>
       </c>
       <c r="C949" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D949" s="122">
         <v>6322</v>
@@ -31587,7 +31162,7 @@
         <v>1854</v>
       </c>
       <c r="C950" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D950" s="122">
         <v>3608</v>
@@ -31601,7 +31176,7 @@
         <v>1855</v>
       </c>
       <c r="C951" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D951" s="122">
         <v>3610</v>
@@ -31615,7 +31190,7 @@
         <v>1856</v>
       </c>
       <c r="C952" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D952" s="122">
         <v>3613</v>
@@ -31629,7 +31204,7 @@
         <v>1857</v>
       </c>
       <c r="C953" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D953" s="122">
         <v>3617</v>
@@ -31643,7 +31218,7 @@
         <v>1858</v>
       </c>
       <c r="C954" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D954" s="122">
         <v>3619</v>
@@ -31657,7 +31232,7 @@
         <v>1859</v>
       </c>
       <c r="C955" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D955" s="122">
         <v>2390</v>
@@ -31671,7 +31246,7 @@
         <v>1860</v>
       </c>
       <c r="C956" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D956" s="122">
         <v>2391</v>
@@ -31685,7 +31260,7 @@
         <v>1861</v>
       </c>
       <c r="C957" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D957" s="122">
         <v>2392</v>
@@ -31699,7 +31274,7 @@
         <v>1862</v>
       </c>
       <c r="C958" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D958" s="122">
         <v>2589</v>
@@ -31713,7 +31288,7 @@
         <v>1863</v>
       </c>
       <c r="C959" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D959" s="122">
         <v>2393</v>
@@ -31727,7 +31302,7 @@
         <v>1864</v>
       </c>
       <c r="C960" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D960" s="122">
         <v>2394</v>
@@ -31741,7 +31316,7 @@
         <v>1865</v>
       </c>
       <c r="C961" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D961" s="122">
         <v>2395</v>
@@ -31755,7 +31330,7 @@
         <v>1866</v>
       </c>
       <c r="C962" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D962" s="122">
         <v>2396</v>
@@ -31769,7 +31344,7 @@
         <v>1867</v>
       </c>
       <c r="C963" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D963" s="122">
         <v>2397</v>
@@ -31783,7 +31358,7 @@
         <v>1868</v>
       </c>
       <c r="C964" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D964" s="122">
         <v>2398</v>
@@ -31797,7 +31372,7 @@
         <v>1869</v>
       </c>
       <c r="C965" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D965" s="122">
         <v>2399</v>
@@ -31811,7 +31386,7 @@
         <v>1870</v>
       </c>
       <c r="C966" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D966" s="122">
         <v>2400</v>
@@ -31825,7 +31400,7 @@
         <v>1871</v>
       </c>
       <c r="C967" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D967" s="122">
         <v>2401</v>
@@ -31839,7 +31414,7 @@
         <v>1872</v>
       </c>
       <c r="C968" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D968" s="122">
         <v>2402</v>
@@ -31853,7 +31428,7 @@
         <v>1873</v>
       </c>
       <c r="C969" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D969" s="122">
         <v>2590</v>
@@ -31867,7 +31442,7 @@
         <v>1874</v>
       </c>
       <c r="C970" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D970" s="122">
         <v>2403</v>
@@ -31881,7 +31456,7 @@
         <v>1875</v>
       </c>
       <c r="C971" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D971" s="122">
         <v>2404</v>
@@ -31895,7 +31470,7 @@
         <v>1876</v>
       </c>
       <c r="C972" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D972" s="122">
         <v>2405</v>
@@ -31909,7 +31484,7 @@
         <v>1877</v>
       </c>
       <c r="C973" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D973" s="122">
         <v>2406</v>
@@ -31923,7 +31498,7 @@
         <v>1878</v>
       </c>
       <c r="C974" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D974" s="122">
         <v>2591</v>
@@ -31937,7 +31512,7 @@
         <v>1879</v>
       </c>
       <c r="C975" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D975" s="122">
         <v>2407</v>
@@ -31951,7 +31526,7 @@
         <v>1880</v>
       </c>
       <c r="C976" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D976" s="122">
         <v>2408</v>
@@ -31965,7 +31540,7 @@
         <v>1881</v>
       </c>
       <c r="C977" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D977" s="122">
         <v>2592</v>
@@ -31979,7 +31554,7 @@
         <v>1882</v>
       </c>
       <c r="C978" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D978" s="122">
         <v>2627</v>
@@ -31993,7 +31568,7 @@
         <v>1883</v>
       </c>
       <c r="C979" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D979" s="122">
         <v>2409</v>
@@ -32007,7 +31582,7 @@
         <v>1884</v>
       </c>
       <c r="C980" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D980" s="122">
         <v>2410</v>
@@ -32021,7 +31596,7 @@
         <v>1885</v>
       </c>
       <c r="C981" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D981" s="122">
         <v>2415</v>
@@ -32035,7 +31610,7 @@
         <v>1886</v>
       </c>
       <c r="C982" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D982" s="122">
         <v>2411</v>
@@ -32049,7 +31624,7 @@
         <v>1887</v>
       </c>
       <c r="C983" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D983" s="122">
         <v>2418</v>
@@ -32063,7 +31638,7 @@
         <v>1888</v>
       </c>
       <c r="C984" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D984" s="122">
         <v>2414</v>
@@ -32077,7 +31652,7 @@
         <v>1889</v>
       </c>
       <c r="C985" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D985" s="122">
         <v>2416</v>
@@ -32091,7 +31666,7 @@
         <v>1890</v>
       </c>
       <c r="C986" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D986" s="122">
         <v>2505</v>
@@ -32105,7 +31680,7 @@
         <v>1891</v>
       </c>
       <c r="C987" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D987" s="122">
         <v>3812</v>
@@ -32119,7 +31694,7 @@
         <v>1892</v>
       </c>
       <c r="C988" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D988" s="122">
         <v>3829</v>
@@ -32133,7 +31708,7 @@
         <v>1893</v>
       </c>
       <c r="C989" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D989" s="122">
         <v>931</v>
@@ -32147,7 +31722,7 @@
         <v>1894</v>
       </c>
       <c r="C990" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D990" s="122">
         <v>3430</v>
@@ -32161,7 +31736,7 @@
         <v>1895</v>
       </c>
       <c r="C991" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D991" s="122">
         <v>3431</v>
@@ -32175,7 +31750,7 @@
         <v>1896</v>
       </c>
       <c r="C992" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D992" s="125">
         <v>1124</v>
@@ -32189,7 +31764,7 @@
         <v>1897</v>
       </c>
       <c r="C993" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D993" s="122">
         <v>31</v>
@@ -32203,7 +31778,7 @@
         <v>1898</v>
       </c>
       <c r="C994" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D994" s="122">
         <v>2328</v>
@@ -32217,7 +31792,7 @@
         <v>1899</v>
       </c>
       <c r="C995" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D995" s="122">
         <v>45</v>
@@ -32231,7 +31806,7 @@
         <v>1900</v>
       </c>
       <c r="C996" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D996" s="122">
         <v>635</v>
@@ -32245,7 +31820,7 @@
         <v>1901</v>
       </c>
       <c r="C997" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D997" s="122">
         <v>1076</v>
@@ -32259,7 +31834,7 @@
         <v>1902</v>
       </c>
       <c r="C998" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D998" s="122">
         <v>1123</v>
@@ -32273,7 +31848,7 @@
         <v>1903</v>
       </c>
       <c r="C999" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D999" s="122">
         <v>2233</v>
@@ -32287,7 +31862,7 @@
         <v>1904</v>
       </c>
       <c r="C1000" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1000" s="125">
         <v>3104</v>
@@ -32301,7 +31876,7 @@
         <v>1905</v>
       </c>
       <c r="C1001" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1001" s="122">
         <v>4969</v>
@@ -32315,7 +31890,7 @@
         <v>1906</v>
       </c>
       <c r="C1002" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1002" s="122">
         <v>1363</v>
@@ -32329,7 +31904,7 @@
         <v>1907</v>
       </c>
       <c r="C1003" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1003" s="122">
         <v>724</v>
@@ -32343,7 +31918,7 @@
         <v>1908</v>
       </c>
       <c r="C1004" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1004" s="122">
         <v>1045</v>
@@ -32357,7 +31932,7 @@
         <v>1909</v>
       </c>
       <c r="C1005" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1005" s="122">
         <v>3279</v>
@@ -32371,7 +31946,7 @@
         <v>1910</v>
       </c>
       <c r="C1006" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1006" s="123">
         <v>3280</v>
@@ -32385,7 +31960,7 @@
         <v>1911</v>
       </c>
       <c r="C1007" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1007" s="123">
         <v>4965</v>
@@ -32399,7 +31974,7 @@
         <v>1912</v>
       </c>
       <c r="C1008" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1008" s="122">
         <v>903</v>
@@ -32413,7 +31988,7 @@
         <v>1913</v>
       </c>
       <c r="C1009" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1009" s="122">
         <v>1036</v>
@@ -32427,7 +32002,7 @@
         <v>1914</v>
       </c>
       <c r="C1010" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1010" s="122">
         <v>4401</v>
@@ -32441,7 +32016,7 @@
         <v>1915</v>
       </c>
       <c r="C1011" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1011" s="122">
         <v>3314</v>
@@ -32455,7 +32030,7 @@
         <v>1916</v>
       </c>
       <c r="C1012" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1012" s="122">
         <v>3723</v>
@@ -32469,7 +32044,7 @@
         <v>1917</v>
       </c>
       <c r="C1013" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1013" s="122">
         <v>3722</v>
@@ -32483,7 +32058,7 @@
         <v>1918</v>
       </c>
       <c r="C1014" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1014" s="122">
         <v>75</v>
@@ -32497,7 +32072,7 @@
         <v>1919</v>
       </c>
       <c r="C1015" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1015" s="122">
         <v>5013</v>
@@ -32511,7 +32086,7 @@
         <v>1920</v>
       </c>
       <c r="C1016" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1016" s="122">
         <v>2749</v>
@@ -32525,7 +32100,7 @@
         <v>1921</v>
       </c>
       <c r="C1017" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1017" s="122">
         <v>2750</v>
@@ -32539,7 +32114,7 @@
         <v>1922</v>
       </c>
       <c r="C1018" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1018" s="122">
         <v>1067</v>
@@ -32553,7 +32128,7 @@
         <v>1923</v>
       </c>
       <c r="C1019" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1019" s="122">
         <v>3354</v>
@@ -32567,7 +32142,7 @@
         <v>1924</v>
       </c>
       <c r="C1020" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1020" s="122">
         <v>3352</v>
@@ -32581,7 +32156,7 @@
         <v>1925</v>
       </c>
       <c r="C1021" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1021" s="122">
         <v>5165</v>
@@ -32595,7 +32170,7 @@
         <v>1926</v>
       </c>
       <c r="C1022" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1022" s="122">
         <v>3462</v>
@@ -32609,7 +32184,7 @@
         <v>1927</v>
       </c>
       <c r="C1023" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1023" s="122">
         <v>3832</v>
@@ -32623,7 +32198,7 @@
         <v>1928</v>
       </c>
       <c r="C1024" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1024" s="122">
         <v>3330</v>
@@ -32637,7 +32212,7 @@
         <v>1929</v>
       </c>
       <c r="C1025" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1025" s="122">
         <v>7261</v>
@@ -32651,7 +32226,7 @@
         <v>1930</v>
       </c>
       <c r="C1026" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1026" s="122">
         <v>2535</v>
@@ -32665,7 +32240,7 @@
         <v>1931</v>
       </c>
       <c r="C1027" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1027" s="122">
         <v>4431</v>
@@ -32679,7 +32254,7 @@
         <v>1932</v>
       </c>
       <c r="C1028" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1028" s="122">
         <v>4817</v>
@@ -32693,7 +32268,7 @@
         <v>1933</v>
       </c>
       <c r="C1029" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1029" s="122">
         <v>7259</v>
@@ -32707,7 +32282,7 @@
         <v>1934</v>
       </c>
       <c r="C1030" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1030" s="122">
         <v>4430</v>
@@ -32721,7 +32296,7 @@
         <v>1935</v>
       </c>
       <c r="C1031" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1031" s="122">
         <v>3289</v>
@@ -32735,7 +32310,7 @@
         <v>1936</v>
       </c>
       <c r="C1032" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1032" s="122">
         <v>3290</v>
@@ -32749,7 +32324,7 @@
         <v>1937</v>
       </c>
       <c r="C1033" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1033" s="122">
         <v>3291</v>
@@ -32763,7 +32338,7 @@
         <v>1938</v>
       </c>
       <c r="C1034" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1034" s="122">
         <v>6235</v>
@@ -32777,7 +32352,7 @@
         <v>1939</v>
       </c>
       <c r="C1035" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1035" s="122">
         <v>6218</v>
@@ -32791,7 +32366,7 @@
         <v>1940</v>
       </c>
       <c r="C1036" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1036" s="122">
         <v>6138</v>
@@ -32805,7 +32380,7 @@
         <v>1941</v>
       </c>
       <c r="C1037" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1037" s="122">
         <v>6230</v>
@@ -32819,7 +32394,7 @@
         <v>1942</v>
       </c>
       <c r="C1038" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1038" s="122">
         <v>3860</v>
@@ -32833,7 +32408,7 @@
         <v>1943</v>
       </c>
       <c r="C1039" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1039" s="122">
         <v>668</v>
@@ -32847,7 +32422,7 @@
         <v>1944</v>
       </c>
       <c r="C1040" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1040" s="122">
         <v>4161</v>
@@ -32861,7 +32436,7 @@
         <v>1945</v>
       </c>
       <c r="C1041" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1041" s="122">
         <v>3052</v>
@@ -32875,7 +32450,7 @@
         <v>1946</v>
       </c>
       <c r="C1042" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1042" s="122">
         <v>3417</v>
@@ -32889,7 +32464,7 @@
         <v>1947</v>
       </c>
       <c r="C1043" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1043" s="122">
         <v>6836</v>
@@ -32903,7 +32478,7 @@
         <v>1948</v>
       </c>
       <c r="C1044" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1044" s="122">
         <v>5504</v>
@@ -32917,7 +32492,7 @@
         <v>1949</v>
       </c>
       <c r="C1045" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1045" s="125">
         <v>5508</v>
@@ -32931,7 +32506,7 @@
         <v>1950</v>
       </c>
       <c r="C1046" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1046" s="122">
         <v>4959</v>
@@ -32945,7 +32520,7 @@
         <v>1951</v>
       </c>
       <c r="C1047" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1047" s="122">
         <v>3049</v>
@@ -32959,7 +32534,7 @@
         <v>1952</v>
       </c>
       <c r="C1048" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1048" s="122">
         <v>1393</v>
@@ -32973,7 +32548,7 @@
         <v>1953</v>
       </c>
       <c r="C1049" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1049" s="122">
         <v>4649</v>
@@ -32987,7 +32562,7 @@
         <v>1954</v>
       </c>
       <c r="C1050" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1050" s="122">
         <v>1353</v>
@@ -33001,7 +32576,7 @@
         <v>1955</v>
       </c>
       <c r="C1051" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1051" s="122">
         <v>67</v>
@@ -33015,7 +32590,7 @@
         <v>1956</v>
       </c>
       <c r="C1052" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1052" s="123">
         <v>3397</v>
@@ -33029,7 +32604,7 @@
         <v>1957</v>
       </c>
       <c r="C1053" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1053" s="123">
         <v>7225</v>
@@ -33043,7 +32618,7 @@
         <v>1958</v>
       </c>
       <c r="C1054" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1054" s="122">
         <v>3242</v>
@@ -33057,7 +32632,7 @@
         <v>1959</v>
       </c>
       <c r="C1055" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1055" s="122">
         <v>2650</v>
@@ -33071,7 +32646,7 @@
         <v>1960</v>
       </c>
       <c r="C1056" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1056" s="122">
         <v>2506</v>
@@ -33085,7 +32660,7 @@
         <v>1961</v>
       </c>
       <c r="C1057" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1057" s="122">
         <v>4404</v>
@@ -33099,7 +32674,7 @@
         <v>1962</v>
       </c>
       <c r="C1058" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1058" s="122">
         <v>4831</v>
@@ -33113,7 +32688,7 @@
         <v>1963</v>
       </c>
       <c r="C1059" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1059" s="122">
         <v>3806</v>
@@ -33127,7 +32702,7 @@
         <v>1964</v>
       </c>
       <c r="C1060" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1060" s="123">
         <v>6900</v>
@@ -33141,7 +32716,7 @@
         <v>1965</v>
       </c>
       <c r="C1061" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1061" s="123">
         <v>6901</v>
@@ -33155,7 +32730,7 @@
         <v>1966</v>
       </c>
       <c r="C1062" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1062" s="123">
         <v>6899</v>
@@ -33169,7 +32744,7 @@
         <v>1967</v>
       </c>
       <c r="C1063" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1063" s="122">
         <v>4968</v>
@@ -33183,7 +32758,7 @@
         <v>1968</v>
       </c>
       <c r="C1064" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1064" s="122">
         <v>2316</v>
@@ -33197,7 +32772,7 @@
         <v>1969</v>
       </c>
       <c r="C1065" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1065" s="122">
         <v>2649</v>
@@ -33211,7 +32786,7 @@
         <v>1970</v>
       </c>
       <c r="C1066" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1066" s="122">
         <v>4839</v>
@@ -33225,7 +32800,7 @@
         <v>1971</v>
       </c>
       <c r="C1067" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1067" s="122">
         <v>3218</v>
@@ -33239,7 +32814,7 @@
         <v>1972</v>
       </c>
       <c r="C1068" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1068" s="122">
         <v>3219</v>
@@ -33253,7 +32828,7 @@
         <v>1973</v>
       </c>
       <c r="C1069" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1069" s="122">
         <v>2554</v>
@@ -33267,7 +32842,7 @@
         <v>1974</v>
       </c>
       <c r="C1070" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1070" s="122">
         <v>2662</v>
@@ -33281,7 +32856,7 @@
         <v>1975</v>
       </c>
       <c r="C1071" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1071" s="122">
         <v>2555</v>
@@ -33295,7 +32870,7 @@
         <v>1976</v>
       </c>
       <c r="C1072" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1072" s="122">
         <v>2556</v>
@@ -33309,7 +32884,7 @@
         <v>1977</v>
       </c>
       <c r="C1073" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1073" s="122">
         <v>2557</v>
@@ -33323,7 +32898,7 @@
         <v>1978</v>
       </c>
       <c r="C1074" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1074" s="122">
         <v>2558</v>
@@ -33337,7 +32912,7 @@
         <v>1979</v>
       </c>
       <c r="C1075" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1075" s="122">
         <v>2559</v>
@@ -33351,7 +32926,7 @@
         <v>1980</v>
       </c>
       <c r="C1076" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1076" s="122">
         <v>2663</v>
@@ -33365,7 +32940,7 @@
         <v>1981</v>
       </c>
       <c r="C1077" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1077" s="122">
         <v>2664</v>
@@ -33379,7 +32954,7 @@
         <v>1982</v>
       </c>
       <c r="C1078" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1078" s="122">
         <v>2560</v>
@@ -33393,7 +32968,7 @@
         <v>1983</v>
       </c>
       <c r="C1079" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1079" s="122">
         <v>2665</v>
@@ -33407,7 +32982,7 @@
         <v>1984</v>
       </c>
       <c r="C1080" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1080" s="122">
         <v>2561</v>
@@ -33421,7 +32996,7 @@
         <v>1985</v>
       </c>
       <c r="C1081" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1081" s="122">
         <v>2104</v>
@@ -33435,7 +33010,7 @@
         <v>1986</v>
       </c>
       <c r="C1082" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1082" s="122">
         <v>3824</v>
@@ -33449,7 +33024,7 @@
         <v>1987</v>
       </c>
       <c r="C1083" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1083" s="122">
         <v>1050</v>
@@ -33463,7 +33038,7 @@
         <v>1988</v>
       </c>
       <c r="C1084" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1084" s="122">
         <v>3379</v>
@@ -33477,7 +33052,7 @@
         <v>1989</v>
       </c>
       <c r="C1085" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1085" s="122">
         <v>519</v>
@@ -33491,7 +33066,7 @@
         <v>1990</v>
       </c>
       <c r="C1086" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1086" s="122">
         <v>529</v>
@@ -33505,7 +33080,7 @@
         <v>1991</v>
       </c>
       <c r="C1087" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1087" s="122">
         <v>3121</v>
@@ -33519,7 +33094,7 @@
         <v>1992</v>
       </c>
       <c r="C1088" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1088" s="122">
         <v>5182</v>
@@ -33533,7 +33108,7 @@
         <v>1993</v>
       </c>
       <c r="C1089" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1089" s="122">
         <v>5181</v>
@@ -33547,7 +33122,7 @@
         <v>1994</v>
       </c>
       <c r="C1090" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1090" s="122">
         <v>5183</v>
@@ -33561,7 +33136,7 @@
         <v>1995</v>
       </c>
       <c r="C1091" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1091" s="122">
         <v>2628</v>
@@ -33575,7 +33150,7 @@
         <v>1996</v>
       </c>
       <c r="C1092" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1092" s="122">
         <v>2237</v>
@@ -33589,7 +33164,7 @@
         <v>1997</v>
       </c>
       <c r="C1093" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1093" s="123">
         <v>2500</v>
@@ -33603,7 +33178,7 @@
         <v>1998</v>
       </c>
       <c r="C1094" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1094" s="123">
         <v>7147</v>
@@ -33617,7 +33192,7 @@
         <v>1999</v>
       </c>
       <c r="C1095" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1095" s="122">
         <v>3091</v>
@@ -33631,7 +33206,7 @@
         <v>2000</v>
       </c>
       <c r="C1096" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1096" s="122">
         <v>3090</v>
@@ -33645,7 +33220,7 @@
         <v>2001</v>
       </c>
       <c r="C1097" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1097" s="122">
         <v>6207</v>
@@ -33659,7 +33234,7 @@
         <v>2002</v>
       </c>
       <c r="C1098" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1098" s="123">
         <v>4618</v>
@@ -33673,7 +33248,7 @@
         <v>2003</v>
       </c>
       <c r="C1099" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1099" s="122">
         <v>4644</v>
@@ -33687,7 +33262,7 @@
         <v>2004</v>
       </c>
       <c r="C1100" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1100" s="122">
         <v>2515</v>
@@ -33701,7 +33276,7 @@
         <v>2005</v>
       </c>
       <c r="C1101" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1101" s="122">
         <v>2516</v>
@@ -33715,7 +33290,7 @@
         <v>2006</v>
       </c>
       <c r="C1102" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1102" s="123">
         <v>911</v>
@@ -33729,7 +33304,7 @@
         <v>2007</v>
       </c>
       <c r="C1103" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1103" s="122">
         <v>4631</v>
@@ -33743,7 +33318,7 @@
         <v>2008</v>
       </c>
       <c r="C1104" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1104" s="122">
         <v>3862</v>
@@ -33757,7 +33332,7 @@
         <v>2009</v>
       </c>
       <c r="C1105" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1105" s="122">
         <v>3856</v>
@@ -33771,7 +33346,7 @@
         <v>2010</v>
       </c>
       <c r="C1106" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1106" s="122">
         <v>3428</v>
@@ -33785,7 +33360,7 @@
         <v>2011</v>
       </c>
       <c r="C1107" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1107" s="122">
         <v>3429</v>
@@ -33799,7 +33374,7 @@
         <v>2012</v>
       </c>
       <c r="C1108" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1108" s="122">
         <v>2509</v>
@@ -33813,7 +33388,7 @@
         <v>2013</v>
       </c>
       <c r="C1109" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1109" s="122">
         <v>2541</v>
@@ -33827,7 +33402,7 @@
         <v>2014</v>
       </c>
       <c r="C1110" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1110" s="122">
         <v>1020</v>
@@ -33841,7 +33416,7 @@
         <v>2015</v>
       </c>
       <c r="C1111" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1111" s="122">
         <v>1394</v>
@@ -33855,7 +33430,7 @@
         <v>2016</v>
       </c>
       <c r="C1112" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1112" s="122">
         <v>7296</v>
@@ -33869,7 +33444,7 @@
         <v>2017</v>
       </c>
       <c r="C1113" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1113" s="122">
         <v>2165</v>
@@ -33883,7 +33458,7 @@
         <v>2018</v>
       </c>
       <c r="C1114" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1114" s="122">
         <v>3238</v>
@@ -33897,7 +33472,7 @@
         <v>2019</v>
       </c>
       <c r="C1115" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1115" s="122">
         <v>3822</v>
@@ -33911,7 +33486,7 @@
         <v>2020</v>
       </c>
       <c r="C1116" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1116" s="122">
         <v>4423</v>
@@ -33925,7 +33500,7 @@
         <v>2021</v>
       </c>
       <c r="C1117" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1117" s="122">
         <v>1046</v>
@@ -33939,7 +33514,7 @@
         <v>2022</v>
       </c>
       <c r="C1118" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1118" s="122">
         <v>1043</v>
@@ -33953,7 +33528,7 @@
         <v>2023</v>
       </c>
       <c r="C1119" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1119" s="122">
         <v>3513</v>
@@ -33967,7 +33542,7 @@
         <v>2024</v>
       </c>
       <c r="C1120" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1120" s="122">
         <v>3511</v>
@@ -33981,7 +33556,7 @@
         <v>2025</v>
       </c>
       <c r="C1121" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1121" s="125">
         <v>4622</v>
@@ -33995,7 +33570,7 @@
         <v>2026</v>
       </c>
       <c r="C1122" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1122" s="122">
         <v>4824</v>
@@ -34009,7 +33584,7 @@
         <v>2027</v>
       </c>
       <c r="C1123" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1123" s="122">
         <v>3301</v>
@@ -34023,7 +33598,7 @@
         <v>2028</v>
       </c>
       <c r="C1124" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1124" s="122">
         <v>4836</v>
@@ -34037,7 +33612,7 @@
         <v>2029</v>
       </c>
       <c r="C1125" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1125" s="125">
         <v>5032</v>
@@ -34051,7 +33626,7 @@
         <v>2030</v>
       </c>
       <c r="C1126" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1126" s="122">
         <v>2181</v>
@@ -34065,7 +33640,7 @@
         <v>2031</v>
       </c>
       <c r="C1127" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1127" s="123">
         <v>6347</v>
@@ -34079,7 +33654,7 @@
         <v>2032</v>
       </c>
       <c r="C1128" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1128" s="129">
         <v>5033</v>
@@ -34093,7 +33668,7 @@
         <v>2033</v>
       </c>
       <c r="C1129" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1129" s="122">
         <v>2624</v>
@@ -34107,7 +33682,7 @@
         <v>2034</v>
       </c>
       <c r="C1130" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1130" s="125">
         <v>2623</v>
@@ -34121,7 +33696,7 @@
         <v>2035</v>
       </c>
       <c r="C1131" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1131" s="122">
         <v>4623</v>
@@ -34135,7 +33710,7 @@
         <v>2036</v>
       </c>
       <c r="C1132" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1132" s="122">
         <v>1086</v>
@@ -34149,7 +33724,7 @@
         <v>2037</v>
       </c>
       <c r="C1133" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1133" s="122">
         <v>6307</v>
@@ -34163,7 +33738,7 @@
         <v>2038</v>
       </c>
       <c r="C1134" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1134" s="130">
         <v>4423</v>
@@ -34177,7 +33752,7 @@
         <v>2039</v>
       </c>
       <c r="C1135" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1135" s="122">
         <v>6210</v>
@@ -34191,7 +33766,7 @@
         <v>2040</v>
       </c>
       <c r="C1136" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1136" s="122">
         <v>6211</v>
@@ -34205,7 +33780,7 @@
         <v>2041</v>
       </c>
       <c r="C1137" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1137" s="122">
         <v>4650</v>
@@ -34219,7 +33794,7 @@
         <v>2042</v>
       </c>
       <c r="C1138" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1138" s="122">
         <v>5036</v>
@@ -34233,7 +33808,7 @@
         <v>2043</v>
       </c>
       <c r="C1139" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1139" s="130">
         <v>5037</v>
@@ -34247,7 +33822,7 @@
         <v>2044</v>
       </c>
       <c r="C1140" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1140" s="122">
         <v>5019</v>
@@ -34261,7 +33836,7 @@
         <v>2045</v>
       </c>
       <c r="C1141" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1141" s="122">
         <v>175</v>
@@ -34275,7 +33850,7 @@
         <v>2046</v>
       </c>
       <c r="C1142" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1142" s="122">
         <v>875</v>
@@ -34289,7 +33864,7 @@
         <v>2047</v>
       </c>
       <c r="C1143" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1143" s="122">
         <v>3840</v>
@@ -34303,7 +33878,7 @@
         <v>2048</v>
       </c>
       <c r="C1144" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1144" s="122">
         <v>811</v>
@@ -34317,7 +33892,7 @@
         <v>2049</v>
       </c>
       <c r="C1145" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1145" s="122">
         <v>2318</v>
@@ -34331,7 +33906,7 @@
         <v>2050</v>
       </c>
       <c r="C1146" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1146" s="123">
         <v>5023</v>
@@ -34345,7 +33920,7 @@
         <v>2051</v>
       </c>
       <c r="C1147" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1147" s="123">
         <v>5024</v>
@@ -34359,7 +33934,7 @@
         <v>2052</v>
       </c>
       <c r="C1148" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1148" s="122">
         <v>4235</v>
@@ -34373,7 +33948,7 @@
         <v>2053</v>
       </c>
       <c r="C1149" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1149" s="122">
         <v>4616</v>
@@ -34387,7 +33962,7 @@
         <v>2054</v>
       </c>
       <c r="C1150" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1150" s="122">
         <v>4615</v>
@@ -34401,7 +33976,7 @@
         <v>2055</v>
       </c>
       <c r="C1151" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1151" s="125">
         <v>6583</v>
@@ -34415,7 +33990,7 @@
         <v>2056</v>
       </c>
       <c r="C1152" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1152" s="122">
         <v>1421</v>
@@ -34429,7 +34004,7 @@
         <v>2057</v>
       </c>
       <c r="C1153" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1153" s="122">
         <v>2620</v>
@@ -34443,7 +34018,7 @@
         <v>2058</v>
       </c>
       <c r="C1154" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1154" s="122">
         <v>2621</v>
@@ -34457,7 +34032,7 @@
         <v>2059</v>
       </c>
       <c r="C1155" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1155" s="122">
         <v>2622</v>
@@ -34471,7 +34046,7 @@
         <v>2060</v>
       </c>
       <c r="C1156" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1156" s="122">
         <v>3322</v>
@@ -34485,7 +34060,7 @@
         <v>2061</v>
       </c>
       <c r="C1157" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1157" s="122">
         <v>2442</v>
@@ -34499,7 +34074,7 @@
         <v>2062</v>
       </c>
       <c r="C1158" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1158" s="122">
         <v>3355</v>
@@ -34513,7 +34088,7 @@
         <v>2063</v>
       </c>
       <c r="C1159" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1159" s="122">
         <v>4405</v>
@@ -34527,7 +34102,7 @@
         <v>2064</v>
       </c>
       <c r="C1160" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1160" s="122">
         <v>2300</v>
@@ -34541,7 +34116,7 @@
         <v>2065</v>
       </c>
       <c r="C1161" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1161" s="122">
         <v>4410</v>
@@ -34555,7 +34130,7 @@
         <v>2066</v>
       </c>
       <c r="C1162" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1162" s="122">
         <v>1427</v>
@@ -34569,7 +34144,7 @@
         <v>2067</v>
       </c>
       <c r="C1163" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1163" s="122">
         <v>1426</v>
@@ -34583,7 +34158,7 @@
         <v>2068</v>
       </c>
       <c r="C1164" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1164" s="122">
         <v>2302</v>
@@ -34597,7 +34172,7 @@
         <v>2069</v>
       </c>
       <c r="C1165" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1165" s="122">
         <v>6838</v>
@@ -34611,7 +34186,7 @@
         <v>2070</v>
       </c>
       <c r="C1166" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1166" s="122">
         <v>2792</v>
@@ -34625,7 +34200,7 @@
         <v>2071</v>
       </c>
       <c r="C1167" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1167" s="122">
         <v>5250</v>
@@ -34639,7 +34214,7 @@
         <v>2072</v>
       </c>
       <c r="C1168" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1168" s="125">
         <v>3729</v>
@@ -34653,7 +34228,7 @@
         <v>2073</v>
       </c>
       <c r="C1169" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1169" s="122">
         <v>721</v>
@@ -34667,7 +34242,7 @@
         <v>2074</v>
       </c>
       <c r="C1170" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1170" s="122">
         <v>2311</v>
@@ -34681,7 +34256,7 @@
         <v>2075</v>
       </c>
       <c r="C1171" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1171" s="122">
         <v>11</v>
@@ -34695,7 +34270,7 @@
         <v>2076</v>
       </c>
       <c r="C1172" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1172" s="122">
         <v>4825</v>
@@ -34709,7 +34284,7 @@
         <v>2077</v>
       </c>
       <c r="C1173" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1173" s="122">
         <v>4821</v>
@@ -34723,7 +34298,7 @@
         <v>2078</v>
       </c>
       <c r="C1174" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1174" s="122">
         <v>4822</v>
@@ -34737,7 +34312,7 @@
         <v>2079</v>
       </c>
       <c r="C1175" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1175" s="122">
         <v>3339</v>
@@ -34751,7 +34326,7 @@
         <v>2080</v>
       </c>
       <c r="C1176" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1176" s="122">
         <v>3724</v>
@@ -34765,7 +34340,7 @@
         <v>2081</v>
       </c>
       <c r="C1177" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1177" s="122">
         <v>2389</v>
@@ -34779,7 +34354,7 @@
         <v>2082</v>
       </c>
       <c r="C1178" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1178" s="122">
         <v>2315</v>
@@ -34793,7 +34368,7 @@
         <v>2083</v>
       </c>
       <c r="C1179" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1179" s="122">
         <v>1055</v>
@@ -34807,7 +34382,7 @@
         <v>2084</v>
       </c>
       <c r="C1180" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1180" s="122">
         <v>2789</v>
@@ -34821,7 +34396,7 @@
         <v>2085</v>
       </c>
       <c r="C1181" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1181" s="122">
         <v>4835</v>
@@ -34835,7 +34410,7 @@
         <v>2086</v>
       </c>
       <c r="C1182" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1182" s="122">
         <v>4834</v>
@@ -34849,7 +34424,7 @@
         <v>2087</v>
       </c>
       <c r="C1183" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1183" s="122">
         <v>2303</v>
@@ -34863,7 +34438,7 @@
         <v>2088</v>
       </c>
       <c r="C1184" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1184" s="122">
         <v>4951</v>
@@ -34877,7 +34452,7 @@
         <v>2089</v>
       </c>
       <c r="C1185" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1185" s="122">
         <v>4952</v>
@@ -34891,7 +34466,7 @@
         <v>2090</v>
       </c>
       <c r="C1186" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1186" s="125">
         <v>2314</v>
@@ -34905,7 +34480,7 @@
         <v>2091</v>
       </c>
       <c r="C1187" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1187" s="122">
         <v>4409</v>
@@ -34919,7 +34494,7 @@
         <v>2092</v>
       </c>
       <c r="C1188" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1188" s="122">
         <v>3814</v>
@@ -34933,7 +34508,7 @@
         <v>2093</v>
       </c>
       <c r="C1189" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1189" s="122">
         <v>5171</v>
@@ -34947,7 +34522,7 @@
         <v>2094</v>
       </c>
       <c r="C1190" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1190" s="125">
         <v>3813</v>
@@ -34961,7 +34536,7 @@
         <v>2095</v>
       </c>
       <c r="C1191" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1191" s="122">
         <v>6233</v>
@@ -34975,7 +34550,7 @@
         <v>2096</v>
       </c>
       <c r="C1192" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1192" s="122">
         <v>7294</v>
@@ -34989,7 +34564,7 @@
         <v>2097</v>
       </c>
       <c r="C1193" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1193" s="122">
         <v>7258</v>
@@ -35003,7 +34578,7 @@
         <v>2098</v>
       </c>
       <c r="C1194" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1194" s="122">
         <v>6232</v>
@@ -35017,7 +34592,7 @@
         <v>2099</v>
       </c>
       <c r="C1195" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1195" s="122">
         <v>3815</v>
@@ -35031,7 +34606,7 @@
         <v>2100</v>
       </c>
       <c r="C1196" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1196" s="122">
         <v>3816</v>
@@ -35045,7 +34620,7 @@
         <v>2101</v>
       </c>
       <c r="C1197" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1197" s="122">
         <v>3817</v>
@@ -35059,7 +34634,7 @@
         <v>2102</v>
       </c>
       <c r="C1198" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1198" s="125">
         <v>4826</v>
@@ -35073,7 +34648,7 @@
         <v>2103</v>
       </c>
       <c r="C1199" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1199" s="122">
         <v>3100</v>
@@ -35087,7 +34662,7 @@
         <v>2104</v>
       </c>
       <c r="C1200" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1200" s="122">
         <v>3101</v>
@@ -35101,7 +34676,7 @@
         <v>2105</v>
       </c>
       <c r="C1201" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1201" s="123">
         <v>4805</v>
@@ -35115,7 +34690,7 @@
         <v>2106</v>
       </c>
       <c r="C1202" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1202" s="122">
         <v>776</v>
@@ -35129,7 +34704,7 @@
         <v>2107</v>
       </c>
       <c r="C1203" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1203" s="122">
         <v>2246</v>
@@ -35143,7 +34718,7 @@
         <v>2108</v>
       </c>
       <c r="C1204" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1204" s="122">
         <v>3826</v>
@@ -35157,7 +34732,7 @@
         <v>2109</v>
       </c>
       <c r="C1205" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1205" s="122">
         <v>3827</v>
@@ -35171,7 +34746,7 @@
         <v>2110</v>
       </c>
       <c r="C1206" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1206" s="122">
         <v>3828</v>
@@ -35185,7 +34760,7 @@
         <v>2111</v>
       </c>
       <c r="C1207" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1207" s="122">
         <v>3855</v>
@@ -35199,7 +34774,7 @@
         <v>2112</v>
       </c>
       <c r="C1208" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1208" s="122">
         <v>7270</v>
@@ -35213,7 +34788,7 @@
         <v>2113</v>
       </c>
       <c r="C1209" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1209" s="122">
         <v>344</v>
@@ -35227,7 +34802,7 @@
         <v>2114</v>
       </c>
       <c r="C1210" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1210" s="122">
         <v>2057</v>
@@ -35241,7 +34816,7 @@
         <v>2115</v>
       </c>
       <c r="C1211" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1211" s="122">
         <v>204</v>
@@ -35255,7 +34830,7 @@
         <v>2116</v>
       </c>
       <c r="C1212" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1212" s="122">
         <v>3338</v>
@@ -35269,7 +34844,7 @@
         <v>2117</v>
       </c>
       <c r="C1213" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1213" s="123">
         <v>2793</v>
@@ -35283,7 +34858,7 @@
         <v>2118</v>
       </c>
       <c r="C1214" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1214" s="122">
         <v>4234</v>
@@ -35297,7 +34872,7 @@
         <v>2119</v>
       </c>
       <c r="C1215" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1215" s="122">
         <v>4605</v>
@@ -35311,7 +34886,7 @@
         <v>2120</v>
       </c>
       <c r="C1216" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1216" s="122">
         <v>2652</v>
@@ -35325,7 +34900,7 @@
         <v>2121</v>
       </c>
       <c r="C1217" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1217" s="122">
         <v>6810</v>
@@ -35339,7 +34914,7 @@
         <v>2122</v>
       </c>
       <c r="C1218" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1218" s="122">
         <v>2747</v>
@@ -35353,7 +34928,7 @@
         <v>2123</v>
       </c>
       <c r="C1219" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1219" s="122">
         <v>2787</v>
@@ -35367,7 +34942,7 @@
         <v>2124</v>
       </c>
       <c r="C1220" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1220" s="122">
         <v>2788</v>
@@ -35381,7 +34956,7 @@
         <v>2125</v>
       </c>
       <c r="C1221" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1221" s="130">
         <v>3134</v>
@@ -35395,7 +34970,7 @@
         <v>2126</v>
       </c>
       <c r="C1222" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1222" s="122">
         <v>3416</v>
@@ -35409,7 +34984,7 @@
         <v>2127</v>
       </c>
       <c r="C1223" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1223" s="122">
         <v>645</v>
@@ -35423,7 +34998,7 @@
         <v>2128</v>
       </c>
       <c r="C1224" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1224" s="122">
         <v>6302</v>
@@ -35437,7 +35012,7 @@
         <v>2129</v>
       </c>
       <c r="C1225" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1225" s="122">
         <v>237</v>
@@ -35451,7 +35026,7 @@
         <v>2130</v>
       </c>
       <c r="C1226" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1226" s="122">
         <v>346</v>
@@ -35465,7 +35040,7 @@
         <v>2131</v>
       </c>
       <c r="C1227" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1227" s="122">
         <v>3130</v>
@@ -35479,7 +35054,7 @@
         <v>2132</v>
       </c>
       <c r="C1228" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1228" s="122">
         <v>2306</v>
@@ -35493,7 +35068,7 @@
         <v>2133</v>
       </c>
       <c r="C1229" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1229" s="122">
         <v>806</v>
@@ -35507,7 +35082,7 @@
         <v>2134</v>
       </c>
       <c r="C1230" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1230" s="122">
         <v>916</v>
@@ -35521,7 +35096,7 @@
         <v>2135</v>
       </c>
       <c r="C1231" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1231" s="122">
         <v>2510</v>
@@ -35535,7 +35110,7 @@
         <v>2136</v>
       </c>
       <c r="C1232" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1232" s="122">
         <v>2313</v>
@@ -35549,7 +35124,7 @@
         <v>2137</v>
       </c>
       <c r="C1233" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1233" s="122">
         <v>982</v>
@@ -35563,7 +35138,7 @@
         <v>2138</v>
       </c>
       <c r="C1234" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1234" s="122">
         <v>1054</v>
@@ -35577,7 +35152,7 @@
         <v>2139</v>
       </c>
       <c r="C1235" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1235" s="122">
         <v>3129</v>
@@ -35591,7 +35166,7 @@
         <v>2140</v>
       </c>
       <c r="C1236" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1236" s="122">
         <v>2748</v>
@@ -35605,7 +35180,7 @@
         <v>2141</v>
       </c>
       <c r="C1237" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1237" s="123">
         <v>4806</v>
@@ -35619,7 +35194,7 @@
         <v>2142</v>
       </c>
       <c r="C1238" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1238" s="122">
         <v>2107</v>
@@ -35633,7 +35208,7 @@
         <v>2143</v>
       </c>
       <c r="C1239" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1239" s="122">
         <v>2109</v>
@@ -35647,7 +35222,7 @@
         <v>2144</v>
       </c>
       <c r="C1240" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1240" s="122">
         <v>2110</v>
@@ -35661,7 +35236,7 @@
         <v>2145</v>
       </c>
       <c r="C1241" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1241" s="122">
         <v>2111</v>
@@ -35675,7 +35250,7 @@
         <v>2146</v>
       </c>
       <c r="C1242" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1242" s="122">
         <v>2112</v>
@@ -35689,7 +35264,7 @@
         <v>2147</v>
       </c>
       <c r="C1243" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1243" s="122">
         <v>2113</v>
@@ -35703,7 +35278,7 @@
         <v>2148</v>
       </c>
       <c r="C1244" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1244" s="122">
         <v>2114</v>
@@ -35717,7 +35292,7 @@
         <v>2149</v>
       </c>
       <c r="C1245" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1245" s="122">
         <v>2115</v>
@@ -35731,7 +35306,7 @@
         <v>2150</v>
       </c>
       <c r="C1246" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1246" s="122">
         <v>2116</v>
@@ -35745,7 +35320,7 @@
         <v>2151</v>
       </c>
       <c r="C1247" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1247" s="123">
         <v>2117</v>
@@ -35759,7 +35334,7 @@
         <v>2152</v>
       </c>
       <c r="C1248" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1248" s="122">
         <v>2118</v>
@@ -35773,7 +35348,7 @@
         <v>2153</v>
       </c>
       <c r="C1249" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1249" s="122">
         <v>2119</v>
@@ -35787,7 +35362,7 @@
         <v>2154</v>
       </c>
       <c r="C1250" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1250" s="122">
         <v>2120</v>
@@ -35801,7 +35376,7 @@
         <v>2155</v>
       </c>
       <c r="C1251" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1251" s="123">
         <v>2122</v>
@@ -35815,7 +35390,7 @@
         <v>2156</v>
       </c>
       <c r="C1252" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1252" s="122">
         <v>2123</v>
@@ -35829,7 +35404,7 @@
         <v>2157</v>
       </c>
       <c r="C1253" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1253" s="123">
         <v>2608</v>
@@ -35843,7 +35418,7 @@
         <v>2158</v>
       </c>
       <c r="C1254" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1254" s="122">
         <v>2611</v>
@@ -35857,7 +35432,7 @@
         <v>2159</v>
       </c>
       <c r="C1255" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1255" s="122">
         <v>2613</v>
@@ -35871,7 +35446,7 @@
         <v>2160</v>
       </c>
       <c r="C1256" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1256" s="122">
         <v>6250</v>
@@ -35885,7 +35460,7 @@
         <v>2161</v>
       </c>
       <c r="C1257" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1257" s="122">
         <v>2304</v>
@@ -35899,7 +35474,7 @@
         <v>2162</v>
       </c>
       <c r="C1258" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1258" s="122">
         <v>2619</v>
@@ -35913,7 +35488,7 @@
         <v>2163</v>
       </c>
       <c r="C1259" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1259" s="122">
         <v>2219</v>
@@ -35927,7 +35502,7 @@
         <v>2164</v>
       </c>
       <c r="C1260" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1260" s="122">
         <v>2220</v>
@@ -35941,7 +35516,7 @@
         <v>2165</v>
       </c>
       <c r="C1261" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1261" s="122">
         <v>2221</v>
@@ -35955,7 +35530,7 @@
         <v>2166</v>
       </c>
       <c r="C1262" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1262" s="122">
         <v>2429</v>
@@ -35969,7 +35544,7 @@
         <v>2167</v>
       </c>
       <c r="C1263" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1263" s="122">
         <v>3421</v>
@@ -35983,7 +35558,7 @@
         <v>2168</v>
       </c>
       <c r="C1264" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1264" s="122">
         <v>3315</v>
@@ -35997,7 +35572,7 @@
         <v>2169</v>
       </c>
       <c r="C1265" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1265" s="122">
         <v>2307</v>
@@ -36011,7 +35586,7 @@
         <v>2170</v>
       </c>
       <c r="C1266" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1266" s="122">
         <v>2106</v>
@@ -36025,7 +35600,7 @@
         <v>2171</v>
       </c>
       <c r="C1267" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1267" s="125">
         <v>2308</v>
@@ -36039,7 +35614,7 @@
         <v>2172</v>
       </c>
       <c r="C1268" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1268" s="122">
         <v>3378</v>
@@ -36053,7 +35628,7 @@
         <v>2173</v>
       </c>
       <c r="C1269" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1269" s="122">
         <v>241</v>
@@ -36067,7 +35642,7 @@
         <v>2174</v>
       </c>
       <c r="C1270" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1270" s="122">
         <v>242</v>
@@ -36081,7 +35656,7 @@
         <v>2175</v>
       </c>
       <c r="C1271" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1271" s="122">
         <v>1047</v>
@@ -36095,7 +35670,7 @@
         <v>2176</v>
       </c>
       <c r="C1272" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1272" s="135">
         <v>5212</v>
@@ -36109,7 +35684,7 @@
         <v>2177</v>
       </c>
       <c r="C1273" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1273" s="136">
         <v>1056</v>
@@ -36123,7 +35698,7 @@
         <v>2178</v>
       </c>
       <c r="C1274" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1274" s="122">
         <v>3422</v>
@@ -36137,7 +35712,7 @@
         <v>2179</v>
       </c>
       <c r="C1275" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1275" s="122">
         <v>3803</v>
@@ -36151,7 +35726,7 @@
         <v>2180</v>
       </c>
       <c r="C1276" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1276" s="122">
         <v>5041</v>
@@ -36165,7 +35740,7 @@
         <v>2181</v>
       </c>
       <c r="C1277" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1277" s="122">
         <v>5213</v>
@@ -36179,7 +35754,7 @@
         <v>2182</v>
       </c>
       <c r="C1278" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1278" s="122">
         <v>3094</v>
@@ -36193,7 +35768,7 @@
         <v>2183</v>
       </c>
       <c r="C1279" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1279" s="122">
         <v>2534</v>
@@ -36207,7 +35782,7 @@
         <v>2184</v>
       </c>
       <c r="C1280" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1280" s="122">
         <v>4413</v>
@@ -36221,7 +35796,7 @@
         <v>2185</v>
       </c>
       <c r="C1281" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1281" s="122">
         <v>4232</v>
@@ -36235,7 +35810,7 @@
         <v>2186</v>
       </c>
       <c r="C1282" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1282" s="122">
         <v>4231</v>
@@ -36249,7 +35824,7 @@
         <v>2187</v>
       </c>
       <c r="C1283" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1283" s="123">
         <v>4237</v>
@@ -36263,7 +35838,7 @@
         <v>2188</v>
       </c>
       <c r="C1284" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1284" s="122">
         <v>5158</v>
@@ -36277,7 +35852,7 @@
         <v>2189</v>
       </c>
       <c r="C1285" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="D1285" s="122">
         <v>2479</v>
@@ -37336,7 +36911,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="1361" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1361" s="1">
         <v>1362</v>
       </c>
@@ -37350,7 +36925,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="1362" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1362" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1362" s="1">
         <v>1363</v>
       </c>
@@ -37364,7 +36939,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="1363" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1363" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1363" s="1">
         <v>1364</v>
       </c>
@@ -37378,7 +36953,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="1364" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1364" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1364" s="1">
         <v>1365</v>
       </c>
@@ -37391,8 +36966,11 @@
       <c r="D1364" s="126" t="s">
         <v>2349</v>
       </c>
-    </row>
-    <row r="1365" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1364" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1365" s="1">
         <v>1366</v>
       </c>
@@ -37405,8 +36983,11 @@
       <c r="D1365" s="126" t="s">
         <v>2348</v>
       </c>
-    </row>
-    <row r="1366" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1365" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1366" s="1">
         <v>1367</v>
       </c>
@@ -37419,8 +37000,11 @@
       <c r="D1366" s="126" t="s">
         <v>2356</v>
       </c>
-    </row>
-    <row r="1367" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1366" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1367" s="1">
         <v>1368</v>
       </c>
@@ -37433,8 +37017,11 @@
       <c r="D1367" s="126" t="s">
         <v>2357</v>
       </c>
-    </row>
-    <row r="1368" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1367" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1368" s="1">
         <v>1369</v>
       </c>
@@ -37447,8 +37034,11 @@
       <c r="D1368" s="126" t="s">
         <v>2358</v>
       </c>
-    </row>
-    <row r="1369" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1368" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1369" s="1">
         <v>1370</v>
       </c>
@@ -37461,8 +37051,11 @@
       <c r="D1369" s="126" t="s">
         <v>2359</v>
       </c>
-    </row>
-    <row r="1370" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1369" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1370" s="1">
         <v>1371</v>
       </c>
@@ -37475,8 +37068,11 @@
       <c r="D1370" s="126" t="s">
         <v>2360</v>
       </c>
-    </row>
-    <row r="1371" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1370" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1371" s="1">
         <v>1372</v>
       </c>
@@ -37489,8 +37085,11 @@
       <c r="D1371" s="126" t="s">
         <v>2361</v>
       </c>
-    </row>
-    <row r="1372" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1371" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1372" s="1">
         <v>1373</v>
       </c>
@@ -37503,8 +37102,11 @@
       <c r="D1372" s="126" t="s">
         <v>2371</v>
       </c>
-    </row>
-    <row r="1373" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1372" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1373" s="1">
         <v>1374</v>
       </c>
@@ -37517,8 +37119,11 @@
       <c r="D1373" s="126" t="s">
         <v>2372</v>
       </c>
-    </row>
-    <row r="1374" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1373" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1374" s="1">
         <v>1375</v>
       </c>
@@ -37531,8 +37136,11 @@
       <c r="D1374" s="126" t="s">
         <v>2373</v>
       </c>
-    </row>
-    <row r="1375" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1374" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1375" s="1">
         <v>1376</v>
       </c>
@@ -37545,8 +37153,11 @@
       <c r="D1375" s="126" t="s">
         <v>2374</v>
       </c>
-    </row>
-    <row r="1376" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1375" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1376" s="1">
         <v>1377</v>
       </c>
@@ -37559,8 +37170,11 @@
       <c r="D1376" s="126" t="s">
         <v>2375</v>
       </c>
-    </row>
-    <row r="1377" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1376" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1377" s="1">
         <v>1378</v>
       </c>
@@ -37573,8 +37187,11 @@
       <c r="D1377" s="126" t="s">
         <v>2376</v>
       </c>
-    </row>
-    <row r="1378" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1377" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1378" s="1">
         <v>1379</v>
       </c>
@@ -37587,8 +37204,11 @@
       <c r="D1378" s="126" t="s">
         <v>2377</v>
       </c>
-    </row>
-    <row r="1379" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1378" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1379" s="1">
         <v>1380</v>
       </c>
@@ -37601,8 +37221,11 @@
       <c r="D1379" s="126" t="s">
         <v>2378</v>
       </c>
-    </row>
-    <row r="1380" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1379" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1380" s="1">
         <v>1381</v>
       </c>
@@ -37615,8 +37238,11 @@
       <c r="D1380" s="126" t="s">
         <v>2379</v>
       </c>
-    </row>
-    <row r="1381" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1380" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1381" s="1">
         <v>1382</v>
       </c>
@@ -37629,8 +37255,11 @@
       <c r="D1381" s="126" t="s">
         <v>2389</v>
       </c>
-    </row>
-    <row r="1382" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1381" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1382" s="1">
         <v>1383</v>
       </c>
@@ -37643,8 +37272,11 @@
       <c r="D1382" s="126" t="s">
         <v>2390</v>
       </c>
-    </row>
-    <row r="1383" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1382" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1383" s="1">
         <v>1384</v>
       </c>
@@ -37657,8 +37289,11 @@
       <c r="D1383" s="126" t="s">
         <v>2391</v>
       </c>
-    </row>
-    <row r="1384" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1383" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1384" s="1">
         <v>1385</v>
       </c>
@@ -37671,8 +37306,11 @@
       <c r="D1384" s="126" t="s">
         <v>2392</v>
       </c>
-    </row>
-    <row r="1385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1384" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1385" s="1">
         <v>1386</v>
       </c>
@@ -37685,8 +37323,11 @@
       <c r="D1385" s="126" t="s">
         <v>2393</v>
       </c>
-    </row>
-    <row r="1386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1385" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1386" s="1">
         <v>1387</v>
       </c>
@@ -37699,8 +37340,11 @@
       <c r="D1386" s="126" t="s">
         <v>2394</v>
       </c>
-    </row>
-    <row r="1387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1386" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1387" s="1">
         <v>1388</v>
       </c>
@@ -37713,8 +37357,11 @@
       <c r="D1387" s="126" t="s">
         <v>2395</v>
       </c>
-    </row>
-    <row r="1388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1387" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1388" s="1">
         <v>1389</v>
       </c>
@@ -37727,8 +37374,11 @@
       <c r="D1388" s="126" t="s">
         <v>2396</v>
       </c>
-    </row>
-    <row r="1389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1388" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1389" s="1">
         <v>1390</v>
       </c>
@@ -37741,8 +37391,11 @@
       <c r="D1389" s="126" t="s">
         <v>2397</v>
       </c>
-    </row>
-    <row r="1390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F1389" s="1" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1390" s="1">
         <v>1391</v>
       </c>
@@ -37756,7 +37409,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="1391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1391" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1391" s="1">
         <v>1392</v>
       </c>
@@ -37770,7 +37423,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="1392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1392" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1392" s="1">
         <v>1393</v>
       </c>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 10\Desktop\Pagina distri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE0ACAD-6D29-4B58-B355-5CB8F98F1FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC212DA-F115-497B-AF13-36B95F1A2734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="345" windowWidth="9945" windowHeight="10515" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -13700,7 +13700,9 @@
       <c r="D2" s="126">
         <v>6604.3</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
       <c r="F2" s="34" t="s">
         <v>1396</v>
       </c>
@@ -13724,7 +13726,9 @@
       <c r="D3" s="126">
         <v>3764.6</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
       <c r="F3" s="34" t="s">
         <v>1396</v>
       </c>
@@ -13748,7 +13752,9 @@
       <c r="D4" s="126">
         <v>7241.9</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2">
+        <v>100</v>
+      </c>
       <c r="F4" s="34" t="s">
         <v>1398</v>
       </c>
@@ -13772,7 +13778,9 @@
       <c r="D5" s="126">
         <v>4121</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="2">
+        <v>100</v>
+      </c>
       <c r="F5" s="34" t="s">
         <v>1396</v>
       </c>
@@ -13796,7 +13804,9 @@
       <c r="D6" s="126">
         <v>1036.7</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <v>100</v>
+      </c>
       <c r="F6" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13821,7 +13831,9 @@
       <c r="D7" s="126">
         <v>5192.3999999999996</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <v>100</v>
+      </c>
       <c r="F7" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13846,7 +13858,9 @@
       <c r="D8" s="126">
         <v>3285.6</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2">
+        <v>100</v>
+      </c>
       <c r="F8" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13871,7 +13885,9 @@
       <c r="D9" s="126">
         <v>877.8</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>100</v>
+      </c>
       <c r="F9" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13896,7 +13912,9 @@
       <c r="D10" s="126">
         <v>1369.4</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="2">
+        <v>100</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13921,7 +13939,9 @@
       <c r="D11" s="127">
         <v>1234.3</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2">
+        <v>100</v>
+      </c>
       <c r="F11" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13946,7 +13966,9 @@
       <c r="D12" s="126">
         <v>2196</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2">
+        <v>100</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13971,7 +13993,9 @@
       <c r="D13" s="126">
         <v>3728.3</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="2">
+        <v>100</v>
+      </c>
       <c r="F13" s="2" t="s">
         <v>1544</v>
       </c>
@@ -13996,7 +14020,9 @@
       <c r="D14" s="126">
         <v>10323.5</v>
       </c>
-      <c r="E14" s="45"/>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
       <c r="F14" s="34" t="s">
         <v>1396</v>
       </c>
@@ -14021,7 +14047,9 @@
       <c r="D15" s="126">
         <v>1787.6</v>
       </c>
-      <c r="E15" s="46"/>
+      <c r="E15" s="2">
+        <v>100</v>
+      </c>
       <c r="F15" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14046,7 +14074,9 @@
       <c r="D16" s="126">
         <v>1072.4000000000001</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2">
+        <v>100</v>
+      </c>
       <c r="F16" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14071,7 +14101,9 @@
       <c r="D17" s="126">
         <v>1294.8</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2">
+        <v>100</v>
+      </c>
       <c r="F17" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14096,7 +14128,9 @@
       <c r="D18" s="126">
         <v>1738</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="2">
+        <v>100</v>
+      </c>
       <c r="F18" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14121,7 +14155,9 @@
       <c r="D19" s="126">
         <v>2723.9</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="2">
+        <v>100</v>
+      </c>
       <c r="F19" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14146,7 +14182,9 @@
       <c r="D20" s="126">
         <v>2723.9</v>
       </c>
-      <c r="E20" s="47"/>
+      <c r="E20" s="2">
+        <v>100</v>
+      </c>
       <c r="F20" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14171,7 +14209,9 @@
       <c r="D21" s="126">
         <v>5107.2</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2">
+        <v>100</v>
+      </c>
       <c r="F21" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14196,7 +14236,9 @@
       <c r="D22" s="126">
         <v>6060.6</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2">
+        <v>100</v>
+      </c>
       <c r="F22" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14221,7 +14263,9 @@
       <c r="D23" s="126">
         <v>5277.5</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="2">
+        <v>100</v>
+      </c>
       <c r="F23" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14246,7 +14290,9 @@
       <c r="D24" s="127">
         <v>3217.3</v>
       </c>
-      <c r="E24" s="6"/>
+      <c r="E24" s="2">
+        <v>100</v>
+      </c>
       <c r="F24" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14271,7 +14317,9 @@
       <c r="D25" s="128">
         <v>3511.2</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="2">
+        <v>100</v>
+      </c>
       <c r="F25" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14296,7 +14344,9 @@
       <c r="D26" s="126">
         <v>5022.1000000000004</v>
       </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2">
+        <v>100</v>
+      </c>
       <c r="F26" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14321,7 +14371,9 @@
       <c r="D27" s="126">
         <v>4564.6000000000004</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2">
+        <v>100</v>
+      </c>
       <c r="F27" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14346,7 +14398,9 @@
       <c r="D28" s="126">
         <v>468</v>
       </c>
-      <c r="E28" s="2"/>
+      <c r="E28" s="2">
+        <v>100</v>
+      </c>
       <c r="F28" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14371,7 +14425,9 @@
       <c r="D29" s="126">
         <v>260</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" s="2">
+        <v>100</v>
+      </c>
       <c r="F29" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14396,7 +14452,9 @@
       <c r="D30" s="127">
         <v>5969.1</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2">
+        <v>100</v>
+      </c>
       <c r="F30" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14422,7 +14480,9 @@
       <c r="D31" s="126">
         <v>4936.6000000000004</v>
       </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="2">
+        <v>100</v>
+      </c>
       <c r="F31" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14447,7 +14507,9 @@
       <c r="D32" s="126">
         <v>5400</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2">
+        <v>100</v>
+      </c>
       <c r="F32" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14472,7 +14534,9 @@
       <c r="D33" s="126">
         <v>5400</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2">
+        <v>100</v>
+      </c>
       <c r="F33" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14497,7 +14561,9 @@
       <c r="D34" s="126">
         <v>5400</v>
       </c>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2">
+        <v>100</v>
+      </c>
       <c r="F34" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14522,7 +14588,9 @@
       <c r="D35" s="128">
         <v>4915.7</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" s="2">
+        <v>100</v>
+      </c>
       <c r="F35" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14547,7 +14615,9 @@
       <c r="D36" s="128">
         <v>546.9</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" s="2">
+        <v>100</v>
+      </c>
       <c r="F36" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14572,7 +14642,9 @@
       <c r="D37" s="126">
         <v>2274.3000000000002</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" s="2">
+        <v>100</v>
+      </c>
       <c r="F37" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14597,7 +14669,9 @@
       <c r="D38" s="126">
         <v>7660.8</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" s="2">
+        <v>100</v>
+      </c>
       <c r="F38" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14622,7 +14696,9 @@
       <c r="D39" s="126">
         <v>1327.9</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2">
+        <v>100</v>
+      </c>
       <c r="F39" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14645,7 +14721,9 @@
       <c r="D40" s="127">
         <v>2723.9</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" s="2">
+        <v>100</v>
+      </c>
       <c r="F40" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14668,7 +14746,9 @@
       <c r="D41" s="128">
         <v>5107.3</v>
       </c>
-      <c r="E41" s="2"/>
+      <c r="E41" s="2">
+        <v>100</v>
+      </c>
       <c r="F41" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14691,7 +14771,9 @@
       <c r="D42" s="126">
         <v>11916.8</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" s="2">
+        <v>100</v>
+      </c>
       <c r="F42" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14714,7 +14796,9 @@
       <c r="D43" s="127">
         <v>12113.7</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2">
+        <v>100</v>
+      </c>
       <c r="F43" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14737,7 +14821,9 @@
       <c r="D44" s="126">
         <v>1957.7</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2">
+        <v>100</v>
+      </c>
       <c r="F44" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14762,7 +14848,9 @@
       <c r="D45" s="126">
         <v>3288</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2">
+        <v>100</v>
+      </c>
       <c r="F45" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14787,7 +14875,9 @@
       <c r="D46" s="126">
         <v>4697.1000000000004</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" s="2">
+        <v>100</v>
+      </c>
       <c r="F46" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14812,7 +14902,9 @@
       <c r="D47" s="126">
         <v>6144.6</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" s="2">
+        <v>100</v>
+      </c>
       <c r="F47" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14837,7 +14929,9 @@
       <c r="D48" s="127">
         <v>1276.8</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" s="2">
+        <v>100</v>
+      </c>
       <c r="F48" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14862,7 +14956,9 @@
       <c r="D49" s="127">
         <v>93016.4</v>
       </c>
-      <c r="E49" s="125"/>
+      <c r="E49" s="2">
+        <v>100</v>
+      </c>
       <c r="F49" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14887,7 +14983,9 @@
       <c r="D50" s="128">
         <v>2908.4</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" s="2">
+        <v>100</v>
+      </c>
       <c r="F50" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14912,7 +15010,9 @@
       <c r="D51" s="127">
         <v>12113.7</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="2">
+        <v>100</v>
+      </c>
       <c r="F51" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14937,7 +15037,9 @@
       <c r="D52" s="127">
         <v>40558.400000000001</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" s="2">
+        <v>100</v>
+      </c>
       <c r="F52" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14962,7 +15064,9 @@
       <c r="D53" s="127">
         <v>3724</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" s="2">
+        <v>100</v>
+      </c>
       <c r="F53" s="34" t="s">
         <v>1544</v>
       </c>
@@ -14987,7 +15091,9 @@
       <c r="D54" s="127">
         <v>1997.9</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" s="2">
+        <v>100</v>
+      </c>
       <c r="F54" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15013,7 +15119,9 @@
       <c r="D55" s="127">
         <v>1323</v>
       </c>
-      <c r="E55" s="2"/>
+      <c r="E55" s="2">
+        <v>100</v>
+      </c>
       <c r="F55" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15038,7 +15146,9 @@
       <c r="D56" s="127">
         <v>4123</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" s="2">
+        <v>100</v>
+      </c>
       <c r="F56" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15063,7 +15173,9 @@
       <c r="D57" s="127">
         <v>4752</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" s="2">
+        <v>100</v>
+      </c>
       <c r="F57" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15088,7 +15200,9 @@
       <c r="D58" s="127">
         <v>7128</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" s="2">
+        <v>100</v>
+      </c>
       <c r="F58" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15113,7 +15227,9 @@
       <c r="D59" s="127">
         <v>16158.9</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" s="2">
+        <v>100</v>
+      </c>
       <c r="F59" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15138,7 +15254,9 @@
       <c r="D60" s="127">
         <v>11587</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" s="2">
+        <v>100</v>
+      </c>
       <c r="F60" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15163,7 +15281,9 @@
       <c r="D61" s="127">
         <v>5107.3</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" s="2">
+        <v>100</v>
+      </c>
       <c r="F61" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15188,7 +15308,9 @@
       <c r="D62" s="127">
         <v>5958.5</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" s="2">
+        <v>100</v>
+      </c>
       <c r="F62" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15213,7 +15335,9 @@
       <c r="D63" s="127">
         <v>1702.4</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" s="2">
+        <v>100</v>
+      </c>
       <c r="F63" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15238,7 +15362,9 @@
       <c r="D64" s="127">
         <v>1787.4</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" s="2">
+        <v>100</v>
+      </c>
       <c r="F64" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15263,7 +15389,9 @@
       <c r="D65" s="127">
         <v>4980</v>
       </c>
-      <c r="E65" s="2"/>
+      <c r="E65" s="2">
+        <v>100</v>
+      </c>
       <c r="F65" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15288,7 +15416,9 @@
       <c r="D66" s="127">
         <v>1191.7</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" s="2">
+        <v>100</v>
+      </c>
       <c r="F66" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15313,7 +15443,9 @@
       <c r="D67" s="127">
         <v>3072.3</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" s="2">
+        <v>100</v>
+      </c>
       <c r="F67" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15338,7 +15470,9 @@
       <c r="D68" s="127">
         <v>5915.9</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" s="2">
+        <v>100</v>
+      </c>
       <c r="F68" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15363,7 +15497,9 @@
       <c r="D69" s="127">
         <v>6285.3</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" s="2">
+        <v>100</v>
+      </c>
       <c r="F69" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15388,7 +15524,9 @@
       <c r="D70" s="127">
         <v>3796.4</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" s="2">
+        <v>100</v>
+      </c>
       <c r="F70" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15413,7 +15551,9 @@
       <c r="D71" s="127">
         <v>1617.3</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" s="2">
+        <v>100</v>
+      </c>
       <c r="F71" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15438,7 +15578,9 @@
       <c r="D72" s="127">
         <v>2128</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" s="2">
+        <v>100</v>
+      </c>
       <c r="F72" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15463,7 +15605,9 @@
       <c r="D73" s="127">
         <v>8922.7999999999993</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" s="2">
+        <v>100</v>
+      </c>
       <c r="F73" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15488,7 +15632,9 @@
       <c r="D74" s="127">
         <v>972.3</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" s="2">
+        <v>100</v>
+      </c>
       <c r="F74" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15514,7 +15660,9 @@
       <c r="D75" s="127">
         <v>1130.5</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" s="2">
+        <v>100</v>
+      </c>
       <c r="F75" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15539,7 +15687,9 @@
       <c r="D76" s="127">
         <v>1936.5</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" s="2">
+        <v>100</v>
+      </c>
       <c r="F76" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15562,7 +15712,9 @@
       <c r="D77" s="127">
         <v>2195.1999999999998</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" s="2">
+        <v>100</v>
+      </c>
       <c r="F77" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15587,7 +15739,9 @@
       <c r="D78" s="127">
         <v>3575.1</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="2">
+        <v>100</v>
+      </c>
       <c r="F78" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15612,7 +15766,9 @@
       <c r="D79" s="127">
         <v>1536.2</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" s="2">
+        <v>100</v>
+      </c>
       <c r="F79" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15637,7 +15793,9 @@
       <c r="D80" s="128">
         <v>2169.3000000000002</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" s="2">
+        <v>100</v>
+      </c>
       <c r="F80" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15662,7 +15820,9 @@
       <c r="D81" s="128">
         <v>2633.4</v>
       </c>
-      <c r="E81" s="2"/>
+      <c r="E81" s="2">
+        <v>100</v>
+      </c>
       <c r="F81" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15687,7 +15847,9 @@
       <c r="D82" s="127">
         <v>695.9</v>
       </c>
-      <c r="E82" s="2"/>
+      <c r="E82" s="2">
+        <v>100</v>
+      </c>
       <c r="F82" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15712,7 +15874,9 @@
       <c r="D83" s="127">
         <v>15186.4</v>
       </c>
-      <c r="E83" s="2"/>
+      <c r="E83" s="2">
+        <v>100</v>
+      </c>
       <c r="F83" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15737,7 +15901,9 @@
       <c r="D84" s="127">
         <v>10044.200000000001</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" s="2">
+        <v>100</v>
+      </c>
       <c r="F84" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15762,7 +15928,9 @@
       <c r="D85" s="127">
         <v>4564.6000000000004</v>
       </c>
-      <c r="E85" s="2"/>
+      <c r="E85" s="2">
+        <v>100</v>
+      </c>
       <c r="F85" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15787,7 +15955,9 @@
       <c r="D86" s="127">
         <v>5442.4</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" s="2">
+        <v>100</v>
+      </c>
       <c r="F86" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15812,7 +15982,9 @@
       <c r="D87" s="127">
         <v>6320.2</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" s="2">
+        <v>100</v>
+      </c>
       <c r="F87" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15837,7 +16009,9 @@
       <c r="D88" s="127">
         <v>7022.4</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" s="2">
+        <v>100</v>
+      </c>
       <c r="F88" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15862,7 +16036,9 @@
       <c r="D89" s="127">
         <v>3423.5</v>
       </c>
-      <c r="E89" s="2"/>
+      <c r="E89" s="2">
+        <v>100</v>
+      </c>
       <c r="F89" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15887,7 +16063,9 @@
       <c r="D90" s="127">
         <v>1447.1</v>
       </c>
-      <c r="E90" s="2"/>
+      <c r="E90" s="2">
+        <v>100</v>
+      </c>
       <c r="F90" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15912,7 +16090,9 @@
       <c r="D91" s="127">
         <v>2511.1</v>
       </c>
-      <c r="E91" s="2"/>
+      <c r="E91" s="2">
+        <v>100</v>
+      </c>
       <c r="F91" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15937,7 +16117,9 @@
       <c r="D92" s="127">
         <v>6128.8</v>
       </c>
-      <c r="E92" s="2"/>
+      <c r="E92" s="2">
+        <v>100</v>
+      </c>
       <c r="F92" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15962,7 +16144,9 @@
       <c r="D93" s="127">
         <v>1281.5999999999999</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E93" s="2">
+        <v>100</v>
+      </c>
       <c r="F93" s="34" t="s">
         <v>1544</v>
       </c>
@@ -15987,7 +16171,9 @@
       <c r="D94" s="127">
         <v>3234.6</v>
       </c>
-      <c r="E94" s="2"/>
+      <c r="E94" s="2">
+        <v>100</v>
+      </c>
       <c r="F94" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16012,7 +16198,9 @@
       <c r="D95" s="127">
         <v>2475.4</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" s="2">
+        <v>100</v>
+      </c>
       <c r="F95" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16037,7 +16225,9 @@
       <c r="D96" s="126">
         <v>3212.8</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" s="2">
+        <v>100</v>
+      </c>
       <c r="F96" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16062,7 +16252,9 @@
       <c r="D97" s="126">
         <v>4562.5</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" s="2">
+        <v>100</v>
+      </c>
       <c r="F97" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16087,7 +16279,9 @@
       <c r="D98" s="129">
         <v>5958.4</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" s="2">
+        <v>100</v>
+      </c>
       <c r="F98" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16112,7 +16306,9 @@
       <c r="D99" s="126">
         <v>1957.8</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" s="2">
+        <v>100</v>
+      </c>
       <c r="F99" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16137,7 +16333,9 @@
       <c r="D100" s="127">
         <v>3192</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" s="2">
+        <v>100</v>
+      </c>
       <c r="F100" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16162,7 +16360,9 @@
       <c r="D101" s="126">
         <v>22301.8</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" s="2">
+        <v>100</v>
+      </c>
       <c r="F101" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16187,7 +16387,9 @@
       <c r="D102" s="127">
         <v>1578.2</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" s="2">
+        <v>100</v>
+      </c>
       <c r="F102" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16212,7 +16414,9 @@
       <c r="D103" s="128">
         <v>34899.199999999997</v>
       </c>
-      <c r="E103" s="2"/>
+      <c r="E103" s="2">
+        <v>100</v>
+      </c>
       <c r="F103" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16237,7 +16441,9 @@
       <c r="D104" s="126">
         <v>747.9</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" s="2">
+        <v>100</v>
+      </c>
       <c r="F104" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16264,7 +16470,9 @@
       <c r="D105" s="126">
         <v>10469.799999999999</v>
       </c>
-      <c r="E105" s="2"/>
+      <c r="E105" s="2">
+        <v>100</v>
+      </c>
       <c r="F105" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16289,7 +16497,9 @@
       <c r="D106" s="126">
         <v>12087.2</v>
       </c>
-      <c r="E106" s="2"/>
+      <c r="E106" s="2">
+        <v>100</v>
+      </c>
       <c r="F106" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16314,7 +16524,9 @@
       <c r="D107" s="126">
         <v>17024</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" s="2">
+        <v>100</v>
+      </c>
       <c r="F107" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16339,7 +16551,9 @@
       <c r="D108" s="126">
         <v>1895.3</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" s="2">
+        <v>100</v>
+      </c>
       <c r="F108" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16364,7 +16578,9 @@
       <c r="D109" s="126">
         <v>1895.3</v>
       </c>
-      <c r="E109" s="2"/>
+      <c r="E109" s="2">
+        <v>100</v>
+      </c>
       <c r="F109" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16389,7 +16605,9 @@
       <c r="D110" s="126">
         <v>544.79999999999995</v>
       </c>
-      <c r="E110" s="2"/>
+      <c r="E110" s="2">
+        <v>100</v>
+      </c>
       <c r="F110" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16414,7 +16632,9 @@
       <c r="D111" s="126">
         <v>885.2</v>
       </c>
-      <c r="E111" s="2"/>
+      <c r="E111" s="2">
+        <v>100</v>
+      </c>
       <c r="F111" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16439,7 +16659,9 @@
       <c r="D112" s="126">
         <v>3089.9</v>
       </c>
-      <c r="E112" s="2"/>
+      <c r="E112" s="2">
+        <v>100</v>
+      </c>
       <c r="F112" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16464,7 +16686,9 @@
       <c r="D113" s="126">
         <v>7328.3</v>
       </c>
-      <c r="E113" s="2"/>
+      <c r="E113" s="2">
+        <v>100</v>
+      </c>
       <c r="F113" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16489,7 +16713,9 @@
       <c r="D114" s="126">
         <v>10866.1</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" s="2">
+        <v>100</v>
+      </c>
       <c r="F114" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16514,7 +16740,9 @@
       <c r="D115" s="126">
         <v>14277.6</v>
       </c>
-      <c r="E115" s="2"/>
+      <c r="E115" s="2">
+        <v>100</v>
+      </c>
       <c r="F115" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16539,7 +16767,9 @@
       <c r="D116" s="130">
         <v>4652.3999999999996</v>
       </c>
-      <c r="E116" s="2"/>
+      <c r="E116" s="2">
+        <v>100</v>
+      </c>
       <c r="F116" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16564,7 +16794,9 @@
       <c r="D117" s="130">
         <v>54796</v>
       </c>
-      <c r="E117" s="2"/>
+      <c r="E117" s="2">
+        <v>100</v>
+      </c>
       <c r="F117" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16589,7 +16821,9 @@
       <c r="D118" s="130">
         <v>2000</v>
       </c>
-      <c r="E118" s="2"/>
+      <c r="E118" s="2">
+        <v>100</v>
+      </c>
       <c r="F118" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16614,7 +16848,9 @@
       <c r="D119" s="126">
         <v>2894.1</v>
       </c>
-      <c r="E119" s="2"/>
+      <c r="E119" s="2">
+        <v>100</v>
+      </c>
       <c r="F119" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16639,7 +16875,9 @@
       <c r="D120" s="126">
         <v>2194.5</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" s="2">
+        <v>100</v>
+      </c>
       <c r="F120" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16664,7 +16902,9 @@
       <c r="D121" s="131">
         <v>1158.7</v>
       </c>
-      <c r="E121" s="2"/>
+      <c r="E121" s="2">
+        <v>100</v>
+      </c>
       <c r="F121" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16689,7 +16929,9 @@
       <c r="D122" s="34">
         <v>3072.3</v>
       </c>
-      <c r="E122" s="2"/>
+      <c r="E122" s="2">
+        <v>100</v>
+      </c>
       <c r="F122" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16715,7 +16957,9 @@
       <c r="D123" s="132">
         <v>17117.099999999999</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" s="2">
+        <v>100</v>
+      </c>
       <c r="F123" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16740,7 +16984,9 @@
       <c r="D124" s="34">
         <v>1154.5</v>
       </c>
-      <c r="E124" s="2"/>
+      <c r="E124" s="2">
+        <v>100</v>
+      </c>
       <c r="F124" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16765,7 +17011,9 @@
       <c r="D125" s="34">
         <v>2989.2</v>
       </c>
-      <c r="E125" s="2"/>
+      <c r="E125" s="2">
+        <v>100</v>
+      </c>
       <c r="F125" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16790,7 +17038,9 @@
       <c r="D126" s="34">
         <v>3916.9</v>
       </c>
-      <c r="E126" s="2"/>
+      <c r="E126" s="2">
+        <v>100</v>
+      </c>
       <c r="F126" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16815,7 +17065,9 @@
       <c r="D127" s="34">
         <v>12369</v>
       </c>
-      <c r="E127" s="2"/>
+      <c r="E127" s="2">
+        <v>100</v>
+      </c>
       <c r="F127" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16840,7 +17092,9 @@
       <c r="D128" s="34">
         <v>19092.2</v>
       </c>
-      <c r="E128" s="2"/>
+      <c r="E128" s="2">
+        <v>100</v>
+      </c>
       <c r="F128" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16865,7 +17119,9 @@
       <c r="D129" s="34">
         <v>19295.7</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" s="2">
+        <v>100</v>
+      </c>
       <c r="F129" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16890,7 +17146,9 @@
       <c r="D130" s="126">
         <v>19460.599999999999</v>
       </c>
-      <c r="E130" s="2"/>
+      <c r="E130" s="2">
+        <v>100</v>
+      </c>
       <c r="F130" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16915,7 +17173,9 @@
       <c r="D131" s="126">
         <v>46179.4</v>
       </c>
-      <c r="E131" s="2"/>
+      <c r="E131" s="2">
+        <v>100</v>
+      </c>
       <c r="F131" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16940,7 +17200,9 @@
       <c r="D132" s="126">
         <v>1782.6</v>
       </c>
-      <c r="E132" s="2"/>
+      <c r="E132" s="2">
+        <v>100</v>
+      </c>
       <c r="F132" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16965,7 +17227,9 @@
       <c r="D133" s="126">
         <v>31920</v>
       </c>
-      <c r="E133" s="2"/>
+      <c r="E133" s="2">
+        <v>100</v>
+      </c>
       <c r="F133" s="34" t="s">
         <v>1544</v>
       </c>
@@ -16990,7 +17254,9 @@
       <c r="D134" s="128">
         <v>2229.6</v>
       </c>
-      <c r="E134" s="2"/>
+      <c r="E134" s="2">
+        <v>100</v>
+      </c>
       <c r="F134" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17015,7 +17281,9 @@
       <c r="D135" s="126">
         <v>1489.6</v>
       </c>
-      <c r="E135" s="2"/>
+      <c r="E135" s="2">
+        <v>100</v>
+      </c>
       <c r="F135" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17040,7 +17308,9 @@
       <c r="D136" s="127">
         <v>21439.599999999999</v>
       </c>
-      <c r="E136" s="2"/>
+      <c r="E136" s="2">
+        <v>100</v>
+      </c>
       <c r="F136" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17065,7 +17335,9 @@
       <c r="D137" s="126">
         <v>8778</v>
       </c>
-      <c r="E137" s="2"/>
+      <c r="E137" s="2">
+        <v>100</v>
+      </c>
       <c r="F137" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17090,7 +17362,9 @@
       <c r="D138" s="126">
         <v>854.1</v>
       </c>
-      <c r="E138" s="2"/>
+      <c r="E138" s="2">
+        <v>100</v>
+      </c>
       <c r="F138" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17115,7 +17389,9 @@
       <c r="D139" s="126">
         <v>1896.6</v>
       </c>
-      <c r="E139" s="2"/>
+      <c r="E139" s="2">
+        <v>100</v>
+      </c>
       <c r="F139" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17140,7 +17416,9 @@
       <c r="D140" s="127">
         <v>2506.8000000000002</v>
       </c>
-      <c r="E140" s="2"/>
+      <c r="E140" s="2">
+        <v>100</v>
+      </c>
       <c r="F140" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17165,7 +17443,9 @@
       <c r="D141" s="129">
         <v>4123</v>
       </c>
-      <c r="E141" s="2"/>
+      <c r="E141" s="2">
+        <v>100</v>
+      </c>
       <c r="F141" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17190,7 +17470,9 @@
       <c r="D142" s="34">
         <v>5772.2</v>
       </c>
-      <c r="E142" s="2"/>
+      <c r="E142" s="2">
+        <v>100</v>
+      </c>
       <c r="F142" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17215,7 +17497,9 @@
       <c r="D143" s="127">
         <v>766.1</v>
       </c>
-      <c r="E143" s="2"/>
+      <c r="E143" s="2">
+        <v>100</v>
+      </c>
       <c r="F143" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17240,7 +17524,9 @@
       <c r="D144" s="127">
         <v>51072</v>
       </c>
-      <c r="E144" s="2"/>
+      <c r="E144" s="2">
+        <v>100</v>
+      </c>
       <c r="F144" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17265,7 +17551,9 @@
       <c r="D145" s="127">
         <v>62988.800000000003</v>
       </c>
-      <c r="E145" s="2"/>
+      <c r="E145" s="2">
+        <v>100</v>
+      </c>
       <c r="F145" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17290,7 +17578,9 @@
       <c r="D146" s="127">
         <v>5091.3</v>
       </c>
-      <c r="E146" s="2"/>
+      <c r="E146" s="2">
+        <v>100</v>
+      </c>
       <c r="F146" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17315,7 +17605,9 @@
       <c r="D147" s="127">
         <v>8086.4</v>
       </c>
-      <c r="E147" s="2"/>
+      <c r="E147" s="2">
+        <v>100</v>
+      </c>
       <c r="F147" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17340,7 +17632,9 @@
       <c r="D148" s="127">
         <v>1207.0999999999999</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" s="2">
+        <v>100</v>
+      </c>
       <c r="F148" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17365,7 +17659,9 @@
       <c r="D149" s="127">
         <v>790.1</v>
       </c>
-      <c r="E149" s="2"/>
+      <c r="E149" s="2">
+        <v>100</v>
+      </c>
       <c r="F149" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17390,7 +17686,9 @@
       <c r="D150" s="127">
         <v>877.8</v>
       </c>
-      <c r="E150" s="2"/>
+      <c r="E150" s="2">
+        <v>100</v>
+      </c>
       <c r="F150" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17413,7 +17711,9 @@
       <c r="D151" s="127">
         <v>1848.2</v>
       </c>
-      <c r="E151" s="2"/>
+      <c r="E151" s="2">
+        <v>100</v>
+      </c>
       <c r="F151" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17438,7 +17738,9 @@
       <c r="D152" s="127">
         <v>4568.6000000000004</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" s="2">
+        <v>100</v>
+      </c>
       <c r="F152" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17463,7 +17765,9 @@
       <c r="D153" s="127">
         <v>2879.4</v>
       </c>
-      <c r="E153" s="2"/>
+      <c r="E153" s="2">
+        <v>100</v>
+      </c>
       <c r="F153" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17488,7 +17792,9 @@
       <c r="D154" s="127">
         <v>1448.4</v>
       </c>
-      <c r="E154" s="2"/>
+      <c r="E154" s="2">
+        <v>100</v>
+      </c>
       <c r="F154" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17513,7 +17819,9 @@
       <c r="D155" s="127">
         <v>2414</v>
       </c>
-      <c r="E155" s="2"/>
+      <c r="E155" s="2">
+        <v>100</v>
+      </c>
       <c r="F155" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17538,7 +17846,9 @@
       <c r="D156" s="127">
         <v>2194.5</v>
       </c>
-      <c r="E156" s="2"/>
+      <c r="E156" s="2">
+        <v>100</v>
+      </c>
       <c r="F156" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17563,7 +17873,9 @@
       <c r="D157" s="127">
         <v>2633.4</v>
       </c>
-      <c r="E157" s="2"/>
+      <c r="E157" s="2">
+        <v>100</v>
+      </c>
       <c r="F157" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17588,7 +17900,9 @@
       <c r="D158" s="127">
         <v>1242.8</v>
       </c>
-      <c r="E158" s="2"/>
+      <c r="E158" s="2">
+        <v>100</v>
+      </c>
       <c r="F158" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17613,7 +17927,9 @@
       <c r="D159" s="127">
         <v>1276.9000000000001</v>
       </c>
-      <c r="E159" s="2"/>
+      <c r="E159" s="2">
+        <v>100</v>
+      </c>
       <c r="F159" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17638,7 +17954,9 @@
       <c r="D160" s="127">
         <v>1327.9</v>
       </c>
-      <c r="E160" s="2"/>
+      <c r="E160" s="2">
+        <v>100</v>
+      </c>
       <c r="F160" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17663,7 +17981,9 @@
       <c r="D161" s="127">
         <v>1413</v>
       </c>
-      <c r="E161" s="2"/>
+      <c r="E161" s="2">
+        <v>100</v>
+      </c>
       <c r="F161" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17688,7 +18008,9 @@
       <c r="D162" s="127">
         <v>1651.2</v>
       </c>
-      <c r="E162" s="2"/>
+      <c r="E162" s="2">
+        <v>100</v>
+      </c>
       <c r="F162" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17713,7 +18035,9 @@
       <c r="D163" s="127">
         <v>1787.6</v>
       </c>
-      <c r="E163" s="2"/>
+      <c r="E163" s="2">
+        <v>100</v>
+      </c>
       <c r="F163" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17738,7 +18062,9 @@
       <c r="D164" s="127">
         <v>1872.5</v>
       </c>
-      <c r="E164" s="2"/>
+      <c r="E164" s="2">
+        <v>100</v>
+      </c>
       <c r="F164" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17763,7 +18089,9 @@
       <c r="D165" s="127">
         <v>2042.9</v>
       </c>
-      <c r="E165" s="2"/>
+      <c r="E165" s="2">
+        <v>100</v>
+      </c>
       <c r="F165" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17788,7 +18116,9 @@
       <c r="D166" s="127">
         <v>2370.1</v>
       </c>
-      <c r="E166" s="2"/>
+      <c r="E166" s="2">
+        <v>100</v>
+      </c>
       <c r="F166" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17813,7 +18143,9 @@
       <c r="D167" s="127">
         <v>3142.6</v>
       </c>
-      <c r="E167" s="2"/>
+      <c r="E167" s="2">
+        <v>100</v>
+      </c>
       <c r="F167" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17838,7 +18170,9 @@
       <c r="D168" s="127">
         <v>2809</v>
       </c>
-      <c r="E168" s="2"/>
+      <c r="E168" s="2">
+        <v>100</v>
+      </c>
       <c r="F168" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17863,7 +18197,9 @@
       <c r="D169" s="127">
         <v>3330.7</v>
       </c>
-      <c r="E169" s="2"/>
+      <c r="E169" s="2">
+        <v>100</v>
+      </c>
       <c r="F169" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17888,7 +18224,9 @@
       <c r="D170" s="127">
         <v>4143.2</v>
       </c>
-      <c r="E170" s="2"/>
+      <c r="E170" s="2">
+        <v>100</v>
+      </c>
       <c r="F170" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17913,7 +18251,9 @@
       <c r="D171" s="127">
         <v>3915.6</v>
       </c>
-      <c r="E171" s="2"/>
+      <c r="E171" s="2">
+        <v>100</v>
+      </c>
       <c r="F171" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17938,7 +18278,9 @@
       <c r="D172" s="127">
         <v>2511.1</v>
       </c>
-      <c r="E172" s="2"/>
+      <c r="E172" s="2">
+        <v>100</v>
+      </c>
       <c r="F172" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17963,7 +18305,9 @@
       <c r="D173" s="127">
         <v>1213</v>
       </c>
-      <c r="E173" s="2"/>
+      <c r="E173" s="2">
+        <v>100</v>
+      </c>
       <c r="F173" s="34" t="s">
         <v>1544</v>
       </c>
@@ -17988,7 +18332,9 @@
       <c r="D174" s="126">
         <v>9235.6</v>
       </c>
-      <c r="E174" s="2"/>
+      <c r="E174" s="2">
+        <v>100</v>
+      </c>
       <c r="F174" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18013,7 +18359,9 @@
       <c r="D175" s="127">
         <v>3160.1</v>
       </c>
-      <c r="E175" s="2"/>
+      <c r="E175" s="2">
+        <v>100</v>
+      </c>
       <c r="F175" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18036,7 +18384,9 @@
       <c r="D176" s="127">
         <v>4336.3999999999996</v>
       </c>
-      <c r="E176" s="2"/>
+      <c r="E176" s="2">
+        <v>100</v>
+      </c>
       <c r="F176" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18059,7 +18409,9 @@
       <c r="D177" s="127">
         <v>4740.2</v>
       </c>
-      <c r="E177" s="2"/>
+      <c r="E177" s="2">
+        <v>100</v>
+      </c>
       <c r="F177" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18082,7 +18434,9 @@
       <c r="D178" s="127">
         <v>39153.699999999997</v>
       </c>
-      <c r="E178" s="2"/>
+      <c r="E178" s="2">
+        <v>100</v>
+      </c>
       <c r="F178" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18107,7 +18461,9 @@
       <c r="D179" s="127">
         <v>3182.1</v>
       </c>
-      <c r="E179" s="2"/>
+      <c r="E179" s="2">
+        <v>100</v>
+      </c>
       <c r="F179" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18132,7 +18488,9 @@
       <c r="D180" s="127">
         <v>329.3</v>
       </c>
-      <c r="E180" s="2"/>
+      <c r="E180" s="2">
+        <v>100</v>
+      </c>
       <c r="F180" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18157,7 +18515,9 @@
       <c r="D181" s="127">
         <v>3689.8</v>
       </c>
-      <c r="E181" s="2"/>
+      <c r="E181" s="2">
+        <v>100</v>
+      </c>
       <c r="F181" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18182,7 +18542,9 @@
       <c r="D182" s="127">
         <v>3319.8</v>
       </c>
-      <c r="E182" s="2"/>
+      <c r="E182" s="2">
+        <v>100</v>
+      </c>
       <c r="F182" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18205,7 +18567,9 @@
       <c r="D183" s="127">
         <v>2839</v>
       </c>
-      <c r="E183" s="2"/>
+      <c r="E183" s="2">
+        <v>100</v>
+      </c>
       <c r="F183" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18229,7 +18593,9 @@
       <c r="D184" s="128">
         <v>2633.4</v>
       </c>
-      <c r="E184" s="2"/>
+      <c r="E184" s="2">
+        <v>100</v>
+      </c>
       <c r="F184" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18253,7 +18619,9 @@
       <c r="D185" s="128">
         <v>5047.3999999999996</v>
       </c>
-      <c r="E185" s="2"/>
+      <c r="E185" s="2">
+        <v>100</v>
+      </c>
       <c r="F185" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18276,7 +18644,9 @@
       <c r="D186" s="127">
         <v>17649.599999999999</v>
       </c>
-      <c r="E186" s="2"/>
+      <c r="E186" s="2">
+        <v>100</v>
+      </c>
       <c r="F186" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18302,7 +18672,9 @@
       <c r="D187" s="127">
         <v>1053.4000000000001</v>
       </c>
-      <c r="E187" s="2"/>
+      <c r="E187" s="2">
+        <v>100</v>
+      </c>
       <c r="F187" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18328,7 +18700,9 @@
       <c r="D188" s="127">
         <v>1229</v>
       </c>
-      <c r="E188" s="2"/>
+      <c r="E188" s="2">
+        <v>100</v>
+      </c>
       <c r="F188" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18354,7 +18728,9 @@
       <c r="D189" s="127">
         <v>790.1</v>
       </c>
-      <c r="E189" s="2"/>
+      <c r="E189" s="2">
+        <v>100</v>
+      </c>
       <c r="F189" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18379,7 +18755,9 @@
       <c r="D190" s="127">
         <v>1872.7</v>
       </c>
-      <c r="E190" s="2"/>
+      <c r="E190" s="2">
+        <v>100</v>
+      </c>
       <c r="F190" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18404,7 +18782,9 @@
       <c r="D191" s="127">
         <v>3621</v>
       </c>
-      <c r="E191" s="2"/>
+      <c r="E191" s="2">
+        <v>100</v>
+      </c>
       <c r="F191" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18429,7 +18809,9 @@
       <c r="D192" s="127">
         <v>4367.1000000000004</v>
       </c>
-      <c r="E192" s="2"/>
+      <c r="E192" s="2">
+        <v>100</v>
+      </c>
       <c r="F192" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18454,7 +18836,9 @@
       <c r="D193" s="127">
         <v>2194.5</v>
       </c>
-      <c r="E193" s="2"/>
+      <c r="E193" s="2">
+        <v>100</v>
+      </c>
       <c r="F193" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18479,7 +18863,9 @@
       <c r="D194" s="127">
         <v>3048.5</v>
       </c>
-      <c r="E194" s="2"/>
+      <c r="E194" s="2">
+        <v>100</v>
+      </c>
       <c r="F194" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18502,7 +18888,9 @@
       <c r="D195" s="127">
         <v>6254.4</v>
       </c>
-      <c r="E195" s="2"/>
+      <c r="E195" s="2">
+        <v>100</v>
+      </c>
       <c r="F195" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18525,7 +18913,9 @@
       <c r="D196" s="127">
         <v>595.9</v>
       </c>
-      <c r="E196" s="2"/>
+      <c r="E196" s="2">
+        <v>100</v>
+      </c>
       <c r="F196" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18548,7 +18938,9 @@
       <c r="D197" s="127">
         <v>10533.6</v>
       </c>
-      <c r="E197" s="2"/>
+      <c r="E197" s="2">
+        <v>100</v>
+      </c>
       <c r="F197" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18570,7 +18962,9 @@
       <c r="D198" s="127">
         <v>28117.9</v>
       </c>
-      <c r="E198" s="2"/>
+      <c r="E198" s="2">
+        <v>100</v>
+      </c>
       <c r="F198" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18593,7 +18987,9 @@
       <c r="D199" s="126">
         <v>2633.4</v>
       </c>
-      <c r="E199" s="2"/>
+      <c r="E199" s="2">
+        <v>100</v>
+      </c>
       <c r="F199" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18618,7 +19014,9 @@
       <c r="D200" s="126">
         <v>2809</v>
       </c>
-      <c r="E200" s="2"/>
+      <c r="E200" s="2">
+        <v>100</v>
+      </c>
       <c r="F200" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18643,7 +19041,9 @@
       <c r="D201" s="126">
         <v>3072.3</v>
       </c>
-      <c r="E201" s="2"/>
+      <c r="E201" s="2">
+        <v>100</v>
+      </c>
       <c r="F201" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18668,7 +19068,9 @@
       <c r="D202" s="126">
         <v>8171.6</v>
       </c>
-      <c r="E202" s="2"/>
+      <c r="E202" s="2">
+        <v>100</v>
+      </c>
       <c r="F202" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18691,7 +19093,9 @@
       <c r="D203" s="126">
         <v>1316.7</v>
       </c>
-      <c r="E203" s="2"/>
+      <c r="E203" s="2">
+        <v>100</v>
+      </c>
       <c r="F203" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18714,7 +19118,9 @@
       <c r="D204" s="126">
         <v>4389</v>
       </c>
-      <c r="E204" s="2"/>
+      <c r="E204" s="2">
+        <v>100</v>
+      </c>
       <c r="F204" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18737,7 +19143,9 @@
       <c r="D205" s="126">
         <v>3472.9</v>
       </c>
-      <c r="E205" s="2"/>
+      <c r="E205" s="2">
+        <v>100</v>
+      </c>
       <c r="F205" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18760,7 +19168,9 @@
       <c r="D206" s="126">
         <v>957.6</v>
       </c>
-      <c r="E206" s="2"/>
+      <c r="E206" s="2">
+        <v>100</v>
+      </c>
       <c r="F206" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18781,7 +19191,9 @@
       <c r="D207" s="127">
         <v>3660.2</v>
       </c>
-      <c r="E207" s="2"/>
+      <c r="E207" s="2">
+        <v>100</v>
+      </c>
       <c r="F207" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18804,7 +19216,9 @@
       <c r="D208" s="127">
         <v>10554.9</v>
       </c>
-      <c r="E208" s="2"/>
+      <c r="E208" s="2">
+        <v>100</v>
+      </c>
       <c r="F208" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18828,7 +19242,9 @@
       <c r="D209" s="126">
         <v>985.6</v>
       </c>
-      <c r="E209" s="2"/>
+      <c r="E209" s="2">
+        <v>100</v>
+      </c>
       <c r="F209" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18853,7 +19269,9 @@
       <c r="D210" s="128">
         <v>14363.6</v>
       </c>
-      <c r="E210" s="2"/>
+      <c r="E210" s="2">
+        <v>100</v>
+      </c>
       <c r="F210" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18878,7 +19296,9 @@
       <c r="D211" s="126">
         <v>4681.6000000000004</v>
       </c>
-      <c r="E211" s="2"/>
+      <c r="E211" s="2">
+        <v>100</v>
+      </c>
       <c r="F211" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18903,7 +19323,9 @@
       <c r="D212" s="126">
         <v>3745.3</v>
       </c>
-      <c r="E212" s="2"/>
+      <c r="E212" s="2">
+        <v>100</v>
+      </c>
       <c r="F212" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18928,7 +19350,9 @@
       <c r="D213" s="126">
         <v>14981.2</v>
       </c>
-      <c r="E213" s="2"/>
+      <c r="E213" s="2">
+        <v>100</v>
+      </c>
       <c r="F213" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18953,7 +19377,9 @@
       <c r="D214" s="126">
         <v>2157.1</v>
       </c>
-      <c r="E214" s="2"/>
+      <c r="E214" s="2">
+        <v>100</v>
+      </c>
       <c r="F214" s="34" t="s">
         <v>1544</v>
       </c>
@@ -18978,7 +19404,9 @@
       <c r="D215" s="126">
         <v>2342.4</v>
       </c>
-      <c r="E215" s="2"/>
+      <c r="E215" s="2">
+        <v>100</v>
+      </c>
       <c r="F215" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19003,7 +19431,9 @@
       <c r="D216" s="126">
         <v>2408.9</v>
       </c>
-      <c r="E216" s="2"/>
+      <c r="E216" s="2">
+        <v>100</v>
+      </c>
       <c r="F216" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19028,7 +19458,9 @@
       <c r="D217" s="126">
         <v>1021.6</v>
       </c>
-      <c r="E217" s="2"/>
+      <c r="E217" s="2">
+        <v>100</v>
+      </c>
       <c r="F217" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19053,7 +19485,9 @@
       <c r="D218" s="126">
         <v>1786.5</v>
       </c>
-      <c r="E218" s="2"/>
+      <c r="E218" s="2">
+        <v>100</v>
+      </c>
       <c r="F218" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19078,7 +19512,9 @@
       <c r="D219" s="126">
         <v>1855.7</v>
       </c>
-      <c r="E219" s="2"/>
+      <c r="E219" s="2">
+        <v>100</v>
+      </c>
       <c r="F219" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19103,7 +19539,9 @@
       <c r="D220" s="126">
         <v>2342.4</v>
       </c>
-      <c r="E220" s="2"/>
+      <c r="E220" s="2">
+        <v>100</v>
+      </c>
       <c r="F220" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19128,7 +19566,9 @@
       <c r="D221" s="126">
         <v>973.3</v>
       </c>
-      <c r="E221" s="2"/>
+      <c r="E221" s="2">
+        <v>100</v>
+      </c>
       <c r="F221" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19153,7 +19593,9 @@
       <c r="D222" s="126">
         <v>1430</v>
       </c>
-      <c r="E222" s="2"/>
+      <c r="E222" s="2">
+        <v>100</v>
+      </c>
       <c r="F222" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19178,7 +19620,9 @@
       <c r="D223" s="126">
         <v>5940.6</v>
       </c>
-      <c r="E223" s="2"/>
+      <c r="E223" s="2">
+        <v>100</v>
+      </c>
       <c r="F223" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19203,7 +19647,9 @@
       <c r="D224" s="128">
         <v>5618</v>
       </c>
-      <c r="E224" s="2"/>
+      <c r="E224" s="2">
+        <v>100</v>
+      </c>
       <c r="F224" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19228,7 +19674,9 @@
       <c r="D225" s="126">
         <v>5047.3999999999996</v>
       </c>
-      <c r="E225" s="2"/>
+      <c r="E225" s="2">
+        <v>100</v>
+      </c>
       <c r="F225" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19253,7 +19701,9 @@
       <c r="D226" s="126">
         <v>4256</v>
       </c>
-      <c r="E226" s="2"/>
+      <c r="E226" s="2">
+        <v>100</v>
+      </c>
       <c r="F226" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19278,7 +19728,9 @@
       <c r="D227" s="126">
         <v>6384</v>
       </c>
-      <c r="E227" s="2"/>
+      <c r="E227" s="2">
+        <v>100</v>
+      </c>
       <c r="F227" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19303,7 +19755,9 @@
       <c r="D228" s="126">
         <v>9853</v>
       </c>
-      <c r="E228" s="2"/>
+      <c r="E228" s="2">
+        <v>100</v>
+      </c>
       <c r="F228" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19328,7 +19782,9 @@
       <c r="D229" s="126">
         <v>2832.3</v>
       </c>
-      <c r="E229" s="2"/>
+      <c r="E229" s="2">
+        <v>100</v>
+      </c>
       <c r="F229" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19353,7 +19809,9 @@
       <c r="D230" s="126">
         <v>936.4</v>
       </c>
-      <c r="E230" s="2"/>
+      <c r="E230" s="2">
+        <v>100</v>
+      </c>
       <c r="F230" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19378,7 +19836,9 @@
       <c r="D231" s="126">
         <v>970.4</v>
       </c>
-      <c r="E231" s="2"/>
+      <c r="E231" s="2">
+        <v>100</v>
+      </c>
       <c r="F231" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19403,7 +19863,9 @@
       <c r="D232" s="126">
         <v>1075.5</v>
       </c>
-      <c r="E232" s="2"/>
+      <c r="E232" s="2">
+        <v>100</v>
+      </c>
       <c r="F232" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19428,7 +19890,9 @@
       <c r="D233" s="126">
         <v>1106.5999999999999</v>
       </c>
-      <c r="E233" s="2"/>
+      <c r="E233" s="2">
+        <v>100</v>
+      </c>
       <c r="F233" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19453,7 +19917,9 @@
       <c r="D234" s="126">
         <v>1191.7</v>
       </c>
-      <c r="E234" s="2"/>
+      <c r="E234" s="2">
+        <v>100</v>
+      </c>
       <c r="F234" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19479,7 +19945,9 @@
       <c r="D235" s="126">
         <v>1276.8</v>
       </c>
-      <c r="E235" s="2"/>
+      <c r="E235" s="2">
+        <v>100</v>
+      </c>
       <c r="F235" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19504,7 +19972,9 @@
       <c r="D236" s="126">
         <v>1327.9</v>
       </c>
-      <c r="E236" s="2"/>
+      <c r="E236" s="2">
+        <v>100</v>
+      </c>
       <c r="F236" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19529,7 +19999,9 @@
       <c r="D237" s="128">
         <v>1413</v>
       </c>
-      <c r="E237" s="2"/>
+      <c r="E237" s="2">
+        <v>100</v>
+      </c>
       <c r="F237" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19554,7 +20026,9 @@
       <c r="D238" s="126">
         <v>1532.2</v>
       </c>
-      <c r="E238" s="2"/>
+      <c r="E238" s="2">
+        <v>100</v>
+      </c>
       <c r="F238" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19579,7 +20053,9 @@
       <c r="D239" s="126">
         <v>1685.4</v>
       </c>
-      <c r="E239" s="2"/>
+      <c r="E239" s="2">
+        <v>100</v>
+      </c>
       <c r="F239" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19604,7 +20080,9 @@
       <c r="D240" s="126">
         <v>1872.8</v>
       </c>
-      <c r="E240" s="2"/>
+      <c r="E240" s="2">
+        <v>100</v>
+      </c>
       <c r="F240" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19629,7 +20107,9 @@
       <c r="D241" s="126">
         <v>1957.8</v>
       </c>
-      <c r="E241" s="2"/>
+      <c r="E241" s="2">
+        <v>100</v>
+      </c>
       <c r="F241" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19654,7 +20134,9 @@
       <c r="D242" s="126">
         <v>2042.9</v>
       </c>
-      <c r="E242" s="2"/>
+      <c r="E242" s="2">
+        <v>100</v>
+      </c>
       <c r="F242" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19679,7 +20161,9 @@
       <c r="D243" s="126">
         <v>970.4</v>
       </c>
-      <c r="E243" s="2"/>
+      <c r="E243" s="2">
+        <v>100</v>
+      </c>
       <c r="F243" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19704,7 +20188,9 @@
       <c r="D244" s="126">
         <v>1072.5999999999999</v>
       </c>
-      <c r="E244" s="2"/>
+      <c r="E244" s="2">
+        <v>100</v>
+      </c>
       <c r="F244" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19729,7 +20215,9 @@
       <c r="D245" s="126">
         <v>1106.5999999999999</v>
       </c>
-      <c r="E245" s="2"/>
+      <c r="E245" s="2">
+        <v>100</v>
+      </c>
       <c r="F245" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19754,7 +20242,9 @@
       <c r="D246" s="126">
         <v>1191.7</v>
       </c>
-      <c r="E246" s="2"/>
+      <c r="E246" s="2">
+        <v>100</v>
+      </c>
       <c r="F246" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19779,7 +20269,9 @@
       <c r="D247" s="126">
         <v>1276.8</v>
       </c>
-      <c r="E247" s="2"/>
+      <c r="E247" s="2">
+        <v>100</v>
+      </c>
       <c r="F247" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19804,7 +20296,9 @@
       <c r="D248" s="126">
         <v>1413</v>
       </c>
-      <c r="E248" s="2"/>
+      <c r="E248" s="2">
+        <v>100</v>
+      </c>
       <c r="F248" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19829,7 +20323,9 @@
       <c r="D249" s="127">
         <v>1532.2</v>
       </c>
-      <c r="E249" s="2"/>
+      <c r="E249" s="2">
+        <v>100</v>
+      </c>
       <c r="F249" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19854,7 +20350,9 @@
       <c r="D250" s="127">
         <v>1685.4</v>
       </c>
-      <c r="E250" s="2"/>
+      <c r="E250" s="2">
+        <v>100</v>
+      </c>
       <c r="F250" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19879,7 +20377,9 @@
       <c r="D251" s="127">
         <v>1957.8</v>
       </c>
-      <c r="E251" s="2"/>
+      <c r="E251" s="2">
+        <v>100</v>
+      </c>
       <c r="F251" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19904,7 +20404,9 @@
       <c r="D252" s="127">
         <v>2042.9</v>
       </c>
-      <c r="E252" s="2"/>
+      <c r="E252" s="2">
+        <v>100</v>
+      </c>
       <c r="F252" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19929,7 +20431,9 @@
       <c r="D253" s="127">
         <v>2008.9</v>
       </c>
-      <c r="E253" s="2"/>
+      <c r="E253" s="2">
+        <v>100</v>
+      </c>
       <c r="F253" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19954,7 +20458,9 @@
       <c r="D254" s="127">
         <v>2383.4</v>
       </c>
-      <c r="E254" s="2"/>
+      <c r="E254" s="2">
+        <v>100</v>
+      </c>
       <c r="F254" s="34" t="s">
         <v>1544</v>
       </c>
@@ -19977,7 +20483,9 @@
       <c r="D255" s="127">
         <v>2723.9</v>
       </c>
-      <c r="E255" s="2"/>
+      <c r="E255" s="2">
+        <v>100</v>
+      </c>
       <c r="F255" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20000,7 +20508,9 @@
       <c r="D256" s="127">
         <v>724.2</v>
       </c>
-      <c r="E256" s="2"/>
+      <c r="E256" s="2">
+        <v>100</v>
+      </c>
       <c r="F256" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20025,7 +20535,9 @@
       <c r="D257" s="127">
         <v>3511.2</v>
       </c>
-      <c r="E257" s="2"/>
+      <c r="E257" s="2">
+        <v>100</v>
+      </c>
       <c r="F257" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20050,7 +20562,9 @@
       <c r="D258" s="127">
         <v>9873.2000000000007</v>
       </c>
-      <c r="E258" s="2"/>
+      <c r="E258" s="2">
+        <v>100</v>
+      </c>
       <c r="F258" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20075,7 +20589,9 @@
       <c r="D259" s="127">
         <v>6489.3</v>
       </c>
-      <c r="E259" s="2"/>
+      <c r="E259" s="2">
+        <v>100</v>
+      </c>
       <c r="F259" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20098,7 +20614,9 @@
       <c r="D260" s="127">
         <v>912.9</v>
       </c>
-      <c r="E260" s="2"/>
+      <c r="E260" s="2">
+        <v>100</v>
+      </c>
       <c r="F260" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20121,7 +20639,9 @@
       <c r="D261" s="127">
         <v>902.2</v>
       </c>
-      <c r="E261" s="2"/>
+      <c r="E261" s="2">
+        <v>100</v>
+      </c>
       <c r="F261" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20146,7 +20666,9 @@
       <c r="D262" s="127">
         <v>953.3</v>
       </c>
-      <c r="E262" s="2"/>
+      <c r="E262" s="2">
+        <v>100</v>
+      </c>
       <c r="F262" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20171,7 +20693,9 @@
       <c r="D263" s="127">
         <v>987.4</v>
       </c>
-      <c r="E263" s="2"/>
+      <c r="E263" s="2">
+        <v>100</v>
+      </c>
       <c r="F263" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20196,7 +20720,9 @@
       <c r="D264" s="127">
         <v>1106.0999999999999</v>
       </c>
-      <c r="E264" s="2"/>
+      <c r="E264" s="2">
+        <v>100</v>
+      </c>
       <c r="F264" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20221,7 +20747,9 @@
       <c r="D265" s="127">
         <v>1208.8</v>
       </c>
-      <c r="E265" s="2"/>
+      <c r="E265" s="2">
+        <v>100</v>
+      </c>
       <c r="F265" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20246,7 +20774,9 @@
       <c r="D266" s="127">
         <v>1327.9</v>
       </c>
-      <c r="E266" s="2"/>
+      <c r="E266" s="2">
+        <v>100</v>
+      </c>
       <c r="F266" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20271,7 +20801,9 @@
       <c r="D267" s="127">
         <v>2042.8</v>
       </c>
-      <c r="E267" s="2"/>
+      <c r="E267" s="2">
+        <v>100</v>
+      </c>
       <c r="F267" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20296,7 +20828,9 @@
       <c r="D268" s="127">
         <v>2702.6</v>
       </c>
-      <c r="E268" s="2"/>
+      <c r="E268" s="2">
+        <v>100</v>
+      </c>
       <c r="F268" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20321,7 +20855,9 @@
       <c r="D269" s="127">
         <v>15066.5</v>
       </c>
-      <c r="E269" s="2"/>
+      <c r="E269" s="2">
+        <v>100</v>
+      </c>
       <c r="F269" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20344,7 +20880,9 @@
       <c r="D270" s="128">
         <v>1172.5</v>
       </c>
-      <c r="E270" s="2"/>
+      <c r="E270" s="2">
+        <v>100</v>
+      </c>
       <c r="F270" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20367,7 +20905,9 @@
       <c r="D271" s="128">
         <v>1246.5</v>
       </c>
-      <c r="E271" s="2"/>
+      <c r="E271" s="2">
+        <v>100</v>
+      </c>
       <c r="F271" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20390,7 +20930,9 @@
       <c r="D272" s="127">
         <v>1369.4</v>
       </c>
-      <c r="E272" s="2"/>
+      <c r="E272" s="2">
+        <v>100</v>
+      </c>
       <c r="F272" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20413,7 +20955,9 @@
       <c r="D273" s="128">
         <v>17467.2</v>
       </c>
-      <c r="E273" s="2"/>
+      <c r="E273" s="2">
+        <v>100</v>
+      </c>
       <c r="F273" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20436,7 +20980,9 @@
       <c r="D274" s="127">
         <v>4341.2</v>
       </c>
-      <c r="E274" s="2"/>
+      <c r="E274" s="2">
+        <v>100</v>
+      </c>
       <c r="F274" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20459,7 +21005,9 @@
       <c r="D275" s="127">
         <v>13602.2</v>
       </c>
-      <c r="E275" s="2"/>
+      <c r="E275" s="2">
+        <v>100</v>
+      </c>
       <c r="F275" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20482,7 +21030,9 @@
       <c r="D276" s="127">
         <v>2896.8</v>
       </c>
-      <c r="E276" s="2"/>
+      <c r="E276" s="2">
+        <v>100</v>
+      </c>
       <c r="F276" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20505,7 +21055,9 @@
       <c r="D277" s="127">
         <v>5124</v>
       </c>
-      <c r="E277" s="2"/>
+      <c r="E277" s="2">
+        <v>100</v>
+      </c>
       <c r="F277" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20528,7 +21080,9 @@
       <c r="D278" s="127">
         <v>1158.7</v>
       </c>
-      <c r="E278" s="2"/>
+      <c r="E278" s="2">
+        <v>100</v>
+      </c>
       <c r="F278" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20551,7 +21105,9 @@
       <c r="D279" s="127">
         <v>6144.6</v>
       </c>
-      <c r="E279" s="2"/>
+      <c r="E279" s="2">
+        <v>100</v>
+      </c>
       <c r="F279" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20576,7 +21132,9 @@
       <c r="D280" s="127">
         <v>7916.2</v>
       </c>
-      <c r="E280" s="2"/>
+      <c r="E280" s="2">
+        <v>100</v>
+      </c>
       <c r="F280" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20599,7 +21157,9 @@
       <c r="D281" s="127">
         <v>9037.7999999999993</v>
       </c>
-      <c r="E281" s="2"/>
+      <c r="E281" s="2">
+        <v>100</v>
+      </c>
       <c r="F281" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20621,7 +21181,9 @@
       <c r="D282" s="128">
         <v>15098.2</v>
       </c>
-      <c r="E282" s="2"/>
+      <c r="E282" s="2">
+        <v>100</v>
+      </c>
       <c r="F282" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20644,7 +21206,9 @@
       <c r="D283" s="127">
         <v>6495.8</v>
       </c>
-      <c r="E283" s="2"/>
+      <c r="E283" s="2">
+        <v>100</v>
+      </c>
       <c r="F283" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20667,7 +21231,9 @@
       <c r="D284" s="127">
         <v>3160.1</v>
       </c>
-      <c r="E284" s="2"/>
+      <c r="E284" s="2">
+        <v>100</v>
+      </c>
       <c r="F284" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20692,7 +21258,9 @@
       <c r="D285" s="127">
         <v>647</v>
       </c>
-      <c r="E285" s="2"/>
+      <c r="E285" s="2">
+        <v>100</v>
+      </c>
       <c r="F285" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20715,7 +21283,9 @@
       <c r="D286" s="127">
         <v>7490</v>
       </c>
-      <c r="E286" s="2"/>
+      <c r="E286" s="2">
+        <v>100</v>
+      </c>
       <c r="F286" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20738,7 +21308,9 @@
       <c r="D287" s="127">
         <v>17380.5</v>
       </c>
-      <c r="E287" s="2"/>
+      <c r="E287" s="2">
+        <v>100</v>
+      </c>
       <c r="F287" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20763,7 +21335,9 @@
       <c r="D288" s="127">
         <v>4279.3</v>
       </c>
-      <c r="E288" s="2"/>
+      <c r="E288" s="2">
+        <v>100</v>
+      </c>
       <c r="F288" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20786,7 +21360,9 @@
       <c r="D289" s="127">
         <v>7000.5</v>
       </c>
-      <c r="E289" s="2"/>
+      <c r="E289" s="2">
+        <v>100</v>
+      </c>
       <c r="F289" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20809,7 +21385,9 @@
       <c r="D290" s="127">
         <v>12728.1</v>
       </c>
-      <c r="E290" s="2"/>
+      <c r="E290" s="2">
+        <v>100</v>
+      </c>
       <c r="F290" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20834,7 +21412,9 @@
       <c r="D291" s="127">
         <v>6758.5</v>
       </c>
-      <c r="E291" s="2"/>
+      <c r="E291" s="2">
+        <v>100</v>
+      </c>
       <c r="F291" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20857,7 +21437,9 @@
       <c r="D292" s="127">
         <v>8787.7000000000007</v>
       </c>
-      <c r="E292" s="2"/>
+      <c r="E292" s="2">
+        <v>100</v>
+      </c>
       <c r="F292" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20880,7 +21462,9 @@
       <c r="D293" s="127">
         <v>13266.8</v>
       </c>
-      <c r="E293" s="2"/>
+      <c r="E293" s="2">
+        <v>100</v>
+      </c>
       <c r="F293" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20903,7 +21487,9 @@
       <c r="D294" s="127">
         <v>14538.7</v>
       </c>
-      <c r="E294" s="2"/>
+      <c r="E294" s="2">
+        <v>100</v>
+      </c>
       <c r="F294" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20926,7 +21512,9 @@
       <c r="D295" s="128">
         <v>10870.1</v>
       </c>
-      <c r="E295" s="2"/>
+      <c r="E295" s="2">
+        <v>100</v>
+      </c>
       <c r="F295" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20951,7 +21539,9 @@
       <c r="D296" s="127">
         <v>10753</v>
       </c>
-      <c r="E296" s="2"/>
+      <c r="E296" s="2">
+        <v>100</v>
+      </c>
       <c r="F296" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20974,7 +21564,9 @@
       <c r="D297" s="127">
         <v>7241.9</v>
       </c>
-      <c r="E297" s="2"/>
+      <c r="E297" s="2">
+        <v>100</v>
+      </c>
       <c r="F297" s="34" t="s">
         <v>1544</v>
       </c>
@@ -20997,7 +21589,9 @@
       <c r="D298" s="127">
         <v>1896.6</v>
       </c>
-      <c r="E298" s="2"/>
+      <c r="E298" s="2">
+        <v>100</v>
+      </c>
       <c r="F298" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21022,7 +21616,9 @@
       <c r="D299" s="127">
         <v>17875.2</v>
       </c>
-      <c r="E299" s="2"/>
+      <c r="E299" s="2">
+        <v>100</v>
+      </c>
       <c r="F299" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21045,7 +21641,9 @@
       <c r="D300" s="127">
         <v>725.5</v>
       </c>
-      <c r="E300" s="2"/>
+      <c r="E300" s="2">
+        <v>100</v>
+      </c>
       <c r="F300" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21068,7 +21666,9 @@
       <c r="D301" s="126">
         <v>877.8</v>
       </c>
-      <c r="E301" s="2"/>
+      <c r="E301" s="2">
+        <v>100</v>
+      </c>
       <c r="F301" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21091,7 +21691,9 @@
       <c r="D302" s="126">
         <v>902.3</v>
       </c>
-      <c r="E302" s="2"/>
+      <c r="E302" s="2">
+        <v>100</v>
+      </c>
       <c r="F302" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21114,7 +21716,9 @@
       <c r="D303" s="126">
         <v>1053.4000000000001</v>
       </c>
-      <c r="E303" s="2"/>
+      <c r="E303" s="2">
+        <v>100</v>
+      </c>
       <c r="F303" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21137,7 +21741,9 @@
       <c r="D304" s="126">
         <v>4524.1000000000004</v>
       </c>
-      <c r="E304" s="2"/>
+      <c r="E304" s="2">
+        <v>100</v>
+      </c>
       <c r="F304" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21162,7 +21768,9 @@
       <c r="D305" s="126">
         <v>7794.9</v>
       </c>
-      <c r="E305" s="2"/>
+      <c r="E305" s="2">
+        <v>100</v>
+      </c>
       <c r="F305" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21187,7 +21795,9 @@
       <c r="D306" s="126">
         <v>1887.3</v>
       </c>
-      <c r="E306" s="2"/>
+      <c r="E306" s="2">
+        <v>100</v>
+      </c>
       <c r="F306" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21212,7 +21822,9 @@
       <c r="D307" s="128">
         <v>1401.9</v>
       </c>
-      <c r="E307" s="2"/>
+      <c r="E307" s="2">
+        <v>100</v>
+      </c>
       <c r="F307" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21235,7 +21847,9 @@
       <c r="D308" s="134">
         <v>2128.5</v>
       </c>
-      <c r="E308" s="2"/>
+      <c r="E308" s="2">
+        <v>100</v>
+      </c>
       <c r="F308" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21258,7 +21872,9 @@
       <c r="D309" s="126">
         <v>5091.3</v>
       </c>
-      <c r="E309" s="2"/>
+      <c r="E309" s="2">
+        <v>100</v>
+      </c>
       <c r="F309" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21283,7 +21899,9 @@
       <c r="D310" s="126">
         <v>681</v>
       </c>
-      <c r="E310" s="2"/>
+      <c r="E310" s="2">
+        <v>100</v>
+      </c>
       <c r="F310" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21308,7 +21926,9 @@
       <c r="D311" s="126">
         <v>1896.1</v>
       </c>
-      <c r="E311" s="2"/>
+      <c r="E311" s="2">
+        <v>100</v>
+      </c>
       <c r="F311" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21333,7 +21953,9 @@
       <c r="D312" s="126">
         <v>3369.4</v>
       </c>
-      <c r="E312" s="2"/>
+      <c r="E312" s="2">
+        <v>100</v>
+      </c>
       <c r="F312" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21356,7 +21978,9 @@
       <c r="D313" s="126">
         <v>4001.1</v>
       </c>
-      <c r="E313" s="2"/>
+      <c r="E313" s="2">
+        <v>100</v>
+      </c>
       <c r="F313" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21379,7 +22003,9 @@
       <c r="D314" s="126">
         <v>1540.5</v>
       </c>
-      <c r="E314" s="2"/>
+      <c r="E314" s="2">
+        <v>100</v>
+      </c>
       <c r="F314" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21404,7 +22030,9 @@
       <c r="D315" s="126">
         <v>3182.1</v>
       </c>
-      <c r="E315" s="2"/>
+      <c r="E315" s="2">
+        <v>100</v>
+      </c>
       <c r="F315" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21429,7 +22057,9 @@
       <c r="D316" s="127">
         <v>8081.1</v>
       </c>
-      <c r="E316" s="2"/>
+      <c r="E316" s="2">
+        <v>100</v>
+      </c>
       <c r="F316" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21452,7 +22082,9 @@
       <c r="D317" s="126">
         <v>4326.8</v>
       </c>
-      <c r="E317" s="2"/>
+      <c r="E317" s="2">
+        <v>100</v>
+      </c>
       <c r="F317" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21475,7 +22107,9 @@
       <c r="D318" s="126">
         <v>2553.6</v>
       </c>
-      <c r="E318" s="2"/>
+      <c r="E318" s="2">
+        <v>100</v>
+      </c>
       <c r="F318" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21498,7 +22132,9 @@
       <c r="D319" s="126">
         <v>395</v>
       </c>
-      <c r="E319" s="2"/>
+      <c r="E319" s="2">
+        <v>100</v>
+      </c>
       <c r="F319" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21523,7 +22159,9 @@
       <c r="D320" s="126">
         <v>535.70000000000005</v>
       </c>
-      <c r="E320" s="2"/>
+      <c r="E320" s="2">
+        <v>100</v>
+      </c>
       <c r="F320" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21548,7 +22186,9 @@
       <c r="D321" s="126">
         <v>691.2</v>
       </c>
-      <c r="E321" s="2"/>
+      <c r="E321" s="2">
+        <v>100</v>
+      </c>
       <c r="F321" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21573,7 +22213,9 @@
       <c r="D322" s="126">
         <v>1404.5</v>
       </c>
-      <c r="E322" s="2"/>
+      <c r="E322" s="2">
+        <v>100</v>
+      </c>
       <c r="F322" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21596,7 +22238,9 @@
       <c r="D323" s="126">
         <v>4266</v>
       </c>
-      <c r="E323" s="2"/>
+      <c r="E323" s="2">
+        <v>100</v>
+      </c>
       <c r="F323" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21619,7 +22263,9 @@
       <c r="D324" s="126">
         <v>2700</v>
       </c>
-      <c r="E324" s="2"/>
+      <c r="E324" s="2">
+        <v>100</v>
+      </c>
       <c r="F324" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21642,7 +22288,9 @@
       <c r="D325" s="126">
         <v>3118.5</v>
       </c>
-      <c r="E325" s="2"/>
+      <c r="E325" s="2">
+        <v>100</v>
+      </c>
       <c r="F325" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21664,7 +22312,9 @@
       <c r="D326" s="126">
         <v>2497.5</v>
       </c>
-      <c r="E326" s="2"/>
+      <c r="E326" s="2">
+        <v>100</v>
+      </c>
       <c r="F326" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21688,7 +22338,9 @@
       <c r="D327" s="126">
         <v>7965</v>
       </c>
-      <c r="E327" s="2"/>
+      <c r="E327" s="2">
+        <v>100</v>
+      </c>
       <c r="F327" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21710,7 +22362,9 @@
       <c r="D328" s="126">
         <v>8505</v>
       </c>
-      <c r="E328" s="2"/>
+      <c r="E328" s="2">
+        <v>100</v>
+      </c>
       <c r="F328" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21735,7 +22389,9 @@
       <c r="D329" s="126">
         <v>4468.8</v>
       </c>
-      <c r="E329" s="2"/>
+      <c r="E329" s="2">
+        <v>100</v>
+      </c>
       <c r="F329" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21758,7 +22414,9 @@
       <c r="D330" s="126">
         <v>1061.9000000000001</v>
       </c>
-      <c r="E330" s="2"/>
+      <c r="E330" s="2">
+        <v>100</v>
+      </c>
       <c r="F330" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21783,7 +22441,9 @@
       <c r="D331" s="126">
         <v>747.3</v>
       </c>
-      <c r="E331" s="2"/>
+      <c r="E331" s="2">
+        <v>100</v>
+      </c>
       <c r="F331" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21806,7 +22466,9 @@
       <c r="D332" s="126">
         <v>2305.1999999999998</v>
       </c>
-      <c r="E332" s="2"/>
+      <c r="E332" s="2">
+        <v>100</v>
+      </c>
       <c r="F332" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21829,7 +22491,9 @@
       <c r="D333" s="126">
         <v>4000.7</v>
       </c>
-      <c r="E333" s="2"/>
+      <c r="E333" s="2">
+        <v>100</v>
+      </c>
       <c r="F333" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21852,7 +22516,9 @@
       <c r="D334" s="126">
         <v>4652.3999999999996</v>
       </c>
-      <c r="E334" s="2"/>
+      <c r="E334" s="2">
+        <v>100</v>
+      </c>
       <c r="F334" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21875,7 +22541,9 @@
       <c r="D335" s="126">
         <v>2348.9</v>
       </c>
-      <c r="E335" s="2"/>
+      <c r="E335" s="2">
+        <v>100</v>
+      </c>
       <c r="F335" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21898,7 +22566,9 @@
       <c r="D336" s="126">
         <v>2348.9</v>
       </c>
-      <c r="E336" s="2"/>
+      <c r="E336" s="2">
+        <v>100</v>
+      </c>
       <c r="F336" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21919,7 +22589,9 @@
       <c r="D337" s="126">
         <v>34285.199999999997</v>
       </c>
-      <c r="E337" s="2"/>
+      <c r="E337" s="2">
+        <v>100</v>
+      </c>
       <c r="F337" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21940,7 +22612,9 @@
       <c r="D338" s="126">
         <v>26787.4</v>
       </c>
-      <c r="E338" s="2"/>
+      <c r="E338" s="2">
+        <v>100</v>
+      </c>
       <c r="F338" s="34" t="s">
         <v>1544</v>
       </c>
@@ -21961,7 +22635,9 @@
       <c r="D339" s="127">
         <v>2979.2</v>
       </c>
-      <c r="E339" s="2"/>
+      <c r="E339" s="2">
+        <v>100</v>
+      </c>
       <c r="F339" s="34" t="s">
         <v>1544</v>
       </c>
